--- a/research/traditional_assets/database/data/thailand/thailand_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_oil_gas_production_and_exploration.xlsx
@@ -650,10 +650,10 @@
         <v>0.1563156549883596</v>
       </c>
       <c r="X2">
-        <v>0.1216539724461118</v>
+        <v>0.1216334492913891</v>
       </c>
       <c r="Y2">
-        <v>0.03466168254224772</v>
+        <v>0.03468220569697048</v>
       </c>
       <c r="Z2">
         <v>0.6849889491053317</v>
@@ -662,10 +662,10 @@
         <v>0.1729503311031834</v>
       </c>
       <c r="AB2">
-        <v>0.107893554910682</v>
+        <v>0.1078774534055386</v>
       </c>
       <c r="AC2">
-        <v>0.0650567761925014</v>
+        <v>0.06507287769764476</v>
       </c>
       <c r="AD2">
         <v>3779.8</v>
@@ -787,10 +787,10 @@
         <v>0.1563156549883596</v>
       </c>
       <c r="X3">
-        <v>0.1216539724461118</v>
+        <v>0.1216334492913891</v>
       </c>
       <c r="Y3">
-        <v>0.03466168254224772</v>
+        <v>0.03468220569697048</v>
       </c>
       <c r="Z3">
         <v>0.6849889491053317</v>
@@ -799,10 +799,10 @@
         <v>0.1729503311031834</v>
       </c>
       <c r="AB3">
-        <v>0.107893554910682</v>
+        <v>0.1078774534055386</v>
       </c>
       <c r="AC3">
-        <v>0.0650567761925014</v>
+        <v>0.06507287769764476</v>
       </c>
       <c r="AD3">
         <v>3779.8</v>
@@ -1139,7 +1139,7 @@
         <v>10.4921077065924</v>
       </c>
       <c r="F2">
-        <v>8.67069883456549</v>
+        <v>8.8542584730031</v>
       </c>
       <c r="G2">
         <v>0.612391043712129</v>
@@ -1157,13 +1157,13 @@
         <v>13764.2</v>
       </c>
       <c r="L2">
-        <v>11865.0258889053</v>
+        <v>11896.9342002374</v>
       </c>
       <c r="M2">
         <v>13474.4</v>
       </c>
       <c r="N2">
-        <v>13584.9458889053</v>
+        <v>13616.8542002374</v>
       </c>
       <c r="O2">
         <v>3779.8</v>
@@ -1172,16 +1172,16 @@
         <v>5789.52</v>
       </c>
       <c r="Q2">
-        <v>0.107893554910682</v>
+        <v>0.107877453405539</v>
       </c>
       <c r="R2">
-        <v>0.106600808684375</v>
+        <v>0.10621549268602</v>
       </c>
       <c r="S2">
         <v>0.0577847822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.121653972446112</v>
+        <v>0.121633449291389</v>
       </c>
       <c r="X2">
-        <v>0.13249646351336</v>
+        <v>0.132473006799397</v>
       </c>
       <c r="Y2">
         <v>1.17311934261087</v>
@@ -1236,7 +1236,7 @@
         <v>13764.2</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1079912532697547</v>
+        <v>0.1079744267190534</v>
       </c>
       <c r="C2">
-        <v>17535.71865055446</v>
+        <v>17535.77995177093</v>
       </c>
       <c r="D2">
-        <v>13466.11865055446</v>
+        <v>13466.17995177093</v>
       </c>
       <c r="E2">
         <v>-3779.8</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1079912532697547</v>
+        <v>0.1079744267190534</v>
       </c>
       <c r="T2">
         <v>0.9618186075065633</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1079491185853493</v>
+        <v>0.1079211256877494</v>
       </c>
       <c r="C3">
-        <v>17363.84892595143</v>
+        <v>17364.85682985699</v>
       </c>
       <c r="D3">
-        <v>13469.68892595143</v>
+        <v>13470.69682985699</v>
       </c>
       <c r="E3">
         <v>-3604.36</v>
@@ -1539,37 +1539,37 @@
         <v>3390</v>
       </c>
       <c r="M3">
-        <v>11.84763473939995</v>
+        <v>11.60201873939995</v>
       </c>
       <c r="N3">
-        <v>3378.1523652606</v>
+        <v>3378.3979812606</v>
       </c>
       <c r="O3">
-        <v>675.6304730521201</v>
+        <v>675.6795962521201</v>
       </c>
       <c r="P3">
-        <v>2702.52189220848</v>
+        <v>2702.71838500848</v>
       </c>
       <c r="Q3">
-        <v>5484.721892208479</v>
+        <v>5484.918385008479</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1084938088517325</v>
+        <v>0.1084768463289044</v>
       </c>
       <c r="T3">
         <v>0.969590879082374</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>286.1330615406611</v>
+        <v>292.1905296091022</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1079069839009438</v>
+        <v>0.1078678246564453</v>
       </c>
       <c r="C4">
-        <v>17191.98109502647</v>
+        <v>17193.93673909716</v>
       </c>
       <c r="D4">
-        <v>13473.26109502648</v>
+        <v>13475.21673909716</v>
       </c>
       <c r="E4">
         <v>-3428.92</v>
@@ -1621,37 +1621,37 @@
         <v>3390</v>
       </c>
       <c r="M4">
-        <v>23.6952694787999</v>
+        <v>23.2040374787999</v>
       </c>
       <c r="N4">
-        <v>3366.3047305212</v>
+        <v>3366.7959625212</v>
       </c>
       <c r="O4">
-        <v>673.2609461042401</v>
+        <v>673.3591925042401</v>
       </c>
       <c r="P4">
-        <v>2693.04378441696</v>
+        <v>2693.43677001696</v>
       </c>
       <c r="Q4">
-        <v>5475.24378441696</v>
+        <v>5475.636770016959</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1090066206700772</v>
+        <v>0.1089895194001808</v>
       </c>
       <c r="T4">
         <v>0.977521768445446</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>143.0665307703306</v>
+        <v>146.0952648045511</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1078648492165384</v>
+        <v>0.1078145236251413</v>
       </c>
       <c r="C5">
-        <v>17020.11515928662</v>
+        <v>17023.01968254364</v>
       </c>
       <c r="D5">
-        <v>13476.83515928662</v>
+        <v>13479.73968254364</v>
       </c>
       <c r="E5">
         <v>-3253.48</v>
@@ -1703,37 +1703,37 @@
         <v>3390</v>
       </c>
       <c r="M5">
-        <v>35.54290421819984</v>
+        <v>34.80605621819985</v>
       </c>
       <c r="N5">
-        <v>3354.4570957818</v>
+        <v>3355.1939437818</v>
       </c>
       <c r="O5">
-        <v>670.89141915636</v>
+        <v>671.0387887563601</v>
       </c>
       <c r="P5">
-        <v>2683.56567662544</v>
+        <v>2684.15515502544</v>
       </c>
       <c r="Q5">
-        <v>5465.76567662544</v>
+        <v>5466.35515502544</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1095300059279754</v>
+        <v>0.1095127630502465</v>
       </c>
       <c r="T5">
         <v>0.9856161813005401</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>95.37768718022038</v>
+        <v>97.39684320303408</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1078227145321329</v>
+        <v>0.1077612225938372</v>
       </c>
       <c r="C6">
-        <v>16848.25112024047</v>
+        <v>16852.10566325275</v>
       </c>
       <c r="D6">
-        <v>13480.41112024047</v>
+        <v>13484.26566325275</v>
       </c>
       <c r="E6">
         <v>-3078.04</v>
@@ -1785,37 +1785,37 @@
         <v>3390</v>
       </c>
       <c r="M6">
-        <v>47.3905389575998</v>
+        <v>46.4080749575998</v>
       </c>
       <c r="N6">
-        <v>3342.6094610424</v>
+        <v>3343.5919250424</v>
       </c>
       <c r="O6">
-        <v>668.52189220848</v>
+        <v>668.7183850084801</v>
       </c>
       <c r="P6">
-        <v>2674.08756883392</v>
+        <v>2674.87354003392</v>
       </c>
       <c r="Q6">
-        <v>5456.28756883392</v>
+        <v>5457.07354003392</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1100642950454132</v>
+        <v>0.1100469076096885</v>
       </c>
       <c r="T6">
         <v>0.9938792277567822</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>71.53326538516527</v>
+        <v>73.04763240227555</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1077805798477274</v>
+        <v>0.1077079215625332</v>
       </c>
       <c r="C7">
-        <v>16676.38897939825</v>
+        <v>16681.19468428491</v>
       </c>
       <c r="D7">
-        <v>13483.98897939825</v>
+        <v>13488.79468428491</v>
       </c>
       <c r="E7">
         <v>-2902.6</v>
@@ -1867,37 +1867,37 @@
         <v>3390</v>
       </c>
       <c r="M7">
-        <v>59.23817369699975</v>
+        <v>58.01009369699975</v>
       </c>
       <c r="N7">
-        <v>3330.761826303</v>
+        <v>3331.989906303</v>
       </c>
       <c r="O7">
-        <v>666.1523652606002</v>
+        <v>666.3979812606001</v>
       </c>
       <c r="P7">
-        <v>2664.6094610424</v>
+        <v>2665.5919250424</v>
       </c>
       <c r="Q7">
-        <v>5446.8094610424</v>
+        <v>5447.7919250424</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.110609832354797</v>
+        <v>0.1105922973177504</v>
       </c>
       <c r="T7">
         <v>1.002316233085787</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.22661230813222</v>
+        <v>58.43810592182044</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.107738445163322</v>
+        <v>0.1076546205312291</v>
       </c>
       <c r="C8">
-        <v>16504.52873827178</v>
+        <v>16510.28674870464</v>
       </c>
       <c r="D8">
-        <v>13487.56873827178</v>
+        <v>13493.32674870464</v>
       </c>
       <c r="E8">
         <v>-2727.16</v>
@@ -1949,37 +1949,37 @@
         <v>3390</v>
       </c>
       <c r="M8">
-        <v>71.08580843639969</v>
+        <v>69.6121124363997</v>
       </c>
       <c r="N8">
-        <v>3318.914191563601</v>
+        <v>3320.3878875636</v>
       </c>
       <c r="O8">
-        <v>663.7828383127202</v>
+        <v>664.07757751272</v>
       </c>
       <c r="P8">
-        <v>2655.13135325088</v>
+        <v>2656.31031005088</v>
       </c>
       <c r="Q8">
-        <v>5437.33135325088</v>
+        <v>5438.51031005088</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1111669768409762</v>
+        <v>0.111149291062154</v>
       </c>
       <c r="T8">
         <v>1.010932749166473</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.68884359011019</v>
+        <v>48.69842160151703</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1076963104789166</v>
+        <v>0.1076013194999251</v>
       </c>
       <c r="C9">
-        <v>16332.67039837446</v>
+        <v>16339.3818595806</v>
       </c>
       <c r="D9">
-        <v>13491.15039837446</v>
+        <v>13497.8618595806</v>
       </c>
       <c r="E9">
         <v>-2551.72</v>
@@ -2031,37 +2031,37 @@
         <v>3390</v>
       </c>
       <c r="M9">
-        <v>82.93344317579965</v>
+        <v>81.21413117579966</v>
       </c>
       <c r="N9">
-        <v>3307.0665568242</v>
+        <v>3308.7858688242</v>
       </c>
       <c r="O9">
-        <v>661.4133113648401</v>
+        <v>661.7571737648401</v>
       </c>
       <c r="P9">
-        <v>2645.65324545936</v>
+        <v>2647.02869505936</v>
       </c>
       <c r="Q9">
-        <v>5427.853245459361</v>
+        <v>5429.228695059361</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1117361029290088</v>
+        <v>0.1117182631666523</v>
       </c>
       <c r="T9">
         <v>1.019734566668249</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.87615164866587</v>
+        <v>41.74150422987174</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1076541757945111</v>
+        <v>0.107548018468621</v>
       </c>
       <c r="C10">
-        <v>16160.81396122135</v>
+        <v>16168.48001998556</v>
       </c>
       <c r="D10">
-        <v>13494.73396122135</v>
+        <v>13502.40001998556</v>
       </c>
       <c r="E10">
         <v>-2376.28</v>
@@ -2113,37 +2113,37 @@
         <v>3390</v>
       </c>
       <c r="M10">
-        <v>94.7810779151996</v>
+        <v>92.8161499151996</v>
       </c>
       <c r="N10">
-        <v>3295.2189220848</v>
+        <v>3297.1838500848</v>
       </c>
       <c r="O10">
-        <v>659.0437844169601</v>
+        <v>659.4367700169601</v>
       </c>
       <c r="P10">
-        <v>2636.17513766784</v>
+        <v>2637.74708006784</v>
       </c>
       <c r="Q10">
-        <v>5418.37513766784</v>
+        <v>5419.94708006784</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1123176013233028</v>
+        <v>0.1122996042299441</v>
       </c>
       <c r="T10">
         <v>1.028727728028759</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.76663269258263</v>
+        <v>36.52381620113778</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1076120411101057</v>
+        <v>0.107494717437317</v>
       </c>
       <c r="C11">
-        <v>15988.95942832907</v>
+        <v>15997.58123299643</v>
       </c>
       <c r="D11">
-        <v>13498.31942832907</v>
+        <v>13506.94123299643</v>
       </c>
       <c r="E11">
         <v>-2200.84</v>
@@ -2195,37 +2195,37 @@
         <v>3390</v>
       </c>
       <c r="M11">
-        <v>106.6287126545996</v>
+        <v>104.4181686545996</v>
       </c>
       <c r="N11">
-        <v>3283.371287345401</v>
+        <v>3285.581831345401</v>
       </c>
       <c r="O11">
-        <v>656.6742574690802</v>
+        <v>657.1163662690801</v>
       </c>
       <c r="P11">
-        <v>2626.69702987632</v>
+        <v>2628.46546507632</v>
       </c>
       <c r="Q11">
-        <v>5408.89702987632</v>
+        <v>5410.66546507632</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.112911879902087</v>
+        <v>0.1128937220199016</v>
       </c>
       <c r="T11">
         <v>1.037918541287302</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.79256239340679</v>
+        <v>32.46561440101136</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1075699064257002</v>
+        <v>0.107441416406013</v>
       </c>
       <c r="C12">
-        <v>15817.1068012159</v>
+        <v>15826.68550169427</v>
       </c>
       <c r="D12">
-        <v>13501.9068012159</v>
+        <v>13511.48550169427</v>
       </c>
       <c r="E12">
         <v>-2025.4</v>
@@ -2277,37 +2277,37 @@
         <v>3390</v>
       </c>
       <c r="M12">
-        <v>118.4763473939995</v>
+        <v>116.0201873939995</v>
       </c>
       <c r="N12">
-        <v>3271.523652606001</v>
+        <v>3273.979812606</v>
       </c>
       <c r="O12">
-        <v>654.3047305212002</v>
+        <v>654.7959625212002</v>
       </c>
       <c r="P12">
-        <v>2617.2189220848</v>
+        <v>2619.1838500848</v>
       </c>
       <c r="Q12">
-        <v>5399.4189220848</v>
+        <v>5401.3838500848</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1135193646715107</v>
+        <v>0.1135010424274137</v>
       </c>
       <c r="T12">
         <v>1.04731359484048</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.61330615406611</v>
+        <v>29.21905296091022</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1075277717412948</v>
+        <v>0.1073881153747089</v>
       </c>
       <c r="C13">
-        <v>15645.25608140168</v>
+        <v>15655.79282916428</v>
       </c>
       <c r="D13">
-        <v>13505.49608140168</v>
+        <v>13516.03282916428</v>
       </c>
       <c r="E13">
         <v>-1849.96</v>
@@ -2359,37 +2359,37 @@
         <v>3390</v>
       </c>
       <c r="M13">
-        <v>130.3239821333995</v>
+        <v>127.6222061333994</v>
       </c>
       <c r="N13">
-        <v>3259.6760178666</v>
+        <v>3262.377793866601</v>
       </c>
       <c r="O13">
-        <v>651.9352035733201</v>
+        <v>652.4755587733202</v>
       </c>
       <c r="P13">
-        <v>2607.74081429328</v>
+        <v>2609.902235093281</v>
       </c>
       <c r="Q13">
-        <v>5389.940814293281</v>
+        <v>5392.10223509328</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1141405007840675</v>
+        <v>0.1141220104845329</v>
       </c>
       <c r="T13">
         <v>1.056919773192605</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.01209650369646</v>
+        <v>26.5627754190093</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1074856370568893</v>
+        <v>0.1073348143434049</v>
       </c>
       <c r="C14">
-        <v>15473.40727040792</v>
+        <v>15484.9032184958</v>
       </c>
       <c r="D14">
-        <v>13509.08727040792</v>
+        <v>13520.5832184958</v>
       </c>
       <c r="E14">
         <v>-1674.52</v>
@@ -2441,37 +2441,37 @@
         <v>3390</v>
       </c>
       <c r="M14">
-        <v>142.1716168727994</v>
+        <v>139.2242248727994</v>
       </c>
       <c r="N14">
-        <v>3247.828383127201</v>
+        <v>3250.775775127201</v>
       </c>
       <c r="O14">
-        <v>649.5656766254401</v>
+        <v>650.1551550254402</v>
       </c>
       <c r="P14">
-        <v>2598.26270650176</v>
+        <v>2600.62062010176</v>
       </c>
       <c r="Q14">
-        <v>5380.46270650176</v>
+        <v>5382.82062010176</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1147757536264552</v>
+        <v>0.114757091452041</v>
       </c>
       <c r="T14">
         <v>1.066744273780007</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.84442179505509</v>
+        <v>24.34921080075852</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1074435023724839</v>
+        <v>0.1072815133121008</v>
       </c>
       <c r="C15">
-        <v>15301.5603697577</v>
+        <v>15314.01667278236</v>
       </c>
       <c r="D15">
-        <v>13512.6803697577</v>
+        <v>13525.13667278236</v>
       </c>
       <c r="E15">
         <v>-1499.08</v>
@@ -2523,37 +2523,37 @@
         <v>3390</v>
       </c>
       <c r="M15">
-        <v>154.0192516121994</v>
+        <v>150.8262436121994</v>
       </c>
       <c r="N15">
-        <v>3235.980748387801</v>
+        <v>3239.1737563878</v>
       </c>
       <c r="O15">
-        <v>647.1961496775602</v>
+        <v>647.8347512775601</v>
       </c>
       <c r="P15">
-        <v>2588.784598710241</v>
+        <v>2591.339005110241</v>
       </c>
       <c r="Q15">
-        <v>5370.98459871024</v>
+        <v>5373.53900511024</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.115425609982461</v>
+        <v>0.1154067719820207</v>
       </c>
       <c r="T15">
         <v>1.076794624955624</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.01023550312777</v>
+        <v>22.47619458531555</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1074013676880784</v>
+        <v>0.1072282122807968</v>
       </c>
       <c r="C16">
-        <v>15129.71538097576</v>
+        <v>15143.13319512164</v>
       </c>
       <c r="D16">
-        <v>13516.27538097576</v>
+        <v>13529.69319512164</v>
       </c>
       <c r="E16">
         <v>-1323.64</v>
@@ -2605,37 +2605,37 @@
         <v>3390</v>
       </c>
       <c r="M16">
-        <v>165.8668863515993</v>
+        <v>162.4282623515993</v>
       </c>
       <c r="N16">
-        <v>3224.1331136484</v>
+        <v>3227.571737648401</v>
       </c>
       <c r="O16">
-        <v>644.8266227296801</v>
+        <v>645.5143475296802</v>
       </c>
       <c r="P16">
-        <v>2579.306490918721</v>
+        <v>2582.057390118721</v>
       </c>
       <c r="Q16">
-        <v>5361.50649091872</v>
+        <v>5364.257390118721</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1160905792769786</v>
+        <v>0.1160715613615348</v>
       </c>
       <c r="T16">
         <v>1.087078705228348</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.43807582433293</v>
+        <v>20.87075211493587</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.107359233003673</v>
+        <v>0.1071749112494927</v>
       </c>
       <c r="C17">
-        <v>14957.87230558845</v>
+        <v>14972.2527886155</v>
       </c>
       <c r="D17">
-        <v>13519.87230558845</v>
+        <v>13534.2527886155</v>
       </c>
       <c r="E17">
         <v>-1148.2</v>
@@ -2687,37 +2687,37 @@
         <v>3390</v>
       </c>
       <c r="M17">
-        <v>177.7145210909992</v>
+        <v>174.0302810909992</v>
       </c>
       <c r="N17">
-        <v>3212.285478909001</v>
+        <v>3215.969718909001</v>
       </c>
       <c r="O17">
-        <v>642.4570957818001</v>
+        <v>643.1939437818002</v>
       </c>
       <c r="P17">
-        <v>2569.828383127201</v>
+        <v>2572.775775127201</v>
       </c>
       <c r="Q17">
-        <v>5352.028383127201</v>
+        <v>5354.975775127201</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1167711949078377</v>
+        <v>0.1167519928440963</v>
       </c>
       <c r="T17">
         <v>1.097604763860431</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.07553743604407</v>
+        <v>19.47936864060681</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1073170983192675</v>
+        <v>0.1071216102181887</v>
       </c>
       <c r="C18">
-        <v>14786.03114512374</v>
+        <v>14801.37545636998</v>
       </c>
       <c r="D18">
-        <v>13523.47114512374</v>
+        <v>13538.81545636998</v>
       </c>
       <c r="E18">
         <v>-972.7600000000002</v>
@@ -2769,37 +2769,37 @@
         <v>3390</v>
       </c>
       <c r="M18">
-        <v>189.5621558303992</v>
+        <v>185.6322998303992</v>
       </c>
       <c r="N18">
-        <v>3200.437844169601</v>
+        <v>3204.367700169601</v>
       </c>
       <c r="O18">
-        <v>640.0875688339202</v>
+        <v>640.8735400339202</v>
       </c>
       <c r="P18">
-        <v>2560.350275335681</v>
+        <v>2563.494160135681</v>
       </c>
       <c r="Q18">
-        <v>5342.55027533568</v>
+        <v>5345.694160135681</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1174680156727649</v>
+        <v>0.1174486250762425</v>
       </c>
       <c r="T18">
         <v>1.108381442936135</v>
       </c>
       <c r="U18">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.88331634629132</v>
+        <v>18.26190810056889</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1072749636348621</v>
+        <v>0.1070683091868846</v>
       </c>
       <c r="C19">
-        <v>14614.19190111122</v>
+        <v>14630.50120149532</v>
       </c>
       <c r="D19">
-        <v>13527.07190111122</v>
+        <v>13543.38120149532</v>
       </c>
       <c r="E19">
         <v>-797.3200000000002</v>
@@ -2851,37 +2851,37 @@
         <v>3390</v>
       </c>
       <c r="M19">
-        <v>201.4097905697992</v>
+        <v>197.2343185697991</v>
       </c>
       <c r="N19">
-        <v>3188.590209430201</v>
+        <v>3192.765681430201</v>
       </c>
       <c r="O19">
-        <v>637.7180418860403</v>
+        <v>638.5531362860402</v>
       </c>
       <c r="P19">
-        <v>2550.872167544161</v>
+        <v>2554.212545144161</v>
       </c>
       <c r="Q19">
-        <v>5333.07216754416</v>
+        <v>5336.412545144161</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1181816272994976</v>
+        <v>0.1181620436272356</v>
       </c>
       <c r="T19">
         <v>1.119417801025711</v>
       </c>
       <c r="U19">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.83135656121536</v>
+        <v>17.18767821230013</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1072328289504566</v>
+        <v>0.1070150081555806</v>
       </c>
       <c r="C20">
-        <v>14442.35457508213</v>
+        <v>14459.63002710595</v>
       </c>
       <c r="D20">
-        <v>13530.67457508214</v>
+        <v>13547.95002710595</v>
       </c>
       <c r="E20">
         <v>-621.8800000000001</v>
@@ -2933,37 +2933,37 @@
         <v>3390</v>
       </c>
       <c r="M20">
-        <v>213.2574253091991</v>
+        <v>208.8363373091991</v>
       </c>
       <c r="N20">
-        <v>3176.742574690801</v>
+        <v>3181.163662690801</v>
       </c>
       <c r="O20">
-        <v>635.3485149381603</v>
+        <v>636.2327325381602</v>
       </c>
       <c r="P20">
-        <v>2541.394059752641</v>
+        <v>2544.93093015264</v>
       </c>
       <c r="Q20">
-        <v>5323.594059752641</v>
+        <v>5327.13093015264</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.118912644087858</v>
+        <v>0.1188928626306921</v>
       </c>
       <c r="T20">
         <v>1.130723338580887</v>
       </c>
       <c r="U20">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.89628119670339</v>
+        <v>16.23280720050568</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1071906942660512</v>
+        <v>0.1069617071242766</v>
       </c>
       <c r="C21">
-        <v>14270.51916856934</v>
+        <v>14288.76193632049</v>
       </c>
       <c r="D21">
-        <v>13534.27916856934</v>
+        <v>13552.52193632049</v>
       </c>
       <c r="E21">
         <v>-446.4400000000001</v>
@@ -3015,37 +3015,37 @@
         <v>3390</v>
       </c>
       <c r="M21">
-        <v>225.1050600485991</v>
+        <v>220.438356048599</v>
       </c>
       <c r="N21">
-        <v>3164.894939951401</v>
+        <v>3169.561643951401</v>
       </c>
       <c r="O21">
-        <v>632.9789879902802</v>
+        <v>633.9123287902803</v>
       </c>
       <c r="P21">
-        <v>2531.915951961121</v>
+        <v>2535.649315161121</v>
       </c>
       <c r="Q21">
-        <v>5314.115951961121</v>
+        <v>5317.84931516112</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1196617106734618</v>
+        <v>0.1196417265478141</v>
       </c>
       <c r="T21">
         <v>1.142308025211499</v>
       </c>
       <c r="U21">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.05963481792953</v>
+        <v>15.37844892679485</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1071485595816457</v>
+        <v>0.1069084060929725</v>
       </c>
       <c r="C22">
-        <v>14098.68568310733</v>
+        <v>14117.89693226181</v>
       </c>
       <c r="D22">
-        <v>13537.88568310733</v>
+        <v>13557.09693226181</v>
       </c>
       <c r="E22">
         <v>-271</v>
@@ -3097,37 +3097,37 @@
         <v>3390</v>
       </c>
       <c r="M22">
-        <v>236.952694787999</v>
+        <v>232.040374787999</v>
       </c>
       <c r="N22">
-        <v>3153.047305212001</v>
+        <v>3157.959625212001</v>
       </c>
       <c r="O22">
-        <v>630.6094610424002</v>
+        <v>631.5919250424002</v>
       </c>
       <c r="P22">
-        <v>2522.437844169601</v>
+        <v>2526.367700169601</v>
       </c>
       <c r="Q22">
-        <v>5304.637844169601</v>
+        <v>5308.5677001696</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1204295039237056</v>
+        <v>0.1204093120628641</v>
       </c>
       <c r="T22">
         <v>1.154182329007876</v>
       </c>
       <c r="U22">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.30665307703305</v>
+        <v>14.60952648045511</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1071064248972403</v>
+        <v>0.1068551050616685</v>
       </c>
       <c r="C23">
-        <v>13926.85412023223</v>
+        <v>13947.03501805695</v>
       </c>
       <c r="D23">
-        <v>13541.49412023223</v>
+        <v>13561.67501805695</v>
       </c>
       <c r="E23">
         <v>-95.5600000000004</v>
@@ -3179,37 +3179,37 @@
         <v>3390</v>
       </c>
       <c r="M23">
-        <v>248.8003295273989</v>
+        <v>243.642393527399</v>
       </c>
       <c r="N23">
-        <v>3141.199670472601</v>
+        <v>3146.357606472601</v>
       </c>
       <c r="O23">
-        <v>628.2399340945203</v>
+        <v>629.2715212945203</v>
       </c>
       <c r="P23">
-        <v>2512.959736378081</v>
+        <v>2517.086085178081</v>
       </c>
       <c r="Q23">
-        <v>5295.15973637808</v>
+        <v>5299.286085178081</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1212167349777532</v>
+        <v>0.1211963301225989</v>
       </c>
       <c r="T23">
         <v>1.166357248090238</v>
       </c>
       <c r="U23">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.62538388288862</v>
+        <v>13.91383474329058</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1070642902128348</v>
+        <v>0.1068018040303644</v>
       </c>
       <c r="C24">
-        <v>13755.02448148183</v>
+        <v>13776.1761968372</v>
       </c>
       <c r="D24">
-        <v>13545.10448148183</v>
+        <v>13566.25619683721</v>
       </c>
       <c r="E24">
         <v>79.87999999999965</v>
@@ -3261,37 +3261,37 @@
         <v>3390</v>
       </c>
       <c r="M24">
-        <v>260.6479642667989</v>
+        <v>255.2444122667989</v>
       </c>
       <c r="N24">
-        <v>3129.352035733201</v>
+        <v>3134.755587733201</v>
       </c>
       <c r="O24">
-        <v>625.8704071466402</v>
+        <v>626.9511175466403</v>
       </c>
       <c r="P24">
-        <v>2503.481628586561</v>
+        <v>2507.804470186561</v>
       </c>
       <c r="Q24">
-        <v>5285.681628586561</v>
+        <v>5290.004470186561</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1220241514434429</v>
+        <v>0.1220035281325834</v>
       </c>
       <c r="T24">
         <v>1.178844344584967</v>
       </c>
       <c r="U24">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.00604825184823</v>
+        <v>13.28138770950465</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1070221555284294</v>
+        <v>0.1067485029990604</v>
       </c>
       <c r="C25">
-        <v>13583.19676839552</v>
+        <v>13605.3204717381</v>
       </c>
       <c r="D25">
-        <v>13548.71676839552</v>
+        <v>13570.8404717381</v>
       </c>
       <c r="E25">
         <v>255.3200000000002</v>
@@ -3343,37 +3343,37 @@
         <v>3390</v>
       </c>
       <c r="M25">
-        <v>272.4955990061989</v>
+        <v>266.8464310061989</v>
       </c>
       <c r="N25">
-        <v>3117.504400993801</v>
+        <v>3123.153568993801</v>
       </c>
       <c r="O25">
-        <v>623.5008801987602</v>
+        <v>624.6307137987602</v>
       </c>
       <c r="P25">
-        <v>2494.003520795041</v>
+        <v>2498.522855195041</v>
       </c>
       <c r="Q25">
-        <v>5276.203520795041</v>
+        <v>5280.722855195041</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1228525397653844</v>
+        <v>0.1228316923246454</v>
       </c>
       <c r="T25">
         <v>1.191655781248391</v>
       </c>
       <c r="U25">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.44056789307222</v>
+        <v>12.70393606996096</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1069800208440239</v>
+        <v>0.1066952019677563</v>
       </c>
       <c r="C26">
-        <v>13411.37098251436</v>
+        <v>13434.4678458994</v>
       </c>
       <c r="D26">
-        <v>13552.33098251436</v>
+        <v>13575.4278458994</v>
       </c>
       <c r="E26">
         <v>430.7599999999993</v>
@@ -3425,37 +3425,37 @@
         <v>3390</v>
       </c>
       <c r="M26">
-        <v>284.3432337455988</v>
+        <v>278.4484497455988</v>
       </c>
       <c r="N26">
-        <v>3105.656766254401</v>
+        <v>3111.551550254401</v>
       </c>
       <c r="O26">
-        <v>621.1313532508802</v>
+        <v>622.3103100508803</v>
       </c>
       <c r="P26">
-        <v>2484.525413003521</v>
+        <v>2489.241240203521</v>
       </c>
       <c r="Q26">
-        <v>5266.725413003521</v>
+        <v>5271.441240203521</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1237027277800085</v>
+        <v>0.1236816503112353</v>
       </c>
       <c r="T26">
         <v>1.204804360981905</v>
       </c>
       <c r="U26">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.92221089752755</v>
+        <v>12.17460540037926</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1069378861596185</v>
+        <v>0.1066419009364523</v>
       </c>
       <c r="C27">
-        <v>13239.54712538105</v>
+        <v>13263.6183224651</v>
       </c>
       <c r="D27">
-        <v>13555.94712538105</v>
+        <v>13580.0183224651</v>
       </c>
       <c r="E27">
         <v>606.1999999999998</v>
@@ -3507,37 +3507,37 @@
         <v>3390</v>
       </c>
       <c r="M27">
-        <v>296.1908684849988</v>
+        <v>290.0504684849988</v>
       </c>
       <c r="N27">
-        <v>3093.809131515001</v>
+        <v>3099.949531515001</v>
       </c>
       <c r="O27">
-        <v>618.7618263030004</v>
+        <v>619.9899063030002</v>
       </c>
       <c r="P27">
-        <v>2475.047305212001</v>
+        <v>2479.959625212001</v>
       </c>
       <c r="Q27">
-        <v>5257.247305212</v>
+        <v>5262.159625212001</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1245755874750226</v>
+        <v>0.1245542738441343</v>
       </c>
       <c r="T27">
         <v>1.218303569508314</v>
       </c>
       <c r="U27">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.44532246162644</v>
+        <v>11.68762118436409</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.106895751475213</v>
+        <v>0.1065885999051482</v>
       </c>
       <c r="C28">
-        <v>13067.72519853993</v>
+        <v>13092.77190458347</v>
       </c>
       <c r="D28">
-        <v>13559.56519853993</v>
+        <v>13584.61190458347</v>
       </c>
       <c r="E28">
         <v>781.6400000000003</v>
@@ -3589,37 +3589,37 @@
         <v>3390</v>
       </c>
       <c r="M28">
-        <v>308.0385032243987</v>
+        <v>301.6524872243987</v>
       </c>
       <c r="N28">
-        <v>3081.961496775602</v>
+        <v>3088.347512775601</v>
       </c>
       <c r="O28">
-        <v>616.3922993551204</v>
+        <v>617.6695025551203</v>
       </c>
       <c r="P28">
-        <v>2465.569197420481</v>
+        <v>2470.678010220481</v>
       </c>
       <c r="Q28">
-        <v>5247.769197420481</v>
+        <v>5252.878010220481</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1254720379726047</v>
+        <v>0.1254504817968414</v>
       </c>
       <c r="T28">
         <v>1.232167621508408</v>
       </c>
       <c r="U28">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.00511775156389</v>
+        <v>11.23809729265778</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1068536167908076</v>
+        <v>0.1065352988738442</v>
       </c>
       <c r="C29">
-        <v>12895.90520353699</v>
+        <v>12921.92859540703</v>
       </c>
       <c r="D29">
-        <v>13563.18520353699</v>
+        <v>13589.20859540703</v>
       </c>
       <c r="E29">
         <v>957.0799999999999</v>
@@ -3671,37 +3671,37 @@
         <v>3390</v>
       </c>
       <c r="M29">
-        <v>319.8861379637987</v>
+        <v>313.2545059637986</v>
       </c>
       <c r="N29">
-        <v>3070.113862036201</v>
+        <v>3076.745494036201</v>
       </c>
       <c r="O29">
-        <v>614.0227724072403</v>
+        <v>615.3490988072404</v>
       </c>
       <c r="P29">
-        <v>2456.091089628961</v>
+        <v>2461.396395228961</v>
       </c>
       <c r="Q29">
-        <v>5238.291089628961</v>
+        <v>5243.59639522896</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1263930487577917</v>
+        <v>0.1263712433920884</v>
       </c>
       <c r="T29">
         <v>1.246411510549601</v>
       </c>
       <c r="U29">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.59752079780226</v>
+        <v>10.82187146700379</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1068114821064021</v>
+        <v>0.1064819978425401</v>
       </c>
       <c r="C30">
-        <v>12724.08714191988</v>
+        <v>12751.08839809258</v>
       </c>
       <c r="D30">
-        <v>13566.80714191989</v>
+        <v>13593.80839809257</v>
       </c>
       <c r="E30">
         <v>1132.52</v>
@@ -3753,37 +3753,37 @@
         <v>3390</v>
       </c>
       <c r="M30">
-        <v>331.7337727031986</v>
+        <v>324.8565247031987</v>
       </c>
       <c r="N30">
-        <v>3058.266227296801</v>
+        <v>3065.143475296801</v>
       </c>
       <c r="O30">
-        <v>611.6532454593603</v>
+        <v>613.0286950593603</v>
       </c>
       <c r="P30">
-        <v>2446.612981837441</v>
+        <v>2452.114780237441</v>
       </c>
       <c r="Q30">
-        <v>5228.812981837441</v>
+        <v>5234.314780237441</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1273396431759006</v>
+        <v>0.1273175816983145</v>
       </c>
       <c r="T30">
         <v>1.261051063175272</v>
       </c>
       <c r="U30">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.21903791216647</v>
+        <v>10.43537605746793</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1067693474219967</v>
+        <v>0.1064286968112361</v>
       </c>
       <c r="C31">
-        <v>12552.27101523791</v>
+        <v>12580.25131580117</v>
       </c>
       <c r="D31">
-        <v>13570.43101523791</v>
+        <v>13598.41131580117</v>
       </c>
       <c r="E31">
         <v>1307.959999999999</v>
@@ -3835,37 +3835,37 @@
         <v>3390</v>
       </c>
       <c r="M31">
-        <v>343.5814074425985</v>
+        <v>336.4585434425985</v>
       </c>
       <c r="N31">
-        <v>3046.418592557402</v>
+        <v>3053.541456557401</v>
       </c>
       <c r="O31">
-        <v>609.2837185114803</v>
+        <v>610.7082913114804</v>
       </c>
       <c r="P31">
-        <v>2437.134874045921</v>
+        <v>2442.833165245921</v>
       </c>
       <c r="Q31">
-        <v>5219.334874045921</v>
+        <v>5225.033165245921</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1283129022255055</v>
+        <v>0.1282905774216173</v>
       </c>
       <c r="T31">
         <v>1.276102997565046</v>
       </c>
       <c r="U31">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.866657294505556</v>
+        <v>10.07553550376215</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1067272127375912</v>
+        <v>0.106375395779932</v>
       </c>
       <c r="C32">
-        <v>12380.45682504202</v>
+        <v>12409.41735169815</v>
       </c>
       <c r="D32">
-        <v>13574.05682504202</v>
+        <v>13603.01735169815</v>
       </c>
       <c r="E32">
         <v>1483.4</v>
@@ -3917,37 +3917,37 @@
         <v>3390</v>
       </c>
       <c r="M32">
-        <v>355.4290421819985</v>
+        <v>348.0605621819985</v>
       </c>
       <c r="N32">
-        <v>3034.570957818002</v>
+        <v>3041.939437818001</v>
       </c>
       <c r="O32">
-        <v>606.9141915636004</v>
+        <v>608.3878875636003</v>
       </c>
       <c r="P32">
-        <v>2427.656766254401</v>
+        <v>2433.551550254401</v>
       </c>
       <c r="Q32">
-        <v>5209.856766254401</v>
+        <v>5215.751550254401</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1293139686765278</v>
+        <v>0.1292913730227289</v>
       </c>
       <c r="T32">
         <v>1.2915849872231</v>
       </c>
       <c r="U32">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.537768718022038</v>
+        <v>9.739684320303407</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1066850780531858</v>
+        <v>0.106322094748628</v>
       </c>
       <c r="C33">
-        <v>12208.64457288482</v>
+        <v>12238.58650895318</v>
       </c>
       <c r="D33">
-        <v>13577.68457288482</v>
+        <v>13607.62650895318</v>
       </c>
       <c r="E33">
         <v>1658.84</v>
@@ -3999,37 +3999,37 @@
         <v>3390</v>
       </c>
       <c r="M33">
-        <v>367.2766769213985</v>
+        <v>359.6625809213985</v>
       </c>
       <c r="N33">
-        <v>3022.723323078601</v>
+        <v>3030.337419078602</v>
       </c>
       <c r="O33">
-        <v>604.5446646157203</v>
+        <v>606.0674838157204</v>
       </c>
       <c r="P33">
-        <v>2418.178658462881</v>
+        <v>2424.269935262882</v>
       </c>
       <c r="Q33">
-        <v>5200.378658462882</v>
+        <v>5206.469935262881</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1303440515464202</v>
+        <v>0.1303211771919886</v>
       </c>
       <c r="T33">
         <v>1.307515730204575</v>
       </c>
       <c r="U33">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.230098759376164</v>
+        <v>9.425500955132328</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1066429433687803</v>
+        <v>0.1062687937173239</v>
       </c>
       <c r="C34">
-        <v>12036.8342603206</v>
+        <v>12067.75879074018</v>
       </c>
       <c r="D34">
-        <v>13581.3142603206</v>
+        <v>13612.23879074018</v>
       </c>
       <c r="E34">
         <v>1834.28</v>
@@ -4081,37 +4081,37 @@
         <v>3390</v>
       </c>
       <c r="M34">
-        <v>379.1243116607984</v>
+        <v>371.2645996607984</v>
       </c>
       <c r="N34">
-        <v>3010.875688339202</v>
+        <v>3018.735400339202</v>
       </c>
       <c r="O34">
-        <v>602.1751376678403</v>
+        <v>603.7470800678403</v>
       </c>
       <c r="P34">
-        <v>2408.700550671361</v>
+        <v>2414.988320271361</v>
       </c>
       <c r="Q34">
-        <v>5190.900550671361</v>
+        <v>5197.188320271362</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1314044309713094</v>
+        <v>0.1313812697191676</v>
       </c>
       <c r="T34">
         <v>1.323915024450211</v>
       </c>
       <c r="U34">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.941658173145658</v>
+        <v>9.130954050284444</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1066008086843749</v>
+        <v>0.1062154926860199</v>
       </c>
       <c r="C35">
-        <v>11865.02588890527</v>
+        <v>11896.9342002374</v>
       </c>
       <c r="D35">
-        <v>13584.94588890527</v>
+        <v>13616.8542002374</v>
       </c>
       <c r="E35">
         <v>2009.72</v>
@@ -4163,37 +4163,37 @@
         <v>3390</v>
       </c>
       <c r="M35">
-        <v>390.9719464001984</v>
+        <v>382.8666184001984</v>
       </c>
       <c r="N35">
-        <v>2999.028053599802</v>
+        <v>3007.133381599801</v>
       </c>
       <c r="O35">
-        <v>599.8056107199603</v>
+        <v>601.4266763199603</v>
       </c>
       <c r="P35">
-        <v>2399.222442879841</v>
+        <v>2405.706705279841</v>
       </c>
       <c r="Q35">
-        <v>5181.422442879841</v>
+        <v>5187.906705279841</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1324964635133595</v>
+        <v>0.1324730067993969</v>
       </c>
       <c r="T35">
         <v>1.340803849867358</v>
       </c>
       <c r="U35">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.670698834565489</v>
+        <v>8.854258473003096</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1068578739999694</v>
+        <v>0.1065701916547158</v>
       </c>
       <c r="C36">
-        <v>11667.45935727115</v>
+        <v>11690.83908393441</v>
       </c>
       <c r="D36">
-        <v>13562.81935727115</v>
+        <v>13586.19908393441</v>
       </c>
       <c r="E36">
         <v>2185.16</v>
@@ -4245,37 +4245,37 @@
         <v>3390</v>
       </c>
       <c r="M36">
-        <v>409.3810371395983</v>
+        <v>403.4160771395983</v>
       </c>
       <c r="N36">
-        <v>2980.618962860402</v>
+        <v>2986.583922860402</v>
       </c>
       <c r="O36">
-        <v>596.1237925720803</v>
+        <v>597.3167845720803</v>
       </c>
       <c r="P36">
-        <v>2384.495170288321</v>
+        <v>2389.267138288321</v>
       </c>
       <c r="Q36">
-        <v>5166.695170288322</v>
+        <v>5171.467138288321</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1336215879506233</v>
+        <v>0.1335978268214512</v>
       </c>
       <c r="T36">
         <v>1.358204457872905</v>
       </c>
       <c r="U36">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.280793911917359</v>
+        <v>8.403234754639991</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.106824539315564</v>
+        <v>0.1065288906234118</v>
       </c>
       <c r="C37">
-        <v>11494.88452471291</v>
+        <v>11518.96145360641</v>
       </c>
       <c r="D37">
-        <v>13565.68452471291</v>
+        <v>13589.76145360641</v>
       </c>
       <c r="E37">
         <v>2360.6</v>
@@ -4327,37 +4327,37 @@
         <v>3390</v>
       </c>
       <c r="M37">
-        <v>421.4216558789983</v>
+        <v>415.2812558789983</v>
       </c>
       <c r="N37">
-        <v>2968.578344121001</v>
+        <v>2974.718744121002</v>
       </c>
       <c r="O37">
-        <v>593.7156688242003</v>
+        <v>594.9437488242004</v>
       </c>
       <c r="P37">
-        <v>2374.862675296801</v>
+        <v>2379.774995296802</v>
       </c>
       <c r="Q37">
-        <v>5157.062675296801</v>
+        <v>5161.974995296801</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1347813316013413</v>
+        <v>0.134757256690338</v>
       </c>
       <c r="T37">
         <v>1.376140469201698</v>
       </c>
       <c r="U37">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.044199800148292</v>
+        <v>8.163142333078847</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1067912046311585</v>
+        <v>0.1064875895921077</v>
       </c>
       <c r="C38">
-        <v>11322.31090295294</v>
+        <v>11347.08569191084</v>
       </c>
       <c r="D38">
-        <v>13568.55090295294</v>
+        <v>13593.32569191084</v>
       </c>
       <c r="E38">
         <v>2536.04</v>
@@ -4409,37 +4409,37 @@
         <v>3390</v>
       </c>
       <c r="M38">
-        <v>433.4622746183982</v>
+        <v>427.1464346183982</v>
       </c>
       <c r="N38">
-        <v>2956.537725381602</v>
+        <v>2962.853565381602</v>
       </c>
       <c r="O38">
-        <v>591.3075450763204</v>
+        <v>592.5707130763203</v>
       </c>
       <c r="P38">
-        <v>2365.230180305281</v>
+        <v>2370.282852305281</v>
       </c>
       <c r="Q38">
-        <v>5147.430180305281</v>
+        <v>5152.482852305281</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1359773172411443</v>
+        <v>0.1359529187426274</v>
       </c>
       <c r="T38">
         <v>1.394636980884517</v>
       </c>
       <c r="U38">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.820749805699728</v>
+        <v>7.936388379382213</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1067578699467531</v>
+        <v>0.1064462885608037</v>
       </c>
       <c r="C39">
-        <v>11149.7384927589</v>
+        <v>11175.21180031836</v>
       </c>
       <c r="D39">
-        <v>13571.4184927589</v>
+        <v>13596.89180031836</v>
       </c>
       <c r="E39">
         <v>2711.48</v>
@@ -4491,37 +4491,37 @@
         <v>3390</v>
       </c>
       <c r="M39">
-        <v>445.5028933577981</v>
+        <v>439.0116133577981</v>
       </c>
       <c r="N39">
-        <v>2944.497106642202</v>
+        <v>2950.988386642202</v>
       </c>
       <c r="O39">
-        <v>588.8994213284403</v>
+        <v>590.1976773284404</v>
       </c>
       <c r="P39">
-        <v>2355.597685313761</v>
+        <v>2360.790709313761</v>
       </c>
       <c r="Q39">
-        <v>5137.797685313761</v>
+        <v>5142.990709313761</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1372112706790363</v>
+        <v>0.1371865383203865</v>
       </c>
       <c r="T39">
         <v>1.413720683414409</v>
       </c>
       <c r="U39">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.609378189329465</v>
+        <v>7.721891396155668</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1067245352623476</v>
+        <v>0.1064049875294997</v>
       </c>
       <c r="C40">
-        <v>10977.16729489912</v>
+        <v>11003.33978030117</v>
       </c>
       <c r="D40">
-        <v>13574.28729489912</v>
+        <v>13600.45978030117</v>
       </c>
       <c r="E40">
         <v>2886.92</v>
@@ -4573,37 +4573,37 @@
         <v>3390</v>
       </c>
       <c r="M40">
-        <v>457.5435120971981</v>
+        <v>450.8767920971981</v>
       </c>
       <c r="N40">
-        <v>2932.456487902802</v>
+        <v>2939.123207902802</v>
       </c>
       <c r="O40">
-        <v>586.4912975805604</v>
+        <v>587.8246415805604</v>
       </c>
       <c r="P40">
-        <v>2345.965190322242</v>
+        <v>2351.298566322242</v>
       </c>
       <c r="Q40">
-        <v>5128.165190322241</v>
+        <v>5133.498566322241</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1384850290665376</v>
+        <v>0.1384599520780732</v>
       </c>
       <c r="T40">
         <v>1.433419989251717</v>
       </c>
       <c r="U40">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.409131394873427</v>
+        <v>7.518683727835781</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1066912005779422</v>
+        <v>0.1063636864981956</v>
       </c>
       <c r="C41">
-        <v>10804.59731014257</v>
+        <v>10831.46963333304</v>
       </c>
       <c r="D41">
-        <v>13577.15731014257</v>
+        <v>13604.02963333304</v>
       </c>
       <c r="E41">
         <v>3062.36</v>
@@ -4655,37 +4655,37 @@
         <v>3390</v>
       </c>
       <c r="M41">
-        <v>469.584130836598</v>
+        <v>462.7419708365981</v>
       </c>
       <c r="N41">
-        <v>2920.415869163402</v>
+        <v>2927.258029163402</v>
       </c>
       <c r="O41">
-        <v>584.0831738326805</v>
+        <v>585.4516058326805</v>
       </c>
       <c r="P41">
-        <v>2336.332695330721</v>
+        <v>2341.806423330722</v>
       </c>
       <c r="Q41">
-        <v>5118.532695330721</v>
+        <v>5124.006423330722</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.139800550024121</v>
+        <v>0.1397751171065037</v>
       </c>
       <c r="T41">
         <v>1.453765173968937</v>
       </c>
       <c r="U41">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.219153666799749</v>
+        <v>7.325896965583582</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1066578658935368</v>
+        <v>0.1063223854668916</v>
       </c>
       <c r="C42">
-        <v>10632.02853925887</v>
+        <v>10659.60136088927</v>
       </c>
       <c r="D42">
-        <v>13580.02853925887</v>
+        <v>13607.60136088927</v>
       </c>
       <c r="E42">
         <v>3237.8</v>
@@ -4737,37 +4737,37 @@
         <v>3390</v>
       </c>
       <c r="M42">
-        <v>481.6247495759981</v>
+        <v>474.6071495759981</v>
       </c>
       <c r="N42">
-        <v>2908.375250424002</v>
+        <v>2915.392850424002</v>
       </c>
       <c r="O42">
-        <v>581.6750500848004</v>
+        <v>583.0785700848004</v>
       </c>
       <c r="P42">
-        <v>2326.700200339202</v>
+        <v>2332.314280339202</v>
       </c>
       <c r="Q42">
-        <v>5108.900200339202</v>
+        <v>5114.514280339201</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1411599216802905</v>
+        <v>0.1411341209692153</v>
       </c>
       <c r="T42">
         <v>1.474788531510064</v>
       </c>
       <c r="U42">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.038674825129754</v>
+        <v>7.142749541443992</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1066245312091313</v>
+        <v>0.1062810844355875</v>
       </c>
       <c r="C43">
-        <v>10459.4609830183</v>
+        <v>10487.7349644467</v>
       </c>
       <c r="D43">
-        <v>13582.9009830183</v>
+        <v>13611.1749644467</v>
       </c>
       <c r="E43">
         <v>3413.240000000001</v>
@@ -4819,37 +4819,37 @@
         <v>3390</v>
       </c>
       <c r="M43">
-        <v>493.665368315398</v>
+        <v>486.472328315398</v>
       </c>
       <c r="N43">
-        <v>2896.334631684602</v>
+        <v>2903.527671684602</v>
       </c>
       <c r="O43">
-        <v>579.2669263369204</v>
+        <v>580.7055343369204</v>
       </c>
       <c r="P43">
-        <v>2317.067705347682</v>
+        <v>2322.822137347682</v>
       </c>
       <c r="Q43">
-        <v>5099.267705347682</v>
+        <v>5105.022137347682</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1425653737315844</v>
+        <v>0.1425391927594763</v>
       </c>
       <c r="T43">
         <v>1.496524545239026</v>
       </c>
       <c r="U43">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.866999829394882</v>
+        <v>6.968536137994137</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1073303965247259</v>
+        <v>0.1062397834042835</v>
       </c>
       <c r="C44">
-        <v>10223.45510183499</v>
+        <v>10315.87044548375</v>
       </c>
       <c r="D44">
-        <v>13522.33510183499</v>
+        <v>13614.75044548375</v>
       </c>
       <c r="E44">
         <v>3588.679999999999</v>
@@ -4901,45 +4901,45 @@
         <v>3390</v>
       </c>
       <c r="M44">
-        <v>521.9166430547979</v>
+        <v>498.3375070547979</v>
       </c>
       <c r="N44">
-        <v>2868.083356945202</v>
+        <v>2891.662492945202</v>
       </c>
       <c r="O44">
-        <v>573.6166713890404</v>
+        <v>578.3324985890405</v>
       </c>
       <c r="P44">
-        <v>2294.466685556162</v>
+        <v>2313.329994356162</v>
       </c>
       <c r="Q44">
-        <v>5076.666685556162</v>
+        <v>5095.529994356162</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.144019289646716</v>
+        <v>0.1439927153011257</v>
       </c>
       <c r="T44">
         <v>1.519010076682779</v>
       </c>
       <c r="U44">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05666478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.495290091073167</v>
+        <v>6.802618610899041</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1073146618403204</v>
+        <v>0.1067832823729794</v>
       </c>
       <c r="C45">
-        <v>10049.35931010634</v>
+        <v>10093.52884240778</v>
       </c>
       <c r="D45">
-        <v>13523.67931010634</v>
+        <v>13567.84884240778</v>
       </c>
       <c r="E45">
         <v>3764.12</v>
@@ -4983,37 +4983,37 @@
         <v>3390</v>
       </c>
       <c r="M45">
-        <v>534.3432297941978</v>
+        <v>523.0273497941978</v>
       </c>
       <c r="N45">
-        <v>2855.656770205802</v>
+        <v>2866.972650205802</v>
       </c>
       <c r="O45">
-        <v>571.1313540411605</v>
+        <v>573.3945300411605</v>
       </c>
       <c r="P45">
-        <v>2284.525416164642</v>
+        <v>2293.578120164641</v>
       </c>
       <c r="Q45">
-        <v>5066.725416164642</v>
+        <v>5075.778120164641</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.145524220155361</v>
+        <v>0.1454972386337102</v>
       </c>
       <c r="T45">
         <v>1.542284574142103</v>
       </c>
       <c r="U45">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.344236833141234</v>
+        <v>6.481496620270252</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.107298927155915</v>
+        <v>0.1067555813416754</v>
       </c>
       <c r="C46">
-        <v>9875.26378565039</v>
+        <v>9920.471504592118</v>
       </c>
       <c r="D46">
-        <v>13525.02378565039</v>
+        <v>13570.23150459212</v>
       </c>
       <c r="E46">
         <v>3939.559999999999</v>
@@ -5065,37 +5065,37 @@
         <v>3390</v>
       </c>
       <c r="M46">
-        <v>546.7698165335978</v>
+        <v>535.1907765335977</v>
       </c>
       <c r="N46">
-        <v>2843.230183466402</v>
+        <v>2854.809223466402</v>
       </c>
       <c r="O46">
-        <v>568.6460366932805</v>
+        <v>570.9618446932805</v>
       </c>
       <c r="P46">
-        <v>2274.584146773122</v>
+        <v>2283.847378773122</v>
       </c>
       <c r="Q46">
-        <v>5056.784146773121</v>
+        <v>5066.047378773122</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1470828981821719</v>
+        <v>0.1470554949424584</v>
       </c>
       <c r="T46">
         <v>1.566390303653546</v>
       </c>
       <c r="U46">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.200049632388024</v>
+        <v>6.334189878900474</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1072831924715095</v>
+        <v>0.1067278803103713</v>
       </c>
       <c r="C47">
-        <v>9701.16852854687</v>
+        <v>9747.415003766357</v>
       </c>
       <c r="D47">
-        <v>13526.36852854687</v>
+        <v>13572.61500376636</v>
       </c>
       <c r="E47">
         <v>4115</v>
@@ -5147,37 +5147,37 @@
         <v>3390</v>
       </c>
       <c r="M47">
-        <v>559.1964032729977</v>
+        <v>547.3542032729978</v>
       </c>
       <c r="N47">
-        <v>2830.803596727003</v>
+        <v>2842.645796727002</v>
       </c>
       <c r="O47">
-        <v>566.1607193454005</v>
+        <v>568.5291593454004</v>
       </c>
       <c r="P47">
-        <v>2264.642877381602</v>
+        <v>2274.116637381602</v>
       </c>
       <c r="Q47">
-        <v>5046.842877381601</v>
+        <v>5056.316637381602</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1486982554099578</v>
+        <v>0.1486704151169793</v>
       </c>
       <c r="T47">
         <v>1.591372605147223</v>
       </c>
       <c r="U47">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.06227075166829</v>
+        <v>6.193430103813795</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1072674577871041</v>
+        <v>0.1067001792790673</v>
       </c>
       <c r="C48">
-        <v>9527.07353887552</v>
+        <v>9574.359340371593</v>
       </c>
       <c r="D48">
-        <v>13527.71353887552</v>
+        <v>13574.9993403716</v>
       </c>
       <c r="E48">
         <v>4290.440000000001</v>
@@ -5229,37 +5229,37 @@
         <v>3390</v>
       </c>
       <c r="M48">
-        <v>571.6229900123977</v>
+        <v>559.5176300123977</v>
       </c>
       <c r="N48">
-        <v>2818.377009987602</v>
+        <v>2830.482369987602</v>
       </c>
       <c r="O48">
-        <v>563.6754019975205</v>
+        <v>566.0964739975205</v>
       </c>
       <c r="P48">
-        <v>2254.701607990082</v>
+        <v>2264.385895990082</v>
       </c>
       <c r="Q48">
-        <v>5036.901607990081</v>
+        <v>5046.585895990082</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1503734406832172</v>
+        <v>0.1503451471498158</v>
       </c>
       <c r="T48">
         <v>1.617280177066592</v>
       </c>
       <c r="U48">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.930482257066805</v>
+        <v>6.058790318948279</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1072517231026986</v>
+        <v>0.1066724782477633</v>
       </c>
       <c r="C49">
-        <v>9352.978816716135</v>
+        <v>9401.304514849264</v>
       </c>
       <c r="D49">
-        <v>13529.05881671613</v>
+        <v>13577.38451484927</v>
       </c>
       <c r="E49">
         <v>4465.88</v>
@@ -5311,37 +5311,37 @@
         <v>3390</v>
       </c>
       <c r="M49">
-        <v>584.0495767517976</v>
+        <v>571.6810567517977</v>
       </c>
       <c r="N49">
-        <v>2805.950423248202</v>
+        <v>2818.318943248202</v>
       </c>
       <c r="O49">
-        <v>561.1900846496404</v>
+        <v>563.6637886496404</v>
       </c>
       <c r="P49">
-        <v>2244.760338598562</v>
+        <v>2254.655154598562</v>
       </c>
       <c r="Q49">
-        <v>5026.960338598561</v>
+        <v>5036.855154598561</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1521118404950901</v>
+        <v>0.1520830766178536</v>
       </c>
       <c r="T49">
         <v>1.644165393209333</v>
       </c>
       <c r="U49">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.804301783512192</v>
+        <v>5.92987988663023</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1072359884182932</v>
+        <v>0.1066447772164592</v>
       </c>
       <c r="C50">
-        <v>9178.884362148528</v>
+        <v>9228.250527641088</v>
       </c>
       <c r="D50">
-        <v>13530.40436214853</v>
+        <v>13579.77052764109</v>
       </c>
       <c r="E50">
         <v>4641.319999999999</v>
@@ -5393,37 +5393,37 @@
         <v>3390</v>
       </c>
       <c r="M50">
-        <v>596.4761634911976</v>
+        <v>583.8444834911975</v>
       </c>
       <c r="N50">
-        <v>2793.523836508803</v>
+        <v>2806.155516508803</v>
       </c>
       <c r="O50">
-        <v>558.7047673017605</v>
+        <v>561.2311033017605</v>
       </c>
       <c r="P50">
-        <v>2234.819069207042</v>
+        <v>2244.924413207042</v>
       </c>
       <c r="Q50">
-        <v>5017.019069207042</v>
+        <v>5027.124413207042</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1539171018381889</v>
+        <v>0.1538878495269698</v>
       </c>
       <c r="T50">
         <v>1.672084656126795</v>
       </c>
       <c r="U50">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.683378829689022</v>
+        <v>5.806340722325435</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1078082537338877</v>
+        <v>0.1066170761851552</v>
       </c>
       <c r="C51">
-        <v>8954.678842307787</v>
+        <v>9055.197379189109</v>
       </c>
       <c r="D51">
-        <v>13481.63884230779</v>
+        <v>13582.15737918911</v>
       </c>
       <c r="E51">
         <v>4816.759999999999</v>
@@ -5475,45 +5475,45 @@
         <v>3390</v>
       </c>
       <c r="M51">
-        <v>621.7975902305975</v>
+        <v>596.0079102305974</v>
       </c>
       <c r="N51">
-        <v>2768.202409769402</v>
+        <v>2793.992089769403</v>
       </c>
       <c r="O51">
-        <v>553.6404819538806</v>
+        <v>558.7984179538806</v>
       </c>
       <c r="P51">
-        <v>2214.561927815522</v>
+        <v>2235.193671815522</v>
       </c>
       <c r="Q51">
-        <v>4996.761927815522</v>
+        <v>5017.393671815522</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1557931577437622</v>
+        <v>0.1557633978442866</v>
       </c>
       <c r="T51">
         <v>1.701098792099843</v>
       </c>
       <c r="U51">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>5.451934927478245</v>
+        <v>5.687843972890223</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1078045190494823</v>
+        <v>0.1065893751538511</v>
       </c>
       <c r="C52">
-        <v>8779.555953426585</v>
+        <v>8882.145069935668</v>
       </c>
       <c r="D52">
-        <v>13481.95595342659</v>
+        <v>13584.54506993567</v>
       </c>
       <c r="E52">
         <v>4992.2</v>
@@ -5557,45 +5557,45 @@
         <v>3390</v>
       </c>
       <c r="M52">
-        <v>634.4873369699975</v>
+        <v>608.1713369699975</v>
       </c>
       <c r="N52">
-        <v>2755.512663030002</v>
+        <v>2781.828663030003</v>
       </c>
       <c r="O52">
-        <v>551.1025326060005</v>
+        <v>556.3657326060005</v>
       </c>
       <c r="P52">
-        <v>2204.410130424002</v>
+        <v>2225.462930424002</v>
       </c>
       <c r="Q52">
-        <v>4986.610130424002</v>
+        <v>5007.662930424001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1577442558855585</v>
+        <v>0.1577139680942962</v>
       </c>
       <c r="T52">
         <v>1.731273493511814</v>
       </c>
       <c r="U52">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>5.342896228928679</v>
+        <v>5.574087093432417</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1078007843650768</v>
+        <v>0.1068880741225471</v>
       </c>
       <c r="C53">
-        <v>8604.433079463723</v>
+        <v>8681.002903480347</v>
       </c>
       <c r="D53">
-        <v>13482.27307946372</v>
+        <v>13558.84290348035</v>
       </c>
       <c r="E53">
         <v>5167.64</v>
@@ -5639,37 +5639,37 @@
         <v>3390</v>
       </c>
       <c r="M53">
-        <v>647.1770837093975</v>
+        <v>627.4927157093975</v>
       </c>
       <c r="N53">
-        <v>2742.822916290603</v>
+        <v>2762.507284290602</v>
       </c>
       <c r="O53">
-        <v>548.5645832581206</v>
+        <v>552.5014568581205</v>
       </c>
       <c r="P53">
-        <v>2194.258333032482</v>
+        <v>2210.005827432482</v>
       </c>
       <c r="Q53">
-        <v>4976.458333032482</v>
+        <v>4992.205827432482</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1597749906862035</v>
+        <v>0.159744153456551</v>
       </c>
       <c r="T53">
         <v>1.76267981538958</v>
       </c>
       <c r="U53">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.238133557773216</v>
+        <v>5.402453152252952</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1077970496806714</v>
+        <v>0.106866773091243</v>
       </c>
       <c r="C54">
-        <v>8429.310220420251</v>
+        <v>8507.392573493064</v>
       </c>
       <c r="D54">
-        <v>13482.59022042025</v>
+        <v>13560.67257349306</v>
       </c>
       <c r="E54">
         <v>5343.080000000001</v>
@@ -5721,37 +5721,37 @@
         <v>3390</v>
       </c>
       <c r="M54">
-        <v>659.8668304487975</v>
+        <v>639.7964944487975</v>
       </c>
       <c r="N54">
-        <v>2730.133169551203</v>
+        <v>2750.203505551202</v>
       </c>
       <c r="O54">
-        <v>546.0266339102405</v>
+        <v>550.0407011102405</v>
       </c>
       <c r="P54">
-        <v>2184.106535640962</v>
+        <v>2200.162804440962</v>
       </c>
       <c r="Q54">
-        <v>4966.306535640962</v>
+        <v>4982.362804440962</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1618903394368754</v>
+        <v>0.1618589298755664</v>
       </c>
       <c r="T54">
         <v>1.795394734012252</v>
       </c>
       <c r="U54">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.137400220123729</v>
+        <v>5.298559822401933</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1077933149962659</v>
+        <v>0.106845472059939</v>
       </c>
       <c r="C55">
-        <v>8254.187376297228</v>
+        <v>8333.782737374502</v>
       </c>
       <c r="D55">
-        <v>13482.90737629723</v>
+        <v>13562.5027373745</v>
       </c>
       <c r="E55">
         <v>5518.52</v>
@@ -5803,37 +5803,37 @@
         <v>3390</v>
       </c>
       <c r="M55">
-        <v>672.5565771881973</v>
+        <v>652.1002731881973</v>
       </c>
       <c r="N55">
-        <v>2717.443422811803</v>
+        <v>2737.899726811803</v>
       </c>
       <c r="O55">
-        <v>543.4886845623605</v>
+        <v>547.5799453623606</v>
       </c>
       <c r="P55">
-        <v>2173.954738249442</v>
+        <v>2190.319781449442</v>
       </c>
       <c r="Q55">
-        <v>4956.154738249442</v>
+        <v>4972.519781449442</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1640957030280015</v>
+        <v>0.1640636967804974</v>
       </c>
       <c r="T55">
         <v>1.829501776831634</v>
       </c>
       <c r="U55">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.040468140498755</v>
+        <v>5.198586995564162</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1077895803118605</v>
+        <v>0.1068241710286349</v>
       </c>
       <c r="C56">
-        <v>8079.064547095697</v>
+        <v>8160.173395324635</v>
       </c>
       <c r="D56">
-        <v>13483.2245470957</v>
+        <v>13564.33339532464</v>
       </c>
       <c r="E56">
         <v>5693.96</v>
@@ -5885,37 +5885,37 @@
         <v>3390</v>
       </c>
       <c r="M56">
-        <v>685.2463239275972</v>
+        <v>664.4040519275974</v>
       </c>
       <c r="N56">
-        <v>2704.753676072403</v>
+        <v>2725.595948072403</v>
       </c>
       <c r="O56">
-        <v>540.9507352144806</v>
+        <v>545.1191896144805</v>
       </c>
       <c r="P56">
-        <v>2163.802940857922</v>
+        <v>2180.476758457922</v>
       </c>
       <c r="Q56">
-        <v>4946.002940857922</v>
+        <v>4962.676758457922</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1663969519926548</v>
+        <v>0.1663643231160775</v>
       </c>
       <c r="T56">
         <v>1.865091734556205</v>
       </c>
       <c r="U56">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.947126137896927</v>
+        <v>5.102316866016677</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.107785845627455</v>
+        <v>0.1068028699973309</v>
       </c>
       <c r="C57">
-        <v>7903.941732816722</v>
+        <v>7986.564547543567</v>
       </c>
       <c r="D57">
-        <v>13483.54173281672</v>
+        <v>13566.16454754357</v>
       </c>
       <c r="E57">
         <v>5869.400000000001</v>
@@ -5967,37 +5967,37 @@
         <v>3390</v>
       </c>
       <c r="M57">
-        <v>697.9360706669972</v>
+        <v>676.7078306669973</v>
       </c>
       <c r="N57">
-        <v>2692.063929333003</v>
+        <v>2713.292169333003</v>
       </c>
       <c r="O57">
-        <v>538.4127858666005</v>
+        <v>542.6584338666006</v>
       </c>
       <c r="P57">
-        <v>2153.651143466402</v>
+        <v>2170.633735466402</v>
       </c>
       <c r="Q57">
-        <v>4935.851143466401</v>
+        <v>4952.833735466402</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1688004786890704</v>
+        <v>0.1687671995110168</v>
       </c>
       <c r="T57">
         <v>1.902263468179648</v>
       </c>
       <c r="U57">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.857178389935163</v>
+        <v>5.009547468452737</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1077821109430496</v>
+        <v>0.1067815689660268</v>
       </c>
       <c r="C58">
-        <v>7728.818933461347</v>
+        <v>7812.956194231492</v>
       </c>
       <c r="D58">
-        <v>13483.85893346135</v>
+        <v>13567.99619423149</v>
       </c>
       <c r="E58">
         <v>6044.840000000001</v>
@@ -6049,37 +6049,37 @@
         <v>3390</v>
       </c>
       <c r="M58">
-        <v>710.6258174063972</v>
+        <v>689.0116094063974</v>
       </c>
       <c r="N58">
-        <v>2679.374182593603</v>
+        <v>2700.988390593603</v>
       </c>
       <c r="O58">
-        <v>535.8748365187206</v>
+        <v>540.1976781187205</v>
       </c>
       <c r="P58">
-        <v>2143.499346074882</v>
+        <v>2160.790712474882</v>
       </c>
       <c r="Q58">
-        <v>4925.699346074882</v>
+        <v>4942.990712474882</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1713132565989595</v>
+        <v>0.1712792975602715</v>
       </c>
       <c r="T58">
         <v>1.941124826058701</v>
       </c>
       <c r="U58">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.770443061543464</v>
+        <v>4.920091263658938</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1077783762586441</v>
+        <v>0.1067602679347228</v>
       </c>
       <c r="C59">
-        <v>7553.696149030624</v>
+        <v>7639.348335588733</v>
       </c>
       <c r="D59">
-        <v>13484.17614903063</v>
+        <v>13569.82833558874</v>
       </c>
       <c r="E59">
         <v>6220.280000000002</v>
@@ -6131,37 +6131,37 @@
         <v>3390</v>
       </c>
       <c r="M59">
-        <v>723.3155641457972</v>
+        <v>701.3153881457973</v>
       </c>
       <c r="N59">
-        <v>2666.684435854203</v>
+        <v>2688.684611854203</v>
       </c>
       <c r="O59">
-        <v>533.3368871708407</v>
+        <v>537.7369223708405</v>
       </c>
       <c r="P59">
-        <v>2133.347548683362</v>
+        <v>2150.947689483362</v>
       </c>
       <c r="Q59">
-        <v>4915.547548683362</v>
+        <v>4933.147689483361</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1739429079000062</v>
+        <v>0.173908237379259</v>
       </c>
       <c r="T59">
         <v>1.981793688955384</v>
       </c>
       <c r="U59">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.686751078007614</v>
+        <v>4.83377387306843</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1077746415742387</v>
+        <v>0.1067389669034187</v>
       </c>
       <c r="C60">
-        <v>7378.573379525622</v>
+        <v>7465.740971815701</v>
       </c>
       <c r="D60">
-        <v>13484.49337952562</v>
+        <v>13571.6609718157</v>
       </c>
       <c r="E60">
         <v>6395.719999999998</v>
@@ -6213,37 +6213,37 @@
         <v>3390</v>
       </c>
       <c r="M60">
-        <v>736.005310885197</v>
+        <v>713.619166885197</v>
       </c>
       <c r="N60">
-        <v>2653.994689114803</v>
+        <v>2676.380833114803</v>
       </c>
       <c r="O60">
-        <v>530.7989378229606</v>
+        <v>535.2761666229607</v>
       </c>
       <c r="P60">
-        <v>2123.195751291842</v>
+        <v>2141.104666491842</v>
       </c>
       <c r="Q60">
-        <v>4905.395751291842</v>
+        <v>4923.304666491842</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1766977806915789</v>
+        <v>0.1766623648086743</v>
       </c>
       <c r="T60">
         <v>2.024399164370957</v>
       </c>
       <c r="U60">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.605945024938517</v>
+        <v>4.750432944222425</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1077709068898332</v>
+        <v>0.1067176658721147</v>
       </c>
       <c r="C61">
-        <v>7203.450624947374</v>
+        <v>7292.134103112916</v>
       </c>
       <c r="D61">
-        <v>13484.81062494737</v>
+        <v>13573.49410311292</v>
       </c>
       <c r="E61">
         <v>6571.159999999999</v>
@@ -6295,37 +6295,37 @@
         <v>3390</v>
       </c>
       <c r="M61">
-        <v>748.695057624597</v>
+        <v>725.922945624597</v>
       </c>
       <c r="N61">
-        <v>2641.304942375403</v>
+        <v>2664.077054375403</v>
       </c>
       <c r="O61">
-        <v>528.2609884750806</v>
+        <v>532.8154108750806</v>
       </c>
       <c r="P61">
-        <v>2113.043953900322</v>
+        <v>2131.261643500322</v>
       </c>
       <c r="Q61">
-        <v>4895.243953900323</v>
+        <v>4913.461643500323</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.179587037521765</v>
+        <v>0.1795508399175735</v>
       </c>
       <c r="T61">
         <v>2.069082955660461</v>
       </c>
       <c r="U61">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.527878160109051</v>
+        <v>4.669917131608484</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1077671722054278</v>
+        <v>0.1066963648408107</v>
       </c>
       <c r="C62">
-        <v>7028.327885296947</v>
+        <v>7118.527729681029</v>
       </c>
       <c r="D62">
-        <v>13485.12788529695</v>
+        <v>13575.32772968103</v>
       </c>
       <c r="E62">
         <v>6746.599999999999</v>
@@ -6377,37 +6377,37 @@
         <v>3390</v>
       </c>
       <c r="M62">
-        <v>761.384804363997</v>
+        <v>738.2267243639971</v>
       </c>
       <c r="N62">
-        <v>2628.615195636003</v>
+        <v>2651.773275636003</v>
       </c>
       <c r="O62">
-        <v>525.7230391272007</v>
+        <v>530.3546551272005</v>
       </c>
       <c r="P62">
-        <v>2102.892156508803</v>
+        <v>2121.418620508802</v>
       </c>
       <c r="Q62">
-        <v>4885.092156508803</v>
+        <v>4903.618620508802</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1826207571934604</v>
+        <v>0.1825837387819175</v>
       </c>
       <c r="T62">
         <v>2.116000936514439</v>
       </c>
       <c r="U62">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.452413524107233</v>
+        <v>4.592085179415009</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1077634375210223</v>
+        <v>0.1066750638095066</v>
       </c>
       <c r="C63">
-        <v>6853.205160575391</v>
+        <v>6944.92185172077</v>
       </c>
       <c r="D63">
-        <v>13485.44516057539</v>
+        <v>13577.16185172077</v>
       </c>
       <c r="E63">
         <v>6922.04</v>
@@ -6459,37 +6459,37 @@
         <v>3390</v>
       </c>
       <c r="M63">
-        <v>774.074551103397</v>
+        <v>750.530503103397</v>
       </c>
       <c r="N63">
-        <v>2615.925448896603</v>
+        <v>2639.469496896603</v>
       </c>
       <c r="O63">
-        <v>523.1850897793206</v>
+        <v>527.8938993793207</v>
       </c>
       <c r="P63">
-        <v>2092.740359117282</v>
+        <v>2111.575597517282</v>
       </c>
       <c r="Q63">
-        <v>4874.940359117282</v>
+        <v>4893.775597517282</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.185810052232935</v>
+        <v>0.1857721709213562</v>
       </c>
       <c r="T63">
         <v>2.165324967668622</v>
       </c>
       <c r="U63">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.37942313846613</v>
+        <v>4.516805094506567</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1077597028366169</v>
+        <v>0.1066537627782026</v>
       </c>
       <c r="C64">
-        <v>6678.082450783759</v>
+        <v>6771.316469432999</v>
       </c>
       <c r="D64">
-        <v>13485.76245078376</v>
+        <v>13578.996469433</v>
       </c>
       <c r="E64">
         <v>7097.48</v>
@@ -6541,37 +6541,37 @@
         <v>3390</v>
       </c>
       <c r="M64">
-        <v>786.764297842797</v>
+        <v>762.8342818427969</v>
       </c>
       <c r="N64">
-        <v>2603.235702157203</v>
+        <v>2627.165718157203</v>
       </c>
       <c r="O64">
-        <v>520.6471404314406</v>
+        <v>525.4331436314407</v>
       </c>
       <c r="P64">
-        <v>2082.588561725762</v>
+        <v>2101.732574525763</v>
       </c>
       <c r="Q64">
-        <v>4864.788561725762</v>
+        <v>4883.932574525763</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1891672049060661</v>
+        <v>0.18912841527866</v>
       </c>
       <c r="T64">
         <v>2.217245000462499</v>
       </c>
       <c r="U64">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.308787281394096</v>
+        <v>4.44395339943388</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1084615681522114</v>
+        <v>0.1066324617468985</v>
       </c>
       <c r="C65">
-        <v>6443.274690438926</v>
+        <v>6597.711583018676</v>
       </c>
       <c r="D65">
-        <v>13426.39469043892</v>
+        <v>13580.83158301867</v>
       </c>
       <c r="E65">
         <v>7272.919999999999</v>
@@ -6623,45 +6623,45 @@
         <v>3390</v>
       </c>
       <c r="M65">
-        <v>814.9278525821968</v>
+        <v>775.1380605821969</v>
       </c>
       <c r="N65">
-        <v>2575.072147417803</v>
+        <v>2614.861939417803</v>
       </c>
       <c r="O65">
-        <v>515.0144294835607</v>
+        <v>522.9723878835606</v>
       </c>
       <c r="P65">
-        <v>2060.057717934243</v>
+        <v>2091.889551534242</v>
       </c>
       <c r="Q65">
-        <v>4842.257717934242</v>
+        <v>4874.089551534242</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1927058252912584</v>
+        <v>0.1926660782498721</v>
       </c>
       <c r="T65">
         <v>2.271971521515504</v>
       </c>
       <c r="U65">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.159877453271941</v>
+        <v>4.373414456585723</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.108469033467806</v>
+        <v>0.1066111607155945</v>
       </c>
       <c r="C66">
-        <v>6267.206040864592</v>
+        <v>6424.107192678865</v>
       </c>
       <c r="D66">
-        <v>13425.76604086459</v>
+        <v>13582.66719267887</v>
       </c>
       <c r="E66">
         <v>7448.36</v>
@@ -6705,45 +6705,45 @@
         <v>3390</v>
       </c>
       <c r="M66">
-        <v>827.8632153215967</v>
+        <v>787.4418393215968</v>
       </c>
       <c r="N66">
-        <v>2562.136784678403</v>
+        <v>2602.558160678403</v>
       </c>
       <c r="O66">
-        <v>512.4273569356807</v>
+        <v>520.5116321356807</v>
       </c>
       <c r="P66">
-        <v>2049.709427742723</v>
+        <v>2082.046528542723</v>
       </c>
       <c r="Q66">
-        <v>4831.909427742723</v>
+        <v>4864.246528542722</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1964410356978503</v>
+        <v>0.1964002780528183</v>
       </c>
       <c r="T66">
         <v>2.329738404849231</v>
       </c>
       <c r="U66">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.094879368064566</v>
+        <v>4.305079855701571</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1084764987834005</v>
+        <v>0.1071098596842904</v>
       </c>
       <c r="C67">
-        <v>6091.137450156662</v>
+        <v>6205.821737886627</v>
       </c>
       <c r="D67">
-        <v>13425.13745015666</v>
+        <v>13539.82173788663</v>
       </c>
       <c r="E67">
         <v>7623.8</v>
@@ -6787,37 +6787,37 @@
         <v>3390</v>
       </c>
       <c r="M67">
-        <v>840.7985780609968</v>
+        <v>811.1492180609969</v>
       </c>
       <c r="N67">
-        <v>2549.201421939003</v>
+        <v>2578.850781939003</v>
       </c>
       <c r="O67">
-        <v>509.8402843878006</v>
+        <v>515.7701563878007</v>
       </c>
       <c r="P67">
-        <v>2039.361137551202</v>
+        <v>2063.080625551203</v>
       </c>
       <c r="Q67">
-        <v>4821.561137551202</v>
+        <v>4845.280625551202</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2003896866991045</v>
+        <v>0.2003478607016471</v>
       </c>
       <c r="T67">
         <v>2.390806252944886</v>
       </c>
       <c r="U67">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.031881223940495</v>
+        <v>4.179255708467045</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1084839640989951</v>
+        <v>0.1070965586529864</v>
       </c>
       <c r="C68">
-        <v>5915.068918306868</v>
+        <v>6031.520979996927</v>
       </c>
       <c r="D68">
-        <v>13424.50891830687</v>
+        <v>13540.96097999693</v>
       </c>
       <c r="E68">
         <v>7799.240000000001</v>
@@ -6869,37 +6869,37 @@
         <v>3390</v>
       </c>
       <c r="M68">
-        <v>853.7339408003967</v>
+        <v>823.6284368003968</v>
       </c>
       <c r="N68">
-        <v>2536.266059199603</v>
+        <v>2566.371563199603</v>
       </c>
       <c r="O68">
-        <v>507.2532118399207</v>
+        <v>513.2743126399207</v>
       </c>
       <c r="P68">
-        <v>2029.012847359683</v>
+        <v>2053.097250559683</v>
       </c>
       <c r="Q68">
-        <v>4811.212847359682</v>
+        <v>4835.297250559683</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2045706112886679</v>
+        <v>0.2045276540945246</v>
       </c>
       <c r="T68">
         <v>2.455466327399109</v>
       </c>
       <c r="U68">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.970792114486852</v>
+        <v>4.11593365227815</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1084914294145896</v>
+        <v>0.1070832576216823</v>
       </c>
       <c r="C69">
-        <v>5739.000445306943</v>
+        <v>5857.220413835281</v>
       </c>
       <c r="D69">
-        <v>13423.88044530694</v>
+        <v>13542.10041383528</v>
       </c>
       <c r="E69">
         <v>7974.680000000001</v>
@@ -6951,37 +6951,37 @@
         <v>3390</v>
       </c>
       <c r="M69">
-        <v>866.6693035397967</v>
+        <v>836.1076555397968</v>
       </c>
       <c r="N69">
-        <v>2523.330696460203</v>
+        <v>2553.892344460203</v>
       </c>
       <c r="O69">
-        <v>504.6661392920407</v>
+        <v>510.7784688920407</v>
       </c>
       <c r="P69">
-        <v>2018.664557168163</v>
+        <v>2043.113875568163</v>
       </c>
       <c r="Q69">
-        <v>4800.864557168163</v>
+        <v>4825.313875568163</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2090049252472957</v>
+        <v>0.2089607682990917</v>
       </c>
       <c r="T69">
         <v>2.524045194244497</v>
       </c>
       <c r="U69">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.911526560539287</v>
+        <v>4.054501806721759</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1084988947301842</v>
+        <v>0.1070699565903783</v>
       </c>
       <c r="C70">
-        <v>5562.932031148624</v>
+        <v>5682.920039450086</v>
       </c>
       <c r="D70">
-        <v>13423.25203114863</v>
+        <v>13543.24003945009</v>
       </c>
       <c r="E70">
         <v>8150.12</v>
@@ -7033,37 +7033,37 @@
         <v>3390</v>
       </c>
       <c r="M70">
-        <v>879.6046662791965</v>
+        <v>848.5868742791966</v>
       </c>
       <c r="N70">
-        <v>2510.395333720804</v>
+        <v>2541.413125720803</v>
       </c>
       <c r="O70">
-        <v>502.0790667441607</v>
+        <v>508.2826251441606</v>
       </c>
       <c r="P70">
-        <v>2008.316266976643</v>
+        <v>2033.130500576643</v>
       </c>
       <c r="Q70">
-        <v>4790.516266976643</v>
+        <v>4815.330500576642</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2137163838283377</v>
+        <v>0.2136709521414442</v>
       </c>
       <c r="T70">
         <v>2.596910240267721</v>
       </c>
       <c r="U70">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.854004111119592</v>
+        <v>3.994876780152322</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1085063600457787</v>
+        <v>0.1070566555590742</v>
       </c>
       <c r="C71">
-        <v>5386.863675823646</v>
+        <v>5508.619856889763</v>
       </c>
       <c r="D71">
-        <v>13422.62367582365</v>
+        <v>13544.37985688977</v>
       </c>
       <c r="E71">
         <v>8325.560000000001</v>
@@ -7115,37 +7115,37 @@
         <v>3390</v>
       </c>
       <c r="M71">
-        <v>892.5400290185966</v>
+        <v>861.0660930185967</v>
       </c>
       <c r="N71">
-        <v>2497.459970981403</v>
+        <v>2528.933906981403</v>
       </c>
       <c r="O71">
-        <v>499.4919941962807</v>
+        <v>505.7867813962807</v>
       </c>
       <c r="P71">
-        <v>1997.967976785123</v>
+        <v>2023.147125585122</v>
       </c>
       <c r="Q71">
-        <v>4780.167976785122</v>
+        <v>4805.347125585122</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2187318074791244</v>
+        <v>0.2186850188123357</v>
       </c>
       <c r="T71">
         <v>2.674476257002122</v>
       </c>
       <c r="U71">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.79814897907438</v>
+        <v>3.936980015222577</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1085138253613733</v>
+        <v>0.1070433545277702</v>
       </c>
       <c r="C72">
-        <v>5210.795379323745</v>
+        <v>5334.319866202752</v>
       </c>
       <c r="D72">
-        <v>13421.99537932375</v>
+        <v>13545.51986620275</v>
       </c>
       <c r="E72">
         <v>8501</v>
@@ -7197,37 +7197,37 @@
         <v>3390</v>
       </c>
       <c r="M72">
-        <v>905.4753917579966</v>
+        <v>873.5453117579966</v>
       </c>
       <c r="N72">
-        <v>2484.524608242004</v>
+        <v>2516.454688242004</v>
       </c>
       <c r="O72">
-        <v>496.9049216484007</v>
+        <v>503.2909376484008</v>
       </c>
       <c r="P72">
-        <v>1987.619686593603</v>
+        <v>2013.163750593603</v>
       </c>
       <c r="Q72">
-        <v>4769.819686593602</v>
+        <v>4795.363750593602</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2240815927066302</v>
+        <v>0.2240333565946198</v>
       </c>
       <c r="T72">
         <v>2.757213341518815</v>
       </c>
       <c r="U72">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.743889707944746</v>
+        <v>3.880737443576541</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1085212906769678</v>
+        <v>0.1070300534964662</v>
       </c>
       <c r="C73">
-        <v>5034.727141640667</v>
+        <v>5160.020067437503</v>
       </c>
       <c r="D73">
-        <v>13421.36714164067</v>
+        <v>13546.6600674375</v>
       </c>
       <c r="E73">
         <v>8676.439999999999</v>
@@ -7279,37 +7279,37 @@
         <v>3390</v>
       </c>
       <c r="M73">
-        <v>918.4107544973964</v>
+        <v>886.0245304973965</v>
       </c>
       <c r="N73">
-        <v>2471.589245502604</v>
+        <v>2503.975469502604</v>
       </c>
       <c r="O73">
-        <v>494.3178491005208</v>
+        <v>500.7950939005207</v>
       </c>
       <c r="P73">
-        <v>1977.271396402083</v>
+        <v>2003.180375602083</v>
       </c>
       <c r="Q73">
-        <v>4759.471396402083</v>
+        <v>4785.380375602082</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2298003286394812</v>
+        <v>0.2297505452584408</v>
       </c>
       <c r="T73">
         <v>2.845656431864246</v>
       </c>
       <c r="U73">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.691158866987778</v>
+        <v>3.82607916972335</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1085287559925624</v>
+        <v>0.1070167524651621</v>
       </c>
       <c r="C74">
-        <v>4858.658962766145</v>
+        <v>4985.720460642489</v>
       </c>
       <c r="D74">
-        <v>13420.73896276615</v>
+        <v>13547.80046064249</v>
       </c>
       <c r="E74">
         <v>8851.880000000001</v>
@@ -7361,37 +7361,37 @@
         <v>3390</v>
       </c>
       <c r="M74">
-        <v>931.3461172367964</v>
+        <v>898.5037492367965</v>
       </c>
       <c r="N74">
-        <v>2458.653882763203</v>
+        <v>2491.496250763204</v>
       </c>
       <c r="O74">
-        <v>491.7307765526407</v>
+        <v>498.2992501526408</v>
       </c>
       <c r="P74">
-        <v>1966.923106210563</v>
+        <v>1993.197000610563</v>
       </c>
       <c r="Q74">
-        <v>4749.123106210563</v>
+        <v>4775.397000610563</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.235927545710393</v>
+        <v>0.2358761045411062</v>
       </c>
       <c r="T74">
         <v>2.940416885805779</v>
       </c>
       <c r="U74">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.639892771612947</v>
+        <v>3.77293918125497</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1085362213081569</v>
+        <v>0.1070034514338581</v>
       </c>
       <c r="C75">
-        <v>4682.59084269193</v>
+        <v>4811.421045866187</v>
       </c>
       <c r="D75">
-        <v>13420.11084269193</v>
+        <v>13548.94104586619</v>
       </c>
       <c r="E75">
         <v>9027.32</v>
@@ -7443,37 +7443,37 @@
         <v>3390</v>
       </c>
       <c r="M75">
-        <v>944.2814799761962</v>
+        <v>910.9829679761964</v>
       </c>
       <c r="N75">
-        <v>2445.718520023804</v>
+        <v>2479.017032023803</v>
       </c>
       <c r="O75">
-        <v>489.1437040047608</v>
+        <v>495.8034064047607</v>
       </c>
       <c r="P75">
-        <v>1956.574816019043</v>
+        <v>1983.213625619043</v>
       </c>
       <c r="Q75">
-        <v>4738.774816019042</v>
+        <v>4765.413625619043</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2425086307124834</v>
+        <v>0.2424554089558208</v>
       </c>
       <c r="T75">
         <v>3.04219663263187</v>
       </c>
       <c r="U75">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V75">
         <v>0.2</v>
       </c>
       <c r="W75">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.590031226796332</v>
+        <v>3.721255082881615</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1085436866237515</v>
+        <v>0.106990150402554</v>
       </c>
       <c r="C76">
-        <v>4506.522781409762</v>
+        <v>4637.121823157113</v>
       </c>
       <c r="D76">
-        <v>13419.48278140976</v>
+        <v>13550.08182315711</v>
       </c>
       <c r="E76">
         <v>9202.759999999998</v>
@@ -7525,37 +7525,37 @@
         <v>3390</v>
       </c>
       <c r="M76">
-        <v>957.2168427155962</v>
+        <v>923.4621867155963</v>
       </c>
       <c r="N76">
-        <v>2432.783157284404</v>
+        <v>2466.537813284403</v>
       </c>
       <c r="O76">
-        <v>486.5566314568808</v>
+        <v>493.3075626568807</v>
       </c>
       <c r="P76">
-        <v>1946.226525827523</v>
+        <v>1973.230250627523</v>
       </c>
       <c r="Q76">
-        <v>4728.426525827523</v>
+        <v>4755.430250627523</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.249595953022427</v>
+        <v>0.2495408137101289</v>
       </c>
       <c r="T76">
         <v>3.151805590752277</v>
       </c>
       <c r="U76">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.541517291299085</v>
+        <v>3.670967852031863</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.108551151939346</v>
+        <v>0.10697684937125</v>
       </c>
       <c r="C77">
-        <v>4330.454778911386</v>
+        <v>4462.822792563773</v>
       </c>
       <c r="D77">
-        <v>13418.85477891139</v>
+        <v>13551.22279256377</v>
       </c>
       <c r="E77">
         <v>9378.200000000001</v>
@@ -7607,37 +7607,37 @@
         <v>3390</v>
       </c>
       <c r="M77">
-        <v>970.1522054549962</v>
+        <v>935.9414054549964</v>
       </c>
       <c r="N77">
-        <v>2419.847794545004</v>
+        <v>2454.058594545004</v>
       </c>
       <c r="O77">
-        <v>483.9695589090009</v>
+        <v>490.8117189090008</v>
       </c>
       <c r="P77">
-        <v>1935.878235636003</v>
+        <v>1963.246875636003</v>
       </c>
       <c r="Q77">
-        <v>4718.078235636003</v>
+        <v>4745.446875636003</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.257250261117166</v>
+        <v>0.2571930508447816</v>
       </c>
       <c r="T77">
         <v>3.270183265522316</v>
       </c>
       <c r="U77">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.49429706074843</v>
+        <v>3.622021614004772</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1085586172549406</v>
+        <v>0.1069635483399459</v>
       </c>
       <c r="C78">
-        <v>4154.386835188552</v>
+        <v>4288.523954134705</v>
       </c>
       <c r="D78">
-        <v>13418.22683518855</v>
+        <v>13552.36395413471</v>
       </c>
       <c r="E78">
         <v>9553.639999999999</v>
@@ -7689,37 +7689,37 @@
         <v>3390</v>
       </c>
       <c r="M78">
-        <v>983.0875681943962</v>
+        <v>948.4206241943963</v>
       </c>
       <c r="N78">
-        <v>2406.912431805604</v>
+        <v>2441.579375805604</v>
       </c>
       <c r="O78">
-        <v>481.3824863611208</v>
+        <v>488.3158751611208</v>
       </c>
       <c r="P78">
-        <v>1925.529945444483</v>
+        <v>1953.263500644483</v>
       </c>
       <c r="Q78">
-        <v>4707.729945444483</v>
+        <v>4735.463500644482</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2655424282198</v>
+        <v>0.2654829744073221</v>
       </c>
       <c r="T78">
         <v>3.398425746523191</v>
       </c>
       <c r="U78">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.448319467843845</v>
+        <v>3.57436343487313</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1085660825705351</v>
+        <v>0.1069502473086419</v>
       </c>
       <c r="C79">
-        <v>3978.31895023301</v>
+        <v>4114.225307918467</v>
       </c>
       <c r="D79">
-        <v>13417.59895023301</v>
+        <v>13553.50530791847</v>
       </c>
       <c r="E79">
         <v>9729.080000000002</v>
@@ -7771,37 +7771,37 @@
         <v>3390</v>
       </c>
       <c r="M79">
-        <v>996.0229309337961</v>
+        <v>960.8998429337963</v>
       </c>
       <c r="N79">
-        <v>2393.977069066204</v>
+        <v>2429.100157066204</v>
       </c>
       <c r="O79">
-        <v>478.7954138132408</v>
+        <v>485.8200314132408</v>
       </c>
       <c r="P79">
-        <v>1915.181655252963</v>
+        <v>1943.280125652963</v>
       </c>
       <c r="Q79">
-        <v>4697.381655252962</v>
+        <v>4725.480125652963</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2745556533313586</v>
+        <v>0.2744937608883443</v>
       </c>
       <c r="T79">
         <v>3.537819747611099</v>
       </c>
       <c r="U79">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V79">
         <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.403536098131587</v>
+        <v>3.527943130524128</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1085735478861297</v>
+        <v>0.1069369462773378</v>
       </c>
       <c r="C80">
-        <v>3802.251124036509</v>
+        <v>3939.926853963614</v>
       </c>
       <c r="D80">
-        <v>13416.97112403651</v>
+        <v>13554.64685396362</v>
       </c>
       <c r="E80">
         <v>9904.52</v>
@@ -7853,37 +7853,37 @@
         <v>3390</v>
       </c>
       <c r="M80">
-        <v>1008.958293673196</v>
+        <v>973.3790616731961</v>
       </c>
       <c r="N80">
-        <v>2381.041706326804</v>
+        <v>2416.620938326804</v>
       </c>
       <c r="O80">
-        <v>476.2083412653608</v>
+        <v>483.3241876653608</v>
       </c>
       <c r="P80">
-        <v>1904.833365061443</v>
+        <v>1933.296750661443</v>
       </c>
       <c r="Q80">
-        <v>4687.033365061443</v>
+        <v>4715.496750661443</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.284388262543968</v>
+        <v>0.2843237097767322</v>
       </c>
       <c r="T80">
         <v>3.689885930616089</v>
       </c>
       <c r="U80">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.359901019950414</v>
+        <v>3.482713090389203</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1085810132017243</v>
+        <v>0.1069236452460338</v>
       </c>
       <c r="C81">
-        <v>3626.1833565908</v>
+        <v>3765.628592318744</v>
       </c>
       <c r="D81">
-        <v>13416.3433565908</v>
+        <v>13555.78859231874</v>
       </c>
       <c r="E81">
         <v>10079.96</v>
@@ -7935,37 +7935,37 @@
         <v>3390</v>
       </c>
       <c r="M81">
-        <v>1021.893656412596</v>
+        <v>985.8582804125962</v>
       </c>
       <c r="N81">
-        <v>2368.106343587404</v>
+        <v>2404.141719587404</v>
       </c>
       <c r="O81">
-        <v>473.6212687174808</v>
+        <v>480.8283439174808</v>
       </c>
       <c r="P81">
-        <v>1894.485074869923</v>
+        <v>1923.313375669923</v>
       </c>
       <c r="Q81">
-        <v>4676.685074869923</v>
+        <v>4705.513375669923</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.295157310729207</v>
+        <v>0.295089844273538</v>
       </c>
       <c r="T81">
         <v>3.856434607240602</v>
       </c>
       <c r="U81">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.317370627292813</v>
+        <v>3.438628114561491</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1085884785173188</v>
+        <v>0.1069103442147297</v>
       </c>
       <c r="C82">
-        <v>3450.115647887636</v>
+        <v>3591.33052303244</v>
       </c>
       <c r="D82">
-        <v>13415.71564788764</v>
+        <v>13556.93052303244</v>
       </c>
       <c r="E82">
         <v>10255.4</v>
@@ -8017,37 +8017,37 @@
         <v>3390</v>
       </c>
       <c r="M82">
-        <v>1034.829019151996</v>
+        <v>998.3374991519961</v>
       </c>
       <c r="N82">
-        <v>2355.170980848004</v>
+        <v>2391.662500848004</v>
       </c>
       <c r="O82">
-        <v>471.0341961696008</v>
+        <v>478.3325001696008</v>
       </c>
       <c r="P82">
-        <v>1884.136784678403</v>
+        <v>1913.330000678403</v>
       </c>
       <c r="Q82">
-        <v>4666.336784678403</v>
+        <v>4695.530000678404</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3070032637329698</v>
+        <v>0.3069325922200244</v>
       </c>
       <c r="T82">
         <v>4.039638151527567</v>
       </c>
       <c r="U82">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V82">
         <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.275903494451653</v>
+        <v>3.395645263129473</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1085959438329134</v>
+        <v>0.1068970431834257</v>
       </c>
       <c r="C83">
-        <v>3274.047997918775</v>
+        <v>3417.032646153335</v>
       </c>
       <c r="D83">
-        <v>13415.08799791878</v>
+        <v>13558.07264615334</v>
       </c>
       <c r="E83">
         <v>10430.84</v>
@@ -8099,37 +8099,37 @@
         <v>3390</v>
       </c>
       <c r="M83">
-        <v>1047.764381891396</v>
+        <v>1010.816717891396</v>
       </c>
       <c r="N83">
-        <v>2342.235618108604</v>
+        <v>2379.183282108604</v>
       </c>
       <c r="O83">
-        <v>468.4471236217209</v>
+        <v>475.8366564217208</v>
       </c>
       <c r="P83">
-        <v>1873.788494486883</v>
+        <v>1903.346625686883</v>
       </c>
       <c r="Q83">
-        <v>4655.988494486883</v>
+        <v>4685.546625686882</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3200961591581814</v>
+        <v>0.3200219452135094</v>
       </c>
       <c r="T83">
         <v>4.242126279423687</v>
       </c>
       <c r="U83">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V83">
         <v>0.2</v>
       </c>
       <c r="W83">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.235460241433731</v>
+        <v>3.353723716671084</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1086034091485079</v>
+        <v>0.1068837421521216</v>
       </c>
       <c r="C84">
-        <v>3097.980406675975</v>
+        <v>3242.734961730057</v>
       </c>
       <c r="D84">
-        <v>13414.46040667598</v>
+        <v>13559.21496173006</v>
       </c>
       <c r="E84">
         <v>10606.28</v>
@@ -8181,37 +8181,37 @@
         <v>3390</v>
       </c>
       <c r="M84">
-        <v>1060.699744630796</v>
+        <v>1023.295936630796</v>
       </c>
       <c r="N84">
-        <v>2329.300255369204</v>
+        <v>2366.704063369204</v>
       </c>
       <c r="O84">
-        <v>465.8600510738409</v>
+        <v>473.3408126738408</v>
       </c>
       <c r="P84">
-        <v>1863.440204295363</v>
+        <v>1893.363250695363</v>
       </c>
       <c r="Q84">
-        <v>4645.640204295363</v>
+        <v>4675.563250695363</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3346438207417497</v>
+        <v>0.334565670761826</v>
       </c>
       <c r="T84">
         <v>4.467113088197151</v>
       </c>
       <c r="U84">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.196003409221124</v>
+        <v>3.312824646955583</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1086108744641024</v>
+        <v>0.1068704411208176</v>
       </c>
       <c r="C85">
-        <v>2921.912874150992</v>
+        <v>3068.437469811252</v>
       </c>
       <c r="D85">
-        <v>13413.83287415099</v>
+        <v>13560.35746981125</v>
       </c>
       <c r="E85">
         <v>10781.72</v>
@@ -8263,37 +8263,37 @@
         <v>3390</v>
       </c>
       <c r="M85">
-        <v>1073.635107370196</v>
+        <v>1035.775155370196</v>
       </c>
       <c r="N85">
-        <v>2316.364892629804</v>
+        <v>2354.224844629804</v>
       </c>
       <c r="O85">
-        <v>463.2729785259609</v>
+        <v>470.8449689259608</v>
       </c>
       <c r="P85">
-        <v>1853.091914103843</v>
+        <v>1883.379875703843</v>
       </c>
       <c r="Q85">
-        <v>4635.291914103844</v>
+        <v>4665.579875703843</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3509029719233849</v>
+        <v>0.3508204228452387</v>
       </c>
       <c r="T85">
         <v>4.718568933296907</v>
       </c>
       <c r="U85">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V85">
         <v>0.2</v>
       </c>
       <c r="W85">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.157497344049786</v>
+        <v>3.272911096992263</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.108618339779697</v>
+        <v>0.1068571400895136</v>
       </c>
       <c r="C86">
-        <v>2745.845400335587</v>
+        <v>2894.140170445586</v>
       </c>
       <c r="D86">
-        <v>13413.20540033559</v>
+        <v>13561.50017044559</v>
       </c>
       <c r="E86">
         <v>10957.16</v>
@@ -8345,37 +8345,37 @@
         <v>3390</v>
       </c>
       <c r="M86">
-        <v>1086.570470109596</v>
+        <v>1048.254374109596</v>
       </c>
       <c r="N86">
-        <v>2303.429529890404</v>
+        <v>2341.745625890404</v>
       </c>
       <c r="O86">
-        <v>460.6859059780809</v>
+        <v>468.3491251780808</v>
       </c>
       <c r="P86">
-        <v>1842.743623912324</v>
+        <v>1873.396500712323</v>
       </c>
       <c r="Q86">
-        <v>4624.943623912323</v>
+        <v>4655.596500712323</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3691945170027244</v>
+        <v>0.3691070189390778</v>
       </c>
       <c r="T86">
         <v>5.001456759034129</v>
       </c>
       <c r="U86">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.119908089953956</v>
+        <v>3.233947869647118</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1086258050952916</v>
+        <v>0.1068438390582095</v>
       </c>
       <c r="C87">
-        <v>2569.777985221515</v>
+        <v>2719.843063681745</v>
       </c>
       <c r="D87">
-        <v>13412.57798522152</v>
+        <v>13562.64306368174</v>
       </c>
       <c r="E87">
         <v>11132.6</v>
@@ -8427,37 +8427,37 @@
         <v>3390</v>
       </c>
       <c r="M87">
-        <v>1099.505832848996</v>
+        <v>1060.733592848996</v>
       </c>
       <c r="N87">
-        <v>2290.494167151004</v>
+        <v>2329.266407151004</v>
       </c>
       <c r="O87">
-        <v>458.0988334302008</v>
+        <v>465.8532814302009</v>
       </c>
       <c r="P87">
-        <v>1832.395333720803</v>
+        <v>1863.413125720803</v>
       </c>
       <c r="Q87">
-        <v>4614.595333720803</v>
+        <v>4645.613125720804</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3899249347593093</v>
+        <v>0.3898318278454289</v>
       </c>
       <c r="T87">
         <v>5.322062961536317</v>
       </c>
       <c r="U87">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V87">
         <v>0.2</v>
       </c>
       <c r="W87">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.083203288895673</v>
+        <v>3.195901424121857</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1086332704108861</v>
+        <v>0.1068305380269055</v>
       </c>
       <c r="C88">
-        <v>2393.710628800549</v>
+        <v>2545.546149568425</v>
       </c>
       <c r="D88">
-        <v>13411.95062880055</v>
+        <v>13563.78614956842</v>
       </c>
       <c r="E88">
         <v>11308.04</v>
@@ -8509,37 +8509,37 @@
         <v>3390</v>
       </c>
       <c r="M88">
-        <v>1112.441195588396</v>
+        <v>1073.212811588396</v>
       </c>
       <c r="N88">
-        <v>2277.558804411604</v>
+        <v>2316.787188411604</v>
       </c>
       <c r="O88">
-        <v>455.5117608823209</v>
+        <v>463.3574376823208</v>
       </c>
       <c r="P88">
-        <v>1822.047043529283</v>
+        <v>1853.429750729283</v>
       </c>
       <c r="Q88">
-        <v>4604.247043529283</v>
+        <v>4635.629750729283</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.413616840766835</v>
+        <v>0.4135173237384017</v>
       </c>
       <c r="T88">
         <v>5.688470050110246</v>
       </c>
       <c r="U88">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V88">
         <v>0.2</v>
       </c>
       <c r="W88">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.047352087862003</v>
+        <v>3.158739779655324</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1086407357264807</v>
+        <v>0.1068172369956014</v>
       </c>
       <c r="C89">
-        <v>2217.643331064448</v>
+        <v>2371.249428154339</v>
       </c>
       <c r="D89">
-        <v>13411.32333106445</v>
+        <v>13564.92942815434</v>
       </c>
       <c r="E89">
         <v>11483.48</v>
@@ -8591,37 +8591,37 @@
         <v>3390</v>
       </c>
       <c r="M89">
-        <v>1125.376558327796</v>
+        <v>1085.692030327796</v>
       </c>
       <c r="N89">
-        <v>2264.623441672205</v>
+        <v>2304.307969672204</v>
       </c>
       <c r="O89">
-        <v>452.9246883344409</v>
+        <v>460.8615939344409</v>
       </c>
       <c r="P89">
-        <v>1811.698753337764</v>
+        <v>1843.446375737763</v>
       </c>
       <c r="Q89">
-        <v>4593.898753337764</v>
+        <v>4625.646375737763</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4409536553909029</v>
+        <v>0.4408467420764471</v>
       </c>
       <c r="T89">
         <v>6.11124746000324</v>
       </c>
       <c r="U89">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V89">
         <v>0.2</v>
       </c>
       <c r="W89">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.012325052369336</v>
+        <v>3.122432425866183</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1104786010420752</v>
+        <v>0.1068039359642974</v>
       </c>
       <c r="C90">
-        <v>1889.535766010767</v>
+        <v>2196.952899488226</v>
       </c>
       <c r="D90">
-        <v>13258.65576601077</v>
+        <v>13566.07289948822</v>
       </c>
       <c r="E90">
         <v>11658.92</v>
@@ -8673,45 +8673,45 @@
         <v>3390</v>
       </c>
       <c r="M90">
-        <v>1178.452593067195</v>
+        <v>1098.171249067196</v>
       </c>
       <c r="N90">
-        <v>2211.547406932805</v>
+        <v>2291.828750932804</v>
       </c>
       <c r="O90">
-        <v>442.3094813865609</v>
+        <v>458.3657501865609</v>
       </c>
       <c r="P90">
-        <v>1769.237925546244</v>
+        <v>1833.463000746243</v>
       </c>
       <c r="Q90">
-        <v>4551.437925546244</v>
+        <v>4615.663000746243</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.472846605785649</v>
+        <v>0.4727310634708335</v>
       </c>
       <c r="T90">
         <v>6.604487771545068</v>
       </c>
       <c r="U90">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V90">
         <v>0.2</v>
       </c>
       <c r="W90">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.876653689714188</v>
+        <v>3.086950239208612</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1105068663576698</v>
+        <v>0.1067906349329933</v>
       </c>
       <c r="C91">
-        <v>1711.774960364524</v>
+        <v>2022.656563618824</v>
       </c>
       <c r="D91">
-        <v>13256.33496036452</v>
+        <v>13567.21656361883</v>
       </c>
       <c r="E91">
         <v>11834.36</v>
@@ -8755,45 +8755,45 @@
         <v>3390</v>
       </c>
       <c r="M91">
-        <v>1191.844099806595</v>
+        <v>1110.650467806596</v>
       </c>
       <c r="N91">
-        <v>2198.155900193405</v>
+        <v>2279.349532193404</v>
       </c>
       <c r="O91">
-        <v>439.631180038681</v>
+        <v>455.8699064386809</v>
       </c>
       <c r="P91">
-        <v>1758.524720154724</v>
+        <v>1823.479625754723</v>
       </c>
       <c r="Q91">
-        <v>4540.724720154723</v>
+        <v>4605.679625754723</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5105382744339851</v>
+        <v>0.5104125342096537</v>
       </c>
       <c r="T91">
         <v>7.187408139730865</v>
       </c>
       <c r="U91">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V91">
         <v>0.2</v>
       </c>
       <c r="W91">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.844331738144366</v>
+        <v>3.052265405060201</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1105351316732643</v>
+        <v>0.1067773339016893</v>
       </c>
       <c r="C92">
-        <v>1534.014967047418</v>
+        <v>1848.3604205949</v>
       </c>
       <c r="D92">
-        <v>13254.01496704742</v>
+        <v>13568.3604205949</v>
       </c>
       <c r="E92">
         <v>12009.8</v>
@@ -8837,45 +8837,45 @@
         <v>3390</v>
       </c>
       <c r="M92">
-        <v>1205.235606545995</v>
+        <v>1123.129686545996</v>
       </c>
       <c r="N92">
-        <v>2184.764393454005</v>
+        <v>2266.870313454005</v>
       </c>
       <c r="O92">
-        <v>436.952878690801</v>
+        <v>453.3740626908009</v>
       </c>
       <c r="P92">
-        <v>1747.811514763204</v>
+        <v>1813.496250763204</v>
       </c>
       <c r="Q92">
-        <v>4530.011514763204</v>
+        <v>4595.696250763203</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5557682768119886</v>
+        <v>0.5556302990962382</v>
       </c>
       <c r="T92">
         <v>7.886912581553822</v>
       </c>
       <c r="U92">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.812728052164983</v>
+        <v>3.018351345003977</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1105633969888589</v>
+        <v>0.1085840328703852</v>
       </c>
       <c r="C93">
-        <v>1356.255785633028</v>
+        <v>1519.294838484726</v>
       </c>
       <c r="D93">
-        <v>13251.69578563303</v>
+        <v>13414.73483848473</v>
       </c>
       <c r="E93">
         <v>12185.24</v>
@@ -8919,37 +8919,37 @@
         <v>3390</v>
       </c>
       <c r="M93">
-        <v>1218.627113285395</v>
+        <v>1175.521505285396</v>
       </c>
       <c r="N93">
-        <v>2171.372886714605</v>
+        <v>2214.478494714604</v>
       </c>
       <c r="O93">
-        <v>434.274577342921</v>
+        <v>442.8956989429209</v>
       </c>
       <c r="P93">
-        <v>1737.098309371684</v>
+        <v>1771.582795771684</v>
       </c>
       <c r="Q93">
-        <v>4519.298309371683</v>
+        <v>4553.782795771684</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6110493908295485</v>
+        <v>0.6108964561798412</v>
       </c>
       <c r="T93">
         <v>8.74186245489299</v>
       </c>
       <c r="U93">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V93">
         <v>0.2</v>
       </c>
       <c r="W93">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.781818952690643</v>
+        <v>2.883826441930528</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1105916623044534</v>
+        <v>0.1085907318390812</v>
       </c>
       <c r="C94">
-        <v>1178.497415695232</v>
+        <v>1343.291690956155</v>
       </c>
       <c r="D94">
-        <v>13249.37741569523</v>
+        <v>13414.17169095616</v>
       </c>
       <c r="E94">
         <v>12360.68</v>
@@ -9001,37 +9001,37 @@
         <v>3390</v>
       </c>
       <c r="M94">
-        <v>1232.018620024795</v>
+        <v>1188.439324024795</v>
       </c>
       <c r="N94">
-        <v>2157.981379975205</v>
+        <v>2201.560675975205</v>
       </c>
       <c r="O94">
-        <v>431.596275995041</v>
+        <v>440.3121351950409</v>
       </c>
       <c r="P94">
-        <v>1726.385103980164</v>
+        <v>1761.248540780164</v>
       </c>
       <c r="Q94">
-        <v>4508.585103980164</v>
+        <v>4543.448540780164</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6801507833514984</v>
+        <v>0.6799791525343453</v>
       </c>
       <c r="T94">
         <v>9.810549796566953</v>
       </c>
       <c r="U94">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V94">
         <v>0.2</v>
       </c>
       <c r="W94">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.751581790161397</v>
+        <v>2.852480502344326</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.110619927620048</v>
+        <v>0.1085974308077771</v>
       </c>
       <c r="C95">
-        <v>1000.739856808204</v>
+        <v>1167.28859070721</v>
       </c>
       <c r="D95">
-        <v>13247.05985680821</v>
+        <v>13413.60859070721</v>
       </c>
       <c r="E95">
         <v>12536.12</v>
@@ -9083,37 +9083,37 @@
         <v>3390</v>
       </c>
       <c r="M95">
-        <v>1245.410126764195</v>
+        <v>1201.357142764195</v>
       </c>
       <c r="N95">
-        <v>2144.589873235805</v>
+        <v>2188.642857235805</v>
       </c>
       <c r="O95">
-        <v>428.9179746471609</v>
+        <v>437.7285714471609</v>
       </c>
       <c r="P95">
-        <v>1715.671898588644</v>
+        <v>1750.914285788644</v>
       </c>
       <c r="Q95">
-        <v>4497.871898588643</v>
+        <v>4533.114285788643</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.7689954308797194</v>
+        <v>0.7687997621329931</v>
       </c>
       <c r="T95">
         <v>11.18457637871919</v>
       </c>
       <c r="U95">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V95">
         <v>0.2</v>
       </c>
       <c r="W95">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.72199488919192</v>
+        <v>2.821808668985785</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1106481929356425</v>
+        <v>0.1086041297764731</v>
       </c>
       <c r="C96">
-        <v>822.9831085464139</v>
+        <v>991.2855377319393</v>
       </c>
       <c r="D96">
-        <v>13244.74310854642</v>
+        <v>13413.04553773194</v>
       </c>
       <c r="E96">
         <v>12711.56</v>
@@ -9165,37 +9165,37 @@
         <v>3390</v>
       </c>
       <c r="M96">
-        <v>1258.801633503595</v>
+        <v>1214.274961503595</v>
       </c>
       <c r="N96">
-        <v>2131.198366496405</v>
+        <v>2175.725038496405</v>
       </c>
       <c r="O96">
-        <v>426.2396732992809</v>
+        <v>435.1450076992809</v>
       </c>
       <c r="P96">
-        <v>1704.958693197124</v>
+        <v>1740.580030797124</v>
       </c>
       <c r="Q96">
-        <v>4487.158693197123</v>
+        <v>4522.780030797123</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.8874549609173477</v>
+        <v>0.8872272415978569</v>
       </c>
       <c r="T96">
         <v>13.01661182158884</v>
       </c>
       <c r="U96">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V96">
         <v>0.2</v>
       </c>
       <c r="W96">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.693037496753707</v>
+        <v>2.791789427826362</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1106764582512371</v>
+        <v>0.108610828745169</v>
       </c>
       <c r="C97">
-        <v>645.227170484628</v>
+        <v>815.2825320243828</v>
       </c>
       <c r="D97">
-        <v>13242.42717048463</v>
+        <v>13412.48253202439</v>
       </c>
       <c r="E97">
         <v>12887</v>
@@ -9247,37 +9247,37 @@
         <v>3390</v>
       </c>
       <c r="M97">
-        <v>1272.193140242995</v>
+        <v>1227.192780242995</v>
       </c>
       <c r="N97">
-        <v>2117.806859757005</v>
+        <v>2162.807219757005</v>
       </c>
       <c r="O97">
-        <v>423.5613719514009</v>
+        <v>432.5614439514009</v>
       </c>
       <c r="P97">
-        <v>1694.245487805604</v>
+        <v>1730.245775805604</v>
       </c>
       <c r="Q97">
-        <v>4476.445487805604</v>
+        <v>4512.445775805603</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.053298302970028</v>
+        <v>1.053025712848667</v>
       </c>
       <c r="T97">
         <v>15.58146144160635</v>
       </c>
       <c r="U97">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V97">
         <v>0.2</v>
       </c>
       <c r="W97">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.664689733629984</v>
+        <v>2.762402170691348</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1107047235668316</v>
+        <v>0.108617527713865</v>
       </c>
       <c r="C98">
-        <v>467.4720421979218</v>
+        <v>639.2795735786021</v>
       </c>
       <c r="D98">
-        <v>13240.11204219792</v>
+        <v>13411.9195735786</v>
       </c>
       <c r="E98">
         <v>13062.44</v>
@@ -9329,37 +9329,37 @@
         <v>3390</v>
       </c>
       <c r="M98">
-        <v>1285.584646982395</v>
+        <v>1240.110598982395</v>
       </c>
       <c r="N98">
-        <v>2104.415353017605</v>
+        <v>2149.889401017605</v>
       </c>
       <c r="O98">
-        <v>420.8830706035211</v>
+        <v>429.977880203521</v>
       </c>
       <c r="P98">
-        <v>1683.532282414084</v>
+        <v>1719.911520814084</v>
       </c>
       <c r="Q98">
-        <v>4465.732282414085</v>
+        <v>4502.111520814084</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.302063316049044</v>
+        <v>1.301723419724878</v>
       </c>
       <c r="T98">
         <v>19.42873587163256</v>
       </c>
       <c r="U98">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V98">
         <v>0.2</v>
       </c>
       <c r="W98">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.636932548904673</v>
+        <v>2.73362714807998</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1107329888824262</v>
+        <v>0.1086242266825609</v>
       </c>
       <c r="C99">
-        <v>289.717723261645</v>
+        <v>463.2766623886346</v>
       </c>
       <c r="D99">
-        <v>13237.79772326165</v>
+        <v>13411.35666238863</v>
       </c>
       <c r="E99">
         <v>13237.88</v>
@@ -9411,37 +9411,37 @@
         <v>3390</v>
       </c>
       <c r="M99">
-        <v>1298.976153721795</v>
+        <v>1253.028417721795</v>
       </c>
       <c r="N99">
-        <v>2091.023846278205</v>
+        <v>2136.971582278205</v>
       </c>
       <c r="O99">
-        <v>418.204769255641</v>
+        <v>427.394316455641</v>
       </c>
       <c r="P99">
-        <v>1672.819077022564</v>
+        <v>1709.577265822564</v>
       </c>
       <c r="Q99">
-        <v>4455.019077022564</v>
+        <v>4491.777265822564</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.716671671180742</v>
+        <v>1.716219597851901</v>
       </c>
       <c r="T99">
         <v>25.84085992167632</v>
       </c>
       <c r="U99">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V99">
         <v>0.2</v>
       </c>
       <c r="W99">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.609747677266479</v>
+        <v>2.705445424903898</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1107612541980207</v>
+        <v>0.1086309256512569</v>
       </c>
       <c r="C100">
-        <v>111.9642132514709</v>
+        <v>287.273798448532</v>
       </c>
       <c r="D100">
-        <v>13235.48421325147</v>
+        <v>13410.79379844853</v>
       </c>
       <c r="E100">
         <v>13413.32</v>
@@ -9493,37 +9493,37 @@
         <v>3390</v>
       </c>
       <c r="M100">
-        <v>1312.367660461195</v>
+        <v>1265.946236461195</v>
       </c>
       <c r="N100">
-        <v>2077.632339538805</v>
+        <v>2124.053763538805</v>
       </c>
       <c r="O100">
-        <v>415.5264679077611</v>
+        <v>424.810752707761</v>
       </c>
       <c r="P100">
-        <v>1662.105871631044</v>
+        <v>1699.243010831044</v>
       </c>
       <c r="Q100">
-        <v>4444.305871631044</v>
+        <v>4481.443010831044</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.545888381444137</v>
+        <v>2.545211954105945</v>
       </c>
       <c r="T100">
         <v>38.66510802176381</v>
       </c>
       <c r="U100">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V100">
         <v>0.2</v>
       </c>
       <c r="W100">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.583117598927026</v>
+        <v>2.67783883893549</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1107895195136153</v>
+        <v>0.1086376246199528</v>
       </c>
       <c r="C101">
-        <v>-65.78848825665045</v>
+        <v>111.2709817523501</v>
       </c>
       <c r="D101">
-        <v>13233.17151174335</v>
+        <v>13410.23098175235</v>
       </c>
       <c r="E101">
         <v>13588.76</v>
@@ -9575,37 +9575,37 @@
         <v>3390</v>
       </c>
       <c r="M101">
-        <v>1325.759167200595</v>
+        <v>1278.864055200595</v>
       </c>
       <c r="N101">
-        <v>2064.240832799405</v>
+        <v>2111.135944799405</v>
       </c>
       <c r="O101">
-        <v>412.8481665598811</v>
+        <v>422.227188959881</v>
       </c>
       <c r="P101">
-        <v>1651.392666239524</v>
+        <v>1688.908755839524</v>
       </c>
       <c r="Q101">
-        <v>4433.592666239524</v>
+        <v>4471.108755839524</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.033538512234323</v>
+        <v>5.03218902286808</v>
       </c>
       <c r="T101">
         <v>77.13785232202632</v>
       </c>
       <c r="U101">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V101">
         <v>0.2</v>
       </c>
       <c r="W101">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>2.557025501968167</v>
+        <v>2.650789961774525</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/thailand/thailand_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_oil_gas_production_and_exploration.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1079744267190534</v>
+        <v>0.1079211256877494</v>
       </c>
       <c r="C2">
-        <v>17535.77995177093</v>
+        <v>17364.85682985699</v>
       </c>
       <c r="D2">
-        <v>13466.17995177093</v>
+        <v>13470.69682985699</v>
       </c>
       <c r="E2">
-        <v>-3779.8</v>
+        <v>-3604.36</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>175.44</v>
       </c>
       <c r="G2">
         <v>4069.6</v>
@@ -1457,28 +1457,28 @@
         <v>3390</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.60201873939995</v>
       </c>
       <c r="N2">
-        <v>3390</v>
+        <v>3378.3979812606</v>
       </c>
       <c r="O2">
-        <v>678</v>
+        <v>675.6795962521201</v>
       </c>
       <c r="P2">
-        <v>2712</v>
+        <v>2702.71838500848</v>
       </c>
       <c r="Q2">
-        <v>5494.2</v>
+        <v>5484.918385008479</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1079744267190534</v>
+        <v>0.1084768463289044</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065633</v>
+        <v>0.969590879082374</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>292.1905296091022</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1079211256877494</v>
+        <v>0.1078678246564453</v>
       </c>
       <c r="C3">
-        <v>17364.85682985699</v>
+        <v>17193.93673909716</v>
       </c>
       <c r="D3">
-        <v>13470.69682985699</v>
+        <v>13475.21673909716</v>
       </c>
       <c r="E3">
-        <v>-3604.36</v>
+        <v>-3428.92</v>
       </c>
       <c r="F3">
-        <v>175.44</v>
+        <v>350.88</v>
       </c>
       <c r="G3">
         <v>4069.6</v>
@@ -1539,28 +1539,28 @@
         <v>3390</v>
       </c>
       <c r="M3">
-        <v>11.60201873939995</v>
+        <v>23.2040374787999</v>
       </c>
       <c r="N3">
-        <v>3378.3979812606</v>
+        <v>3366.7959625212</v>
       </c>
       <c r="O3">
-        <v>675.6795962521201</v>
+        <v>673.3591925042401</v>
       </c>
       <c r="P3">
-        <v>2702.71838500848</v>
+        <v>2693.43677001696</v>
       </c>
       <c r="Q3">
-        <v>5484.918385008479</v>
+        <v>5475.636770016959</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1084768463289044</v>
+        <v>0.1089895194001808</v>
       </c>
       <c r="T3">
-        <v>0.969590879082374</v>
+        <v>0.977521768445446</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>292.1905296091022</v>
+        <v>146.0952648045511</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1078678246564453</v>
+        <v>0.1078145236251413</v>
       </c>
       <c r="C4">
-        <v>17193.93673909716</v>
+        <v>17023.01968254364</v>
       </c>
       <c r="D4">
-        <v>13475.21673909716</v>
+        <v>13479.73968254364</v>
       </c>
       <c r="E4">
-        <v>-3428.92</v>
+        <v>-3253.48</v>
       </c>
       <c r="F4">
-        <v>350.88</v>
+        <v>526.3199999999999</v>
       </c>
       <c r="G4">
         <v>4069.6</v>
@@ -1621,28 +1621,28 @@
         <v>3390</v>
       </c>
       <c r="M4">
-        <v>23.2040374787999</v>
+        <v>34.80605621819985</v>
       </c>
       <c r="N4">
-        <v>3366.7959625212</v>
+        <v>3355.1939437818</v>
       </c>
       <c r="O4">
-        <v>673.3591925042401</v>
+        <v>671.0387887563601</v>
       </c>
       <c r="P4">
-        <v>2693.43677001696</v>
+        <v>2684.15515502544</v>
       </c>
       <c r="Q4">
-        <v>5475.636770016959</v>
+        <v>5466.35515502544</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1089895194001808</v>
+        <v>0.1095127630502465</v>
       </c>
       <c r="T4">
-        <v>0.977521768445446</v>
+        <v>0.9856161813005401</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>146.0952648045511</v>
+        <v>97.39684320303408</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1078145236251413</v>
+        <v>0.1077612225938372</v>
       </c>
       <c r="C5">
-        <v>17023.01968254364</v>
+        <v>16852.10566325275</v>
       </c>
       <c r="D5">
-        <v>13479.73968254364</v>
+        <v>13484.26566325275</v>
       </c>
       <c r="E5">
-        <v>-3253.48</v>
+        <v>-3078.04</v>
       </c>
       <c r="F5">
-        <v>526.3199999999999</v>
+        <v>701.76</v>
       </c>
       <c r="G5">
         <v>4069.6</v>
@@ -1703,28 +1703,28 @@
         <v>3390</v>
       </c>
       <c r="M5">
-        <v>34.80605621819985</v>
+        <v>46.4080749575998</v>
       </c>
       <c r="N5">
-        <v>3355.1939437818</v>
+        <v>3343.5919250424</v>
       </c>
       <c r="O5">
-        <v>671.0387887563601</v>
+        <v>668.7183850084801</v>
       </c>
       <c r="P5">
-        <v>2684.15515502544</v>
+        <v>2674.87354003392</v>
       </c>
       <c r="Q5">
-        <v>5466.35515502544</v>
+        <v>5457.07354003392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1095127630502465</v>
+        <v>0.1100469076096885</v>
       </c>
       <c r="T5">
-        <v>0.9856161813005401</v>
+        <v>0.9938792277567822</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>97.39684320303408</v>
+        <v>73.04763240227555</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1077612225938372</v>
+        <v>0.1077079215625332</v>
       </c>
       <c r="C6">
-        <v>16852.10566325275</v>
+        <v>16681.19468428491</v>
       </c>
       <c r="D6">
-        <v>13484.26566325275</v>
+        <v>13488.79468428491</v>
       </c>
       <c r="E6">
-        <v>-3078.04</v>
+        <v>-2902.6</v>
       </c>
       <c r="F6">
-        <v>701.76</v>
+        <v>877.2</v>
       </c>
       <c r="G6">
         <v>4069.6</v>
@@ -1785,28 +1785,28 @@
         <v>3390</v>
       </c>
       <c r="M6">
-        <v>46.4080749575998</v>
+        <v>58.01009369699975</v>
       </c>
       <c r="N6">
-        <v>3343.5919250424</v>
+        <v>3331.989906303</v>
       </c>
       <c r="O6">
-        <v>668.7183850084801</v>
+        <v>666.3979812606001</v>
       </c>
       <c r="P6">
-        <v>2674.87354003392</v>
+        <v>2665.5919250424</v>
       </c>
       <c r="Q6">
-        <v>5457.07354003392</v>
+        <v>5447.7919250424</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1100469076096885</v>
+        <v>0.1105922973177504</v>
       </c>
       <c r="T6">
-        <v>0.9938792277567822</v>
+        <v>1.002316233085787</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.04763240227555</v>
+        <v>58.43810592182044</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1077079215625332</v>
+        <v>0.1076546205312291</v>
       </c>
       <c r="C7">
-        <v>16681.19468428491</v>
+        <v>16510.28674870464</v>
       </c>
       <c r="D7">
-        <v>13488.79468428491</v>
+        <v>13493.32674870464</v>
       </c>
       <c r="E7">
-        <v>-2902.6</v>
+        <v>-2727.16</v>
       </c>
       <c r="F7">
-        <v>877.2</v>
+        <v>1052.64</v>
       </c>
       <c r="G7">
         <v>4069.6</v>
@@ -1867,28 +1867,28 @@
         <v>3390</v>
       </c>
       <c r="M7">
-        <v>58.01009369699975</v>
+        <v>69.61211243639971</v>
       </c>
       <c r="N7">
-        <v>3331.989906303</v>
+        <v>3320.3878875636</v>
       </c>
       <c r="O7">
-        <v>666.3979812606001</v>
+        <v>664.07757751272</v>
       </c>
       <c r="P7">
-        <v>2665.5919250424</v>
+        <v>2656.31031005088</v>
       </c>
       <c r="Q7">
-        <v>5447.7919250424</v>
+        <v>5438.51031005088</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1105922973177504</v>
+        <v>0.111149291062154</v>
       </c>
       <c r="T7">
-        <v>1.002316233085787</v>
+        <v>1.010932749166473</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.43810592182044</v>
+        <v>48.69842160151703</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1076546205312291</v>
+        <v>0.1076013194999251</v>
       </c>
       <c r="C8">
-        <v>16510.28674870464</v>
+        <v>16339.3818595806</v>
       </c>
       <c r="D8">
-        <v>13493.32674870464</v>
+        <v>13497.86185958059</v>
       </c>
       <c r="E8">
-        <v>-2727.16</v>
+        <v>-2551.72</v>
       </c>
       <c r="F8">
-        <v>1052.64</v>
+        <v>1228.08</v>
       </c>
       <c r="G8">
         <v>4069.6</v>
@@ -1949,28 +1949,28 @@
         <v>3390</v>
       </c>
       <c r="M8">
-        <v>69.6121124363997</v>
+        <v>81.21413117579965</v>
       </c>
       <c r="N8">
-        <v>3320.3878875636</v>
+        <v>3308.7858688242</v>
       </c>
       <c r="O8">
-        <v>664.07757751272</v>
+        <v>661.7571737648401</v>
       </c>
       <c r="P8">
-        <v>2656.31031005088</v>
+        <v>2647.02869505936</v>
       </c>
       <c r="Q8">
-        <v>5438.51031005088</v>
+        <v>5429.228695059361</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.111149291062154</v>
+        <v>0.1117182631666523</v>
       </c>
       <c r="T8">
-        <v>1.010932749166473</v>
+        <v>1.019734566668249</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.69842160151703</v>
+        <v>41.74150422987175</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1076013194999251</v>
+        <v>0.107548018468621</v>
       </c>
       <c r="C9">
-        <v>16339.3818595806</v>
+        <v>16168.48001998556</v>
       </c>
       <c r="D9">
-        <v>13497.8618595806</v>
+        <v>13502.40001998556</v>
       </c>
       <c r="E9">
-        <v>-2551.72</v>
+        <v>-2376.28</v>
       </c>
       <c r="F9">
-        <v>1228.08</v>
+        <v>1403.52</v>
       </c>
       <c r="G9">
         <v>4069.6</v>
@@ -2031,28 +2031,28 @@
         <v>3390</v>
       </c>
       <c r="M9">
-        <v>81.21413117579966</v>
+        <v>92.8161499151996</v>
       </c>
       <c r="N9">
-        <v>3308.7858688242</v>
+        <v>3297.1838500848</v>
       </c>
       <c r="O9">
-        <v>661.7571737648401</v>
+        <v>659.4367700169601</v>
       </c>
       <c r="P9">
-        <v>2647.02869505936</v>
+        <v>2637.74708006784</v>
       </c>
       <c r="Q9">
-        <v>5429.228695059361</v>
+        <v>5419.94708006784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1117182631666523</v>
+        <v>0.1122996042299441</v>
       </c>
       <c r="T9">
-        <v>1.019734566668249</v>
+        <v>1.028727728028759</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.74150422987174</v>
+        <v>36.52381620113778</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.107548018468621</v>
+        <v>0.107494717437317</v>
       </c>
       <c r="C10">
-        <v>16168.48001998556</v>
+        <v>15997.58123299643</v>
       </c>
       <c r="D10">
-        <v>13502.40001998556</v>
+        <v>13506.94123299643</v>
       </c>
       <c r="E10">
-        <v>-2376.28</v>
+        <v>-2200.84</v>
       </c>
       <c r="F10">
-        <v>1403.52</v>
+        <v>1578.96</v>
       </c>
       <c r="G10">
         <v>4069.6</v>
@@ -2113,28 +2113,28 @@
         <v>3390</v>
       </c>
       <c r="M10">
-        <v>92.8161499151996</v>
+        <v>104.4181686545996</v>
       </c>
       <c r="N10">
-        <v>3297.1838500848</v>
+        <v>3285.581831345401</v>
       </c>
       <c r="O10">
-        <v>659.4367700169601</v>
+        <v>657.1163662690801</v>
       </c>
       <c r="P10">
-        <v>2637.74708006784</v>
+        <v>2628.46546507632</v>
       </c>
       <c r="Q10">
-        <v>5419.94708006784</v>
+        <v>5410.66546507632</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1122996042299441</v>
+        <v>0.1128937220199016</v>
       </c>
       <c r="T10">
-        <v>1.028727728028759</v>
+        <v>1.037918541287302</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.52381620113778</v>
+        <v>32.46561440101136</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.107494717437317</v>
+        <v>0.1074414164060129</v>
       </c>
       <c r="C11">
-        <v>15997.58123299643</v>
+        <v>15826.68550169427</v>
       </c>
       <c r="D11">
-        <v>13506.94123299643</v>
+        <v>13511.48550169427</v>
       </c>
       <c r="E11">
-        <v>-2200.84</v>
+        <v>-2025.4</v>
       </c>
       <c r="F11">
-        <v>1578.96</v>
+        <v>1754.4</v>
       </c>
       <c r="G11">
         <v>4069.6</v>
@@ -2195,28 +2195,28 @@
         <v>3390</v>
       </c>
       <c r="M11">
-        <v>104.4181686545996</v>
+        <v>116.0201873939995</v>
       </c>
       <c r="N11">
-        <v>3285.581831345401</v>
+        <v>3273.979812606</v>
       </c>
       <c r="O11">
-        <v>657.1163662690801</v>
+        <v>654.7959625212002</v>
       </c>
       <c r="P11">
-        <v>2628.46546507632</v>
+        <v>2619.1838500848</v>
       </c>
       <c r="Q11">
-        <v>5410.66546507632</v>
+        <v>5401.3838500848</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1128937220199016</v>
+        <v>0.1135010424274137</v>
       </c>
       <c r="T11">
-        <v>1.037918541287302</v>
+        <v>1.04731359484048</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.46561440101136</v>
+        <v>29.21905296091023</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.107441416406013</v>
+        <v>0.1073881153747089</v>
       </c>
       <c r="C12">
-        <v>15826.68550169427</v>
+        <v>15655.79282916428</v>
       </c>
       <c r="D12">
-        <v>13511.48550169427</v>
+        <v>13516.03282916428</v>
       </c>
       <c r="E12">
-        <v>-2025.4</v>
+        <v>-1849.96</v>
       </c>
       <c r="F12">
-        <v>1754.4</v>
+        <v>1929.84</v>
       </c>
       <c r="G12">
         <v>4069.6</v>
@@ -2277,28 +2277,28 @@
         <v>3390</v>
       </c>
       <c r="M12">
-        <v>116.0201873939995</v>
+        <v>127.6222061333994</v>
       </c>
       <c r="N12">
-        <v>3273.979812606</v>
+        <v>3262.377793866601</v>
       </c>
       <c r="O12">
-        <v>654.7959625212002</v>
+        <v>652.4755587733202</v>
       </c>
       <c r="P12">
-        <v>2619.1838500848</v>
+        <v>2609.902235093281</v>
       </c>
       <c r="Q12">
-        <v>5401.3838500848</v>
+        <v>5392.10223509328</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1135010424274137</v>
+        <v>0.1141220104845329</v>
       </c>
       <c r="T12">
-        <v>1.04731359484048</v>
+        <v>1.056919773192605</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.21905296091022</v>
+        <v>26.5627754190093</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1073881153747089</v>
+        <v>0.1073348143434049</v>
       </c>
       <c r="C13">
-        <v>15655.79282916428</v>
+        <v>15484.9032184958</v>
       </c>
       <c r="D13">
-        <v>13516.03282916428</v>
+        <v>13520.5832184958</v>
       </c>
       <c r="E13">
-        <v>-1849.96</v>
+        <v>-1674.52</v>
       </c>
       <c r="F13">
-        <v>1929.84</v>
+        <v>2105.28</v>
       </c>
       <c r="G13">
         <v>4069.6</v>
@@ -2359,28 +2359,28 @@
         <v>3390</v>
       </c>
       <c r="M13">
-        <v>127.6222061333994</v>
+        <v>139.2242248727994</v>
       </c>
       <c r="N13">
-        <v>3262.377793866601</v>
+        <v>3250.775775127201</v>
       </c>
       <c r="O13">
-        <v>652.4755587733202</v>
+        <v>650.1551550254402</v>
       </c>
       <c r="P13">
-        <v>2609.902235093281</v>
+        <v>2600.62062010176</v>
       </c>
       <c r="Q13">
-        <v>5392.10223509328</v>
+        <v>5382.82062010176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1141220104845329</v>
+        <v>0.114757091452041</v>
       </c>
       <c r="T13">
-        <v>1.056919773192605</v>
+        <v>1.066744273780007</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.5627754190093</v>
+        <v>24.34921080075852</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1073348143434049</v>
+        <v>0.1072815133121008</v>
       </c>
       <c r="C14">
-        <v>15484.9032184958</v>
+        <v>15314.01667278236</v>
       </c>
       <c r="D14">
-        <v>13520.5832184958</v>
+        <v>13525.13667278236</v>
       </c>
       <c r="E14">
-        <v>-1674.52</v>
+        <v>-1499.08</v>
       </c>
       <c r="F14">
-        <v>2105.28</v>
+        <v>2280.72</v>
       </c>
       <c r="G14">
         <v>4069.6</v>
@@ -2441,28 +2441,28 @@
         <v>3390</v>
       </c>
       <c r="M14">
-        <v>139.2242248727994</v>
+        <v>150.8262436121994</v>
       </c>
       <c r="N14">
-        <v>3250.775775127201</v>
+        <v>3239.1737563878</v>
       </c>
       <c r="O14">
-        <v>650.1551550254402</v>
+        <v>647.8347512775601</v>
       </c>
       <c r="P14">
-        <v>2600.62062010176</v>
+        <v>2591.339005110241</v>
       </c>
       <c r="Q14">
-        <v>5382.82062010176</v>
+        <v>5373.53900511024</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.114757091452041</v>
+        <v>0.1154067719820207</v>
       </c>
       <c r="T14">
-        <v>1.066744273780007</v>
+        <v>1.076794624955624</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.34921080075852</v>
+        <v>22.47619458531555</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1072815133121008</v>
+        <v>0.1072282122807968</v>
       </c>
       <c r="C15">
-        <v>15314.01667278236</v>
+        <v>15143.13319512164</v>
       </c>
       <c r="D15">
-        <v>13525.13667278236</v>
+        <v>13529.69319512164</v>
       </c>
       <c r="E15">
-        <v>-1499.08</v>
+        <v>-1323.64</v>
       </c>
       <c r="F15">
-        <v>2280.72</v>
+        <v>2456.16</v>
       </c>
       <c r="G15">
         <v>4069.6</v>
@@ -2523,28 +2523,28 @@
         <v>3390</v>
       </c>
       <c r="M15">
-        <v>150.8262436121994</v>
+        <v>162.4282623515993</v>
       </c>
       <c r="N15">
-        <v>3239.1737563878</v>
+        <v>3227.571737648401</v>
       </c>
       <c r="O15">
-        <v>647.8347512775601</v>
+        <v>645.5143475296802</v>
       </c>
       <c r="P15">
-        <v>2591.339005110241</v>
+        <v>2582.057390118721</v>
       </c>
       <c r="Q15">
-        <v>5373.53900511024</v>
+        <v>5364.257390118721</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1154067719820207</v>
+        <v>0.1160715613615348</v>
       </c>
       <c r="T15">
-        <v>1.076794624955624</v>
+        <v>1.087078705228348</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.47619458531555</v>
+        <v>20.87075211493587</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1072282122807968</v>
+        <v>0.1071749112494927</v>
       </c>
       <c r="C16">
-        <v>15143.13319512164</v>
+        <v>14972.2527886155</v>
       </c>
       <c r="D16">
-        <v>13529.69319512164</v>
+        <v>13534.2527886155</v>
       </c>
       <c r="E16">
-        <v>-1323.64</v>
+        <v>-1148.2</v>
       </c>
       <c r="F16">
-        <v>2456.16</v>
+        <v>2631.6</v>
       </c>
       <c r="G16">
         <v>4069.6</v>
@@ -2605,28 +2605,28 @@
         <v>3390</v>
       </c>
       <c r="M16">
-        <v>162.4282623515993</v>
+        <v>174.0302810909993</v>
       </c>
       <c r="N16">
-        <v>3227.571737648401</v>
+        <v>3215.969718909001</v>
       </c>
       <c r="O16">
-        <v>645.5143475296802</v>
+        <v>643.1939437818002</v>
       </c>
       <c r="P16">
-        <v>2582.057390118721</v>
+        <v>2572.775775127201</v>
       </c>
       <c r="Q16">
-        <v>5364.257390118721</v>
+        <v>5354.975775127201</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1160715613615348</v>
+        <v>0.1167519928440963</v>
       </c>
       <c r="T16">
-        <v>1.087078705228348</v>
+        <v>1.097604763860431</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.87075211493587</v>
+        <v>19.47936864060681</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1071749112494927</v>
+        <v>0.1071216102181887</v>
       </c>
       <c r="C17">
-        <v>14972.2527886155</v>
+        <v>14801.37545636998</v>
       </c>
       <c r="D17">
-        <v>13534.2527886155</v>
+        <v>13538.81545636998</v>
       </c>
       <c r="E17">
-        <v>-1148.2</v>
+        <v>-972.7600000000002</v>
       </c>
       <c r="F17">
-        <v>2631.6</v>
+        <v>2807.04</v>
       </c>
       <c r="G17">
         <v>4069.6</v>
@@ -2687,28 +2687,28 @@
         <v>3390</v>
       </c>
       <c r="M17">
-        <v>174.0302810909992</v>
+        <v>185.6322998303992</v>
       </c>
       <c r="N17">
-        <v>3215.969718909001</v>
+        <v>3204.367700169601</v>
       </c>
       <c r="O17">
-        <v>643.1939437818002</v>
+        <v>640.8735400339202</v>
       </c>
       <c r="P17">
-        <v>2572.775775127201</v>
+        <v>2563.494160135681</v>
       </c>
       <c r="Q17">
-        <v>5354.975775127201</v>
+        <v>5345.694160135681</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1167519928440963</v>
+        <v>0.1174486250762425</v>
       </c>
       <c r="T17">
-        <v>1.097604763860431</v>
+        <v>1.108381442936135</v>
       </c>
       <c r="U17">
         <v>0.06613097776675758</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.47936864060681</v>
+        <v>18.26190810056889</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1071216102181887</v>
+        <v>0.1070683091868846</v>
       </c>
       <c r="C18">
-        <v>14801.37545636998</v>
+        <v>14630.50120149532</v>
       </c>
       <c r="D18">
-        <v>13538.81545636998</v>
+        <v>13543.38120149532</v>
       </c>
       <c r="E18">
-        <v>-972.7600000000002</v>
+        <v>-797.3200000000002</v>
       </c>
       <c r="F18">
-        <v>2807.04</v>
+        <v>2982.48</v>
       </c>
       <c r="G18">
         <v>4069.6</v>
@@ -2769,28 +2769,28 @@
         <v>3390</v>
       </c>
       <c r="M18">
-        <v>185.6322998303992</v>
+        <v>197.2343185697991</v>
       </c>
       <c r="N18">
-        <v>3204.367700169601</v>
+        <v>3192.765681430201</v>
       </c>
       <c r="O18">
-        <v>640.8735400339202</v>
+        <v>638.5531362860402</v>
       </c>
       <c r="P18">
-        <v>2563.494160135681</v>
+        <v>2554.212545144161</v>
       </c>
       <c r="Q18">
-        <v>5345.694160135681</v>
+        <v>5336.412545144161</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1174486250762425</v>
+        <v>0.1181620436272356</v>
       </c>
       <c r="T18">
-        <v>1.108381442936135</v>
+        <v>1.119417801025711</v>
       </c>
       <c r="U18">
         <v>0.06613097776675758</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.26190810056889</v>
+        <v>17.18767821230013</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1070683091868846</v>
+        <v>0.1070150081555806</v>
       </c>
       <c r="C19">
-        <v>14630.50120149532</v>
+        <v>14459.63002710595</v>
       </c>
       <c r="D19">
-        <v>13543.38120149532</v>
+        <v>13547.95002710595</v>
       </c>
       <c r="E19">
-        <v>-797.3200000000002</v>
+        <v>-621.8799999999997</v>
       </c>
       <c r="F19">
-        <v>2982.48</v>
+        <v>3157.920000000001</v>
       </c>
       <c r="G19">
         <v>4069.6</v>
@@ -2851,28 +2851,28 @@
         <v>3390</v>
       </c>
       <c r="M19">
-        <v>197.2343185697991</v>
+        <v>208.8363373091991</v>
       </c>
       <c r="N19">
-        <v>3192.765681430201</v>
+        <v>3181.163662690801</v>
       </c>
       <c r="O19">
-        <v>638.5531362860402</v>
+        <v>636.2327325381602</v>
       </c>
       <c r="P19">
-        <v>2554.212545144161</v>
+        <v>2544.93093015264</v>
       </c>
       <c r="Q19">
-        <v>5336.412545144161</v>
+        <v>5327.13093015264</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1181620436272356</v>
+        <v>0.1188928626306921</v>
       </c>
       <c r="T19">
-        <v>1.119417801025711</v>
+        <v>1.130723338580887</v>
       </c>
       <c r="U19">
         <v>0.06613097776675758</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.18767821230013</v>
+        <v>16.23280720050568</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1070150081555806</v>
+        <v>0.1069617071242766</v>
       </c>
       <c r="C20">
-        <v>14459.63002710595</v>
+        <v>14288.76193632049</v>
       </c>
       <c r="D20">
-        <v>13547.95002710595</v>
+        <v>13552.52193632049</v>
       </c>
       <c r="E20">
-        <v>-621.8800000000001</v>
+        <v>-446.4400000000001</v>
       </c>
       <c r="F20">
-        <v>3157.92</v>
+        <v>3333.36</v>
       </c>
       <c r="G20">
         <v>4069.6</v>
@@ -2933,28 +2933,28 @@
         <v>3390</v>
       </c>
       <c r="M20">
-        <v>208.8363373091991</v>
+        <v>220.438356048599</v>
       </c>
       <c r="N20">
-        <v>3181.163662690801</v>
+        <v>3169.561643951401</v>
       </c>
       <c r="O20">
-        <v>636.2327325381602</v>
+        <v>633.9123287902803</v>
       </c>
       <c r="P20">
-        <v>2544.93093015264</v>
+        <v>2535.649315161121</v>
       </c>
       <c r="Q20">
-        <v>5327.13093015264</v>
+        <v>5317.84931516112</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1188928626306921</v>
+        <v>0.1196417265478141</v>
       </c>
       <c r="T20">
-        <v>1.130723338580887</v>
+        <v>1.142308025211499</v>
       </c>
       <c r="U20">
         <v>0.06613097776675758</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.23280720050568</v>
+        <v>15.37844892679485</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1069617071242766</v>
+        <v>0.1069084060929725</v>
       </c>
       <c r="C21">
-        <v>14288.76193632049</v>
+        <v>14117.89693226181</v>
       </c>
       <c r="D21">
-        <v>13552.52193632049</v>
+        <v>13557.09693226181</v>
       </c>
       <c r="E21">
-        <v>-446.4400000000001</v>
+        <v>-271</v>
       </c>
       <c r="F21">
-        <v>3333.36</v>
+        <v>3508.8</v>
       </c>
       <c r="G21">
         <v>4069.6</v>
@@ -3015,28 +3015,28 @@
         <v>3390</v>
       </c>
       <c r="M21">
-        <v>220.438356048599</v>
+        <v>232.040374787999</v>
       </c>
       <c r="N21">
-        <v>3169.561643951401</v>
+        <v>3157.959625212001</v>
       </c>
       <c r="O21">
-        <v>633.9123287902803</v>
+        <v>631.5919250424002</v>
       </c>
       <c r="P21">
-        <v>2535.649315161121</v>
+        <v>2526.367700169601</v>
       </c>
       <c r="Q21">
-        <v>5317.84931516112</v>
+        <v>5308.5677001696</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1196417265478141</v>
+        <v>0.1204093120628641</v>
       </c>
       <c r="T21">
-        <v>1.142308025211499</v>
+        <v>1.154182329007876</v>
       </c>
       <c r="U21">
         <v>0.06613097776675758</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.37844892679485</v>
+        <v>14.60952648045511</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1069084060929725</v>
+        <v>0.1068551050616685</v>
       </c>
       <c r="C22">
-        <v>14117.89693226181</v>
+        <v>13947.03501805695</v>
       </c>
       <c r="D22">
-        <v>13557.09693226181</v>
+        <v>13561.67501805695</v>
       </c>
       <c r="E22">
-        <v>-271</v>
+        <v>-95.55999999999995</v>
       </c>
       <c r="F22">
-        <v>3508.8</v>
+        <v>3684.24</v>
       </c>
       <c r="G22">
         <v>4069.6</v>
@@ -3097,28 +3097,28 @@
         <v>3390</v>
       </c>
       <c r="M22">
-        <v>232.040374787999</v>
+        <v>243.642393527399</v>
       </c>
       <c r="N22">
-        <v>3157.959625212001</v>
+        <v>3146.357606472601</v>
       </c>
       <c r="O22">
-        <v>631.5919250424002</v>
+        <v>629.2715212945203</v>
       </c>
       <c r="P22">
-        <v>2526.367700169601</v>
+        <v>2517.086085178081</v>
       </c>
       <c r="Q22">
-        <v>5308.5677001696</v>
+        <v>5299.286085178081</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1204093120628641</v>
+        <v>0.1211963301225989</v>
       </c>
       <c r="T22">
-        <v>1.154182329007876</v>
+        <v>1.166357248090238</v>
       </c>
       <c r="U22">
         <v>0.06613097776675758</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.60952648045511</v>
+        <v>13.91383474329058</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1068551050616685</v>
+        <v>0.1068018040303644</v>
       </c>
       <c r="C23">
-        <v>13947.03501805695</v>
+        <v>13776.1761968372</v>
       </c>
       <c r="D23">
-        <v>13561.67501805695</v>
+        <v>13566.25619683721</v>
       </c>
       <c r="E23">
-        <v>-95.5600000000004</v>
+        <v>79.87999999999965</v>
       </c>
       <c r="F23">
-        <v>3684.24</v>
+        <v>3859.68</v>
       </c>
       <c r="G23">
         <v>4069.6</v>
@@ -3179,28 +3179,28 @@
         <v>3390</v>
       </c>
       <c r="M23">
-        <v>243.642393527399</v>
+        <v>255.2444122667989</v>
       </c>
       <c r="N23">
-        <v>3146.357606472601</v>
+        <v>3134.755587733201</v>
       </c>
       <c r="O23">
-        <v>629.2715212945203</v>
+        <v>626.9511175466403</v>
       </c>
       <c r="P23">
-        <v>2517.086085178081</v>
+        <v>2507.804470186561</v>
       </c>
       <c r="Q23">
-        <v>5299.286085178081</v>
+        <v>5290.004470186561</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1211963301225989</v>
+        <v>0.1220035281325834</v>
       </c>
       <c r="T23">
-        <v>1.166357248090238</v>
+        <v>1.178844344584967</v>
       </c>
       <c r="U23">
         <v>0.06613097776675758</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.91383474329058</v>
+        <v>13.28138770950465</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1068018040303644</v>
+        <v>0.1067485029990604</v>
       </c>
       <c r="C24">
-        <v>13776.1761968372</v>
+        <v>13605.3204717381</v>
       </c>
       <c r="D24">
-        <v>13566.25619683721</v>
+        <v>13570.8404717381</v>
       </c>
       <c r="E24">
-        <v>79.87999999999965</v>
+        <v>255.3200000000002</v>
       </c>
       <c r="F24">
-        <v>3859.68</v>
+        <v>4035.12</v>
       </c>
       <c r="G24">
         <v>4069.6</v>
@@ -3261,28 +3261,28 @@
         <v>3390</v>
       </c>
       <c r="M24">
-        <v>255.2444122667989</v>
+        <v>266.8464310061989</v>
       </c>
       <c r="N24">
-        <v>3134.755587733201</v>
+        <v>3123.153568993801</v>
       </c>
       <c r="O24">
-        <v>626.9511175466403</v>
+        <v>624.6307137987602</v>
       </c>
       <c r="P24">
-        <v>2507.804470186561</v>
+        <v>2498.522855195041</v>
       </c>
       <c r="Q24">
-        <v>5290.004470186561</v>
+        <v>5280.722855195041</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1220035281325834</v>
+        <v>0.1228316923246454</v>
       </c>
       <c r="T24">
-        <v>1.178844344584967</v>
+        <v>1.191655781248391</v>
       </c>
       <c r="U24">
         <v>0.06613097776675758</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.28138770950465</v>
+        <v>12.70393606996096</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1067485029990604</v>
+        <v>0.1066952019677563</v>
       </c>
       <c r="C25">
-        <v>13605.3204717381</v>
+        <v>13434.46784589939</v>
       </c>
       <c r="D25">
-        <v>13570.8404717381</v>
+        <v>13575.4278458994</v>
       </c>
       <c r="E25">
-        <v>255.3200000000002</v>
+        <v>430.7600000000002</v>
       </c>
       <c r="F25">
-        <v>4035.12</v>
+        <v>4210.56</v>
       </c>
       <c r="G25">
         <v>4069.6</v>
@@ -3343,28 +3343,28 @@
         <v>3390</v>
       </c>
       <c r="M25">
-        <v>266.8464310061989</v>
+        <v>278.4484497455989</v>
       </c>
       <c r="N25">
-        <v>3123.153568993801</v>
+        <v>3111.551550254401</v>
       </c>
       <c r="O25">
-        <v>624.6307137987602</v>
+        <v>622.3103100508803</v>
       </c>
       <c r="P25">
-        <v>2498.522855195041</v>
+        <v>2489.241240203521</v>
       </c>
       <c r="Q25">
-        <v>5280.722855195041</v>
+        <v>5271.441240203521</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1228316923246454</v>
+        <v>0.1236816503112353</v>
       </c>
       <c r="T25">
-        <v>1.191655781248391</v>
+        <v>1.204804360981906</v>
       </c>
       <c r="U25">
         <v>0.06613097776675758</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.70393606996096</v>
+        <v>12.17460540037926</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1066952019677563</v>
+        <v>0.1066419009364523</v>
       </c>
       <c r="C26">
-        <v>13434.4678458994</v>
+        <v>13263.6183224651</v>
       </c>
       <c r="D26">
-        <v>13575.4278458994</v>
+        <v>13580.0183224651</v>
       </c>
       <c r="E26">
-        <v>430.7599999999993</v>
+        <v>606.1999999999998</v>
       </c>
       <c r="F26">
-        <v>4210.559999999999</v>
+        <v>4386</v>
       </c>
       <c r="G26">
         <v>4069.6</v>
@@ -3425,28 +3425,28 @@
         <v>3390</v>
       </c>
       <c r="M26">
-        <v>278.4484497455988</v>
+        <v>290.0504684849988</v>
       </c>
       <c r="N26">
-        <v>3111.551550254401</v>
+        <v>3099.949531515001</v>
       </c>
       <c r="O26">
-        <v>622.3103100508803</v>
+        <v>619.9899063030002</v>
       </c>
       <c r="P26">
-        <v>2489.241240203521</v>
+        <v>2479.959625212001</v>
       </c>
       <c r="Q26">
-        <v>5271.441240203521</v>
+        <v>5262.159625212001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1236816503112353</v>
+        <v>0.1245542738441343</v>
       </c>
       <c r="T26">
-        <v>1.204804360981905</v>
+        <v>1.218303569508314</v>
       </c>
       <c r="U26">
         <v>0.06613097776675758</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.17460540037926</v>
+        <v>11.68762118436409</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1066419009364523</v>
+        <v>0.1065885999051482</v>
       </c>
       <c r="C27">
-        <v>13263.6183224651</v>
+        <v>13092.77190458347</v>
       </c>
       <c r="D27">
-        <v>13580.0183224651</v>
+        <v>13584.61190458347</v>
       </c>
       <c r="E27">
-        <v>606.1999999999998</v>
+        <v>781.6400000000003</v>
       </c>
       <c r="F27">
-        <v>4386</v>
+        <v>4561.440000000001</v>
       </c>
       <c r="G27">
         <v>4069.6</v>
@@ -3507,28 +3507,28 @@
         <v>3390</v>
       </c>
       <c r="M27">
-        <v>290.0504684849988</v>
+        <v>301.6524872243987</v>
       </c>
       <c r="N27">
-        <v>3099.949531515001</v>
+        <v>3088.347512775601</v>
       </c>
       <c r="O27">
-        <v>619.9899063030002</v>
+        <v>617.6695025551203</v>
       </c>
       <c r="P27">
-        <v>2479.959625212001</v>
+        <v>2470.678010220481</v>
       </c>
       <c r="Q27">
-        <v>5262.159625212001</v>
+        <v>5252.878010220481</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1245542738441343</v>
+        <v>0.1254504817968414</v>
       </c>
       <c r="T27">
-        <v>1.218303569508314</v>
+        <v>1.232167621508408</v>
       </c>
       <c r="U27">
         <v>0.06613097776675758</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.68762118436409</v>
+        <v>11.23809729265778</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1065885999051482</v>
+        <v>0.1065352988738442</v>
       </c>
       <c r="C28">
-        <v>13092.77190458347</v>
+        <v>12921.92859540703</v>
       </c>
       <c r="D28">
-        <v>13584.61190458347</v>
+        <v>13589.20859540703</v>
       </c>
       <c r="E28">
-        <v>781.6400000000003</v>
+        <v>957.0799999999999</v>
       </c>
       <c r="F28">
-        <v>4561.440000000001</v>
+        <v>4736.88</v>
       </c>
       <c r="G28">
         <v>4069.6</v>
@@ -3589,28 +3589,28 @@
         <v>3390</v>
       </c>
       <c r="M28">
-        <v>301.6524872243987</v>
+        <v>313.2545059637986</v>
       </c>
       <c r="N28">
-        <v>3088.347512775601</v>
+        <v>3076.745494036201</v>
       </c>
       <c r="O28">
-        <v>617.6695025551203</v>
+        <v>615.3490988072404</v>
       </c>
       <c r="P28">
-        <v>2470.678010220481</v>
+        <v>2461.396395228961</v>
       </c>
       <c r="Q28">
-        <v>5252.878010220481</v>
+        <v>5243.59639522896</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1254504817968414</v>
+        <v>0.1263712433920884</v>
       </c>
       <c r="T28">
-        <v>1.232167621508408</v>
+        <v>1.246411510549601</v>
       </c>
       <c r="U28">
         <v>0.06613097776675758</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.23809729265778</v>
+        <v>10.82187146700379</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1065352988738442</v>
+        <v>0.1064819978425401</v>
       </c>
       <c r="C29">
-        <v>12921.92859540703</v>
+        <v>12751.08839809258</v>
       </c>
       <c r="D29">
-        <v>13589.20859540703</v>
+        <v>13593.80839809257</v>
       </c>
       <c r="E29">
-        <v>957.0799999999999</v>
+        <v>1132.52</v>
       </c>
       <c r="F29">
-        <v>4736.88</v>
+        <v>4912.320000000001</v>
       </c>
       <c r="G29">
         <v>4069.6</v>
@@ -3671,28 +3671,28 @@
         <v>3390</v>
       </c>
       <c r="M29">
-        <v>313.2545059637986</v>
+        <v>324.8565247031987</v>
       </c>
       <c r="N29">
-        <v>3076.745494036201</v>
+        <v>3065.143475296801</v>
       </c>
       <c r="O29">
-        <v>615.3490988072404</v>
+        <v>613.0286950593603</v>
       </c>
       <c r="P29">
-        <v>2461.396395228961</v>
+        <v>2452.114780237441</v>
       </c>
       <c r="Q29">
-        <v>5243.59639522896</v>
+        <v>5234.314780237441</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1263712433920884</v>
+        <v>0.1273175816983145</v>
       </c>
       <c r="T29">
-        <v>1.246411510549601</v>
+        <v>1.261051063175272</v>
       </c>
       <c r="U29">
         <v>0.06613097776675758</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.82187146700379</v>
+        <v>10.43537605746793</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1064819978425401</v>
+        <v>0.1064286968112361</v>
       </c>
       <c r="C30">
-        <v>12751.08839809258</v>
+        <v>12580.25131580117</v>
       </c>
       <c r="D30">
-        <v>13593.80839809257</v>
+        <v>13598.41131580117</v>
       </c>
       <c r="E30">
-        <v>1132.52</v>
+        <v>1307.96</v>
       </c>
       <c r="F30">
-        <v>4912.320000000001</v>
+        <v>5087.76</v>
       </c>
       <c r="G30">
         <v>4069.6</v>
@@ -3753,28 +3753,28 @@
         <v>3390</v>
       </c>
       <c r="M30">
-        <v>324.8565247031987</v>
+        <v>336.4585434425986</v>
       </c>
       <c r="N30">
-        <v>3065.143475296801</v>
+        <v>3053.541456557401</v>
       </c>
       <c r="O30">
-        <v>613.0286950593603</v>
+        <v>610.7082913114804</v>
       </c>
       <c r="P30">
-        <v>2452.114780237441</v>
+        <v>2442.833165245921</v>
       </c>
       <c r="Q30">
-        <v>5234.314780237441</v>
+        <v>5225.033165245921</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1273175816983145</v>
+        <v>0.1282905774216173</v>
       </c>
       <c r="T30">
-        <v>1.261051063175272</v>
+        <v>1.276102997565046</v>
       </c>
       <c r="U30">
         <v>0.06613097776675758</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.43537605746793</v>
+        <v>10.07553550376215</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1064286968112361</v>
+        <v>0.106375395779932</v>
       </c>
       <c r="C31">
-        <v>12580.25131580117</v>
+        <v>12409.41735169815</v>
       </c>
       <c r="D31">
-        <v>13598.41131580117</v>
+        <v>13603.01735169815</v>
       </c>
       <c r="E31">
-        <v>1307.959999999999</v>
+        <v>1483.4</v>
       </c>
       <c r="F31">
-        <v>5087.759999999999</v>
+        <v>5263.2</v>
       </c>
       <c r="G31">
         <v>4069.6</v>
@@ -3835,28 +3835,28 @@
         <v>3390</v>
       </c>
       <c r="M31">
-        <v>336.4585434425985</v>
+        <v>348.0605621819985</v>
       </c>
       <c r="N31">
-        <v>3053.541456557401</v>
+        <v>3041.939437818001</v>
       </c>
       <c r="O31">
-        <v>610.7082913114804</v>
+        <v>608.3878875636003</v>
       </c>
       <c r="P31">
-        <v>2442.833165245921</v>
+        <v>2433.551550254401</v>
       </c>
       <c r="Q31">
-        <v>5225.033165245921</v>
+        <v>5215.751550254401</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1282905774216173</v>
+        <v>0.1292913730227289</v>
       </c>
       <c r="T31">
-        <v>1.276102997565046</v>
+        <v>1.2915849872231</v>
       </c>
       <c r="U31">
         <v>0.06613097776675758</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.07553550376215</v>
+        <v>9.739684320303407</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.106375395779932</v>
+        <v>0.106322094748628</v>
       </c>
       <c r="C32">
-        <v>12409.41735169815</v>
+        <v>12238.58650895318</v>
       </c>
       <c r="D32">
-        <v>13603.01735169815</v>
+        <v>13607.62650895318</v>
       </c>
       <c r="E32">
-        <v>1483.4</v>
+        <v>1658.84</v>
       </c>
       <c r="F32">
-        <v>5263.2</v>
+        <v>5438.64</v>
       </c>
       <c r="G32">
         <v>4069.6</v>
@@ -3917,28 +3917,28 @@
         <v>3390</v>
       </c>
       <c r="M32">
-        <v>348.0605621819985</v>
+        <v>359.6625809213985</v>
       </c>
       <c r="N32">
-        <v>3041.939437818001</v>
+        <v>3030.337419078602</v>
       </c>
       <c r="O32">
-        <v>608.3878875636003</v>
+        <v>606.0674838157204</v>
       </c>
       <c r="P32">
-        <v>2433.551550254401</v>
+        <v>2424.269935262882</v>
       </c>
       <c r="Q32">
-        <v>5215.751550254401</v>
+        <v>5206.469935262881</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1292913730227289</v>
+        <v>0.1303211771919886</v>
       </c>
       <c r="T32">
-        <v>1.2915849872231</v>
+        <v>1.307515730204575</v>
       </c>
       <c r="U32">
         <v>0.06613097776675758</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.739684320303407</v>
+        <v>9.425500955132328</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.106322094748628</v>
+        <v>0.1062687937173239</v>
       </c>
       <c r="C33">
-        <v>12238.58650895318</v>
+        <v>12067.75879074018</v>
       </c>
       <c r="D33">
-        <v>13607.62650895318</v>
+        <v>13612.23879074018</v>
       </c>
       <c r="E33">
-        <v>1658.84</v>
+        <v>1834.28</v>
       </c>
       <c r="F33">
-        <v>5438.64</v>
+        <v>5614.08</v>
       </c>
       <c r="G33">
         <v>4069.6</v>
@@ -3999,28 +3999,28 @@
         <v>3390</v>
       </c>
       <c r="M33">
-        <v>359.6625809213985</v>
+        <v>371.2645996607984</v>
       </c>
       <c r="N33">
-        <v>3030.337419078602</v>
+        <v>3018.735400339202</v>
       </c>
       <c r="O33">
-        <v>606.0674838157204</v>
+        <v>603.7470800678403</v>
       </c>
       <c r="P33">
-        <v>2424.269935262882</v>
+        <v>2414.988320271361</v>
       </c>
       <c r="Q33">
-        <v>5206.469935262881</v>
+        <v>5197.188320271362</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1303211771919886</v>
+        <v>0.1313812697191676</v>
       </c>
       <c r="T33">
-        <v>1.307515730204575</v>
+        <v>1.323915024450211</v>
       </c>
       <c r="U33">
         <v>0.06613097776675758</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.425500955132328</v>
+        <v>9.130954050284444</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1062687937173239</v>
+        <v>0.1062154926860199</v>
       </c>
       <c r="C34">
-        <v>12067.75879074018</v>
+        <v>11896.9342002374</v>
       </c>
       <c r="D34">
-        <v>13612.23879074018</v>
+        <v>13616.8542002374</v>
       </c>
       <c r="E34">
-        <v>1834.28</v>
+        <v>2009.72</v>
       </c>
       <c r="F34">
-        <v>5614.08</v>
+        <v>5789.52</v>
       </c>
       <c r="G34">
         <v>4069.6</v>
@@ -4081,28 +4081,28 @@
         <v>3390</v>
       </c>
       <c r="M34">
-        <v>371.2645996607984</v>
+        <v>382.8666184001984</v>
       </c>
       <c r="N34">
-        <v>3018.735400339202</v>
+        <v>3007.133381599801</v>
       </c>
       <c r="O34">
-        <v>603.7470800678403</v>
+        <v>601.4266763199603</v>
       </c>
       <c r="P34">
-        <v>2414.988320271361</v>
+        <v>2405.706705279841</v>
       </c>
       <c r="Q34">
-        <v>5197.188320271362</v>
+        <v>5187.906705279841</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1313812697191676</v>
+        <v>0.1324730067993969</v>
       </c>
       <c r="T34">
-        <v>1.323915024450211</v>
+        <v>1.340803849867358</v>
       </c>
       <c r="U34">
         <v>0.06613097776675758</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.130954050284444</v>
+        <v>8.854258473003096</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1062154926860199</v>
+        <v>0.1065701916547158</v>
       </c>
       <c r="C35">
-        <v>11896.9342002374</v>
+        <v>11690.83908393441</v>
       </c>
       <c r="D35">
-        <v>13616.8542002374</v>
+        <v>13586.19908393441</v>
       </c>
       <c r="E35">
-        <v>2009.72</v>
+        <v>2185.16</v>
       </c>
       <c r="F35">
-        <v>5789.52</v>
+        <v>5964.96</v>
       </c>
       <c r="G35">
         <v>4069.6</v>
@@ -4163,45 +4163,45 @@
         <v>3390</v>
       </c>
       <c r="M35">
-        <v>382.8666184001984</v>
+        <v>403.4160771395983</v>
       </c>
       <c r="N35">
-        <v>3007.133381599801</v>
+        <v>2986.583922860402</v>
       </c>
       <c r="O35">
-        <v>601.4266763199603</v>
+        <v>597.3167845720803</v>
       </c>
       <c r="P35">
-        <v>2405.706705279841</v>
+        <v>2389.267138288321</v>
       </c>
       <c r="Q35">
-        <v>5187.906705279841</v>
+        <v>5171.467138288321</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1324730067993969</v>
+        <v>0.1335978268214512</v>
       </c>
       <c r="T35">
-        <v>1.340803849867358</v>
+        <v>1.358204457872905</v>
       </c>
       <c r="U35">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>8.854258473003096</v>
+        <v>8.403234754639991</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1065701916547158</v>
+        <v>0.1065288906234118</v>
       </c>
       <c r="C36">
-        <v>11690.83908393441</v>
+        <v>11518.96145360641</v>
       </c>
       <c r="D36">
-        <v>13586.19908393441</v>
+        <v>13589.76145360641</v>
       </c>
       <c r="E36">
-        <v>2185.16</v>
+        <v>2360.6</v>
       </c>
       <c r="F36">
-        <v>5964.96</v>
+        <v>6140.400000000001</v>
       </c>
       <c r="G36">
         <v>4069.6</v>
@@ -4245,28 +4245,28 @@
         <v>3390</v>
       </c>
       <c r="M36">
-        <v>403.4160771395983</v>
+        <v>415.2812558789983</v>
       </c>
       <c r="N36">
-        <v>2986.583922860402</v>
+        <v>2974.718744121002</v>
       </c>
       <c r="O36">
-        <v>597.3167845720803</v>
+        <v>594.9437488242004</v>
       </c>
       <c r="P36">
-        <v>2389.267138288321</v>
+        <v>2379.774995296802</v>
       </c>
       <c r="Q36">
-        <v>5171.467138288321</v>
+        <v>5161.974995296801</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1335978268214512</v>
+        <v>0.134757256690338</v>
       </c>
       <c r="T36">
-        <v>1.358204457872905</v>
+        <v>1.376140469201698</v>
       </c>
       <c r="U36">
         <v>0.06763097776675758</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.403234754639991</v>
+        <v>8.163142333078847</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1065288906234118</v>
+        <v>0.1064875895921078</v>
       </c>
       <c r="C37">
-        <v>11518.96145360641</v>
+        <v>11347.08569191084</v>
       </c>
       <c r="D37">
-        <v>13589.76145360641</v>
+        <v>13593.32569191084</v>
       </c>
       <c r="E37">
-        <v>2360.6</v>
+        <v>2536.040000000001</v>
       </c>
       <c r="F37">
-        <v>6140.400000000001</v>
+        <v>6315.840000000001</v>
       </c>
       <c r="G37">
         <v>4069.6</v>
@@ -4327,28 +4327,28 @@
         <v>3390</v>
       </c>
       <c r="M37">
-        <v>415.2812558789983</v>
+        <v>427.1464346183983</v>
       </c>
       <c r="N37">
-        <v>2974.718744121002</v>
+        <v>2962.853565381602</v>
       </c>
       <c r="O37">
-        <v>594.9437488242004</v>
+        <v>592.5707130763203</v>
       </c>
       <c r="P37">
-        <v>2379.774995296802</v>
+        <v>2370.282852305281</v>
       </c>
       <c r="Q37">
-        <v>5161.974995296801</v>
+        <v>5152.482852305281</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.134757256690338</v>
+        <v>0.1359529187426275</v>
       </c>
       <c r="T37">
-        <v>1.376140469201698</v>
+        <v>1.394636980884517</v>
       </c>
       <c r="U37">
         <v>0.06763097776675758</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.163142333078847</v>
+        <v>7.936388379382212</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1064875895921077</v>
+        <v>0.1064462885608037</v>
       </c>
       <c r="C38">
-        <v>11347.08569191084</v>
+        <v>11175.21180031836</v>
       </c>
       <c r="D38">
-        <v>13593.32569191084</v>
+        <v>13596.89180031836</v>
       </c>
       <c r="E38">
-        <v>2536.04</v>
+        <v>2711.48</v>
       </c>
       <c r="F38">
-        <v>6315.84</v>
+        <v>6491.28</v>
       </c>
       <c r="G38">
         <v>4069.6</v>
@@ -4409,28 +4409,28 @@
         <v>3390</v>
       </c>
       <c r="M38">
-        <v>427.1464346183982</v>
+        <v>439.0116133577981</v>
       </c>
       <c r="N38">
-        <v>2962.853565381602</v>
+        <v>2950.988386642202</v>
       </c>
       <c r="O38">
-        <v>592.5707130763203</v>
+        <v>590.1976773284404</v>
       </c>
       <c r="P38">
-        <v>2370.282852305281</v>
+        <v>2360.790709313761</v>
       </c>
       <c r="Q38">
-        <v>5152.482852305281</v>
+        <v>5142.990709313761</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1359529187426274</v>
+        <v>0.1371865383203865</v>
       </c>
       <c r="T38">
-        <v>1.394636980884517</v>
+        <v>1.413720683414409</v>
       </c>
       <c r="U38">
         <v>0.06763097776675758</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.936388379382213</v>
+        <v>7.721891396155668</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1064462885608037</v>
+        <v>0.1064049875294997</v>
       </c>
       <c r="C39">
-        <v>11175.21180031836</v>
+        <v>11003.33978030117</v>
       </c>
       <c r="D39">
-        <v>13596.89180031836</v>
+        <v>13600.45978030117</v>
       </c>
       <c r="E39">
-        <v>2711.48</v>
+        <v>2886.92</v>
       </c>
       <c r="F39">
-        <v>6491.28</v>
+        <v>6666.72</v>
       </c>
       <c r="G39">
         <v>4069.6</v>
@@ -4491,28 +4491,28 @@
         <v>3390</v>
       </c>
       <c r="M39">
-        <v>439.0116133577981</v>
+        <v>450.8767920971981</v>
       </c>
       <c r="N39">
-        <v>2950.988386642202</v>
+        <v>2939.123207902802</v>
       </c>
       <c r="O39">
-        <v>590.1976773284404</v>
+        <v>587.8246415805604</v>
       </c>
       <c r="P39">
-        <v>2360.790709313761</v>
+        <v>2351.298566322242</v>
       </c>
       <c r="Q39">
-        <v>5142.990709313761</v>
+        <v>5133.498566322241</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1371865383203865</v>
+        <v>0.1384599520780732</v>
       </c>
       <c r="T39">
-        <v>1.413720683414409</v>
+        <v>1.433419989251717</v>
       </c>
       <c r="U39">
         <v>0.06763097776675758</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.721891396155668</v>
+        <v>7.518683727835781</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1064049875294997</v>
+        <v>0.1063636864981956</v>
       </c>
       <c r="C40">
-        <v>11003.33978030117</v>
+        <v>10831.46963333304</v>
       </c>
       <c r="D40">
-        <v>13600.45978030117</v>
+        <v>13604.02963333304</v>
       </c>
       <c r="E40">
-        <v>2886.92</v>
+        <v>3062.36</v>
       </c>
       <c r="F40">
-        <v>6666.72</v>
+        <v>6842.16</v>
       </c>
       <c r="G40">
         <v>4069.6</v>
@@ -4573,28 +4573,28 @@
         <v>3390</v>
       </c>
       <c r="M40">
-        <v>450.8767920971981</v>
+        <v>462.7419708365981</v>
       </c>
       <c r="N40">
-        <v>2939.123207902802</v>
+        <v>2927.258029163402</v>
       </c>
       <c r="O40">
-        <v>587.8246415805604</v>
+        <v>585.4516058326805</v>
       </c>
       <c r="P40">
-        <v>2351.298566322242</v>
+        <v>2341.806423330722</v>
       </c>
       <c r="Q40">
-        <v>5133.498566322241</v>
+        <v>5124.006423330722</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1384599520780732</v>
+        <v>0.1397751171065037</v>
       </c>
       <c r="T40">
-        <v>1.433419989251717</v>
+        <v>1.453765173968937</v>
       </c>
       <c r="U40">
         <v>0.06763097776675758</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.518683727835781</v>
+        <v>7.325896965583582</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1063636864981956</v>
+        <v>0.1063223854668916</v>
       </c>
       <c r="C41">
-        <v>10831.46963333304</v>
+        <v>10659.60136088927</v>
       </c>
       <c r="D41">
-        <v>13604.02963333304</v>
+        <v>13607.60136088927</v>
       </c>
       <c r="E41">
-        <v>3062.36</v>
+        <v>3237.8</v>
       </c>
       <c r="F41">
-        <v>6842.16</v>
+        <v>7017.6</v>
       </c>
       <c r="G41">
         <v>4069.6</v>
@@ -4655,28 +4655,28 @@
         <v>3390</v>
       </c>
       <c r="M41">
-        <v>462.7419708365981</v>
+        <v>474.6071495759981</v>
       </c>
       <c r="N41">
-        <v>2927.258029163402</v>
+        <v>2915.392850424002</v>
       </c>
       <c r="O41">
-        <v>585.4516058326805</v>
+        <v>583.0785700848004</v>
       </c>
       <c r="P41">
-        <v>2341.806423330722</v>
+        <v>2332.314280339202</v>
       </c>
       <c r="Q41">
-        <v>5124.006423330722</v>
+        <v>5114.514280339201</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1397751171065037</v>
+        <v>0.1411341209692153</v>
       </c>
       <c r="T41">
-        <v>1.453765173968937</v>
+        <v>1.474788531510064</v>
       </c>
       <c r="U41">
         <v>0.06763097776675758</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.325896965583582</v>
+        <v>7.142749541443992</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1063223854668916</v>
+        <v>0.1062810844355875</v>
       </c>
       <c r="C42">
-        <v>10659.60136088927</v>
+        <v>10487.7349644467</v>
       </c>
       <c r="D42">
-        <v>13607.60136088927</v>
+        <v>13611.1749644467</v>
       </c>
       <c r="E42">
-        <v>3237.8</v>
+        <v>3413.240000000001</v>
       </c>
       <c r="F42">
-        <v>7017.6</v>
+        <v>7193.040000000001</v>
       </c>
       <c r="G42">
         <v>4069.6</v>
@@ -4737,28 +4737,28 @@
         <v>3390</v>
       </c>
       <c r="M42">
-        <v>474.6071495759981</v>
+        <v>486.472328315398</v>
       </c>
       <c r="N42">
-        <v>2915.392850424002</v>
+        <v>2903.527671684602</v>
       </c>
       <c r="O42">
-        <v>583.0785700848004</v>
+        <v>580.7055343369204</v>
       </c>
       <c r="P42">
-        <v>2332.314280339202</v>
+        <v>2322.822137347682</v>
       </c>
       <c r="Q42">
-        <v>5114.514280339201</v>
+        <v>5105.022137347682</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1411341209692153</v>
+        <v>0.1425391927594763</v>
       </c>
       <c r="T42">
-        <v>1.474788531510064</v>
+        <v>1.496524545239026</v>
       </c>
       <c r="U42">
         <v>0.06763097776675758</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.142749541443992</v>
+        <v>6.968536137994137</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1062810844355875</v>
+        <v>0.1062397834042835</v>
       </c>
       <c r="C43">
-        <v>10487.7349644467</v>
+        <v>10315.87044548375</v>
       </c>
       <c r="D43">
-        <v>13611.1749644467</v>
+        <v>13614.75044548375</v>
       </c>
       <c r="E43">
-        <v>3413.240000000001</v>
+        <v>3588.68</v>
       </c>
       <c r="F43">
-        <v>7193.040000000001</v>
+        <v>7368.48</v>
       </c>
       <c r="G43">
         <v>4069.6</v>
@@ -4819,28 +4819,28 @@
         <v>3390</v>
       </c>
       <c r="M43">
-        <v>486.472328315398</v>
+        <v>498.3375070547979</v>
       </c>
       <c r="N43">
-        <v>2903.527671684602</v>
+        <v>2891.662492945202</v>
       </c>
       <c r="O43">
-        <v>580.7055343369204</v>
+        <v>578.3324985890404</v>
       </c>
       <c r="P43">
-        <v>2322.822137347682</v>
+        <v>2313.329994356161</v>
       </c>
       <c r="Q43">
-        <v>5105.022137347682</v>
+        <v>5095.529994356161</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1425391927594763</v>
+        <v>0.1439927153011258</v>
       </c>
       <c r="T43">
-        <v>1.496524545239026</v>
+        <v>1.51901007668278</v>
       </c>
       <c r="U43">
         <v>0.06763097776675758</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.968536137994137</v>
+        <v>6.80261861089904</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1062397834042835</v>
+        <v>0.1067832823729794</v>
       </c>
       <c r="C44">
-        <v>10315.87044548375</v>
+        <v>10093.52884240778</v>
       </c>
       <c r="D44">
-        <v>13614.75044548375</v>
+        <v>13567.84884240778</v>
       </c>
       <c r="E44">
-        <v>3588.679999999999</v>
+        <v>3764.12</v>
       </c>
       <c r="F44">
-        <v>7368.48</v>
+        <v>7543.92</v>
       </c>
       <c r="G44">
         <v>4069.6</v>
@@ -4901,45 +4901,45 @@
         <v>3390</v>
       </c>
       <c r="M44">
-        <v>498.3375070547979</v>
+        <v>523.0273497941978</v>
       </c>
       <c r="N44">
-        <v>2891.662492945202</v>
+        <v>2866.972650205802</v>
       </c>
       <c r="O44">
-        <v>578.3324985890405</v>
+        <v>573.3945300411605</v>
       </c>
       <c r="P44">
-        <v>2313.329994356162</v>
+        <v>2293.578120164641</v>
       </c>
       <c r="Q44">
-        <v>5095.529994356162</v>
+        <v>5075.778120164641</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1439927153011257</v>
+        <v>0.1454972386337102</v>
       </c>
       <c r="T44">
-        <v>1.519010076682779</v>
+        <v>1.542284574142103</v>
       </c>
       <c r="U44">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.802618610899041</v>
+        <v>6.481496620270252</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1067832823729794</v>
+        <v>0.1067555813416754</v>
       </c>
       <c r="C45">
-        <v>10093.52884240778</v>
+        <v>9920.471504592118</v>
       </c>
       <c r="D45">
-        <v>13567.84884240778</v>
+        <v>13570.23150459212</v>
       </c>
       <c r="E45">
-        <v>3764.12</v>
+        <v>3939.559999999999</v>
       </c>
       <c r="F45">
-        <v>7543.92</v>
+        <v>7719.36</v>
       </c>
       <c r="G45">
         <v>4069.6</v>
@@ -4983,28 +4983,28 @@
         <v>3390</v>
       </c>
       <c r="M45">
-        <v>523.0273497941978</v>
+        <v>535.1907765335977</v>
       </c>
       <c r="N45">
-        <v>2866.972650205802</v>
+        <v>2854.809223466402</v>
       </c>
       <c r="O45">
-        <v>573.3945300411605</v>
+        <v>570.9618446932805</v>
       </c>
       <c r="P45">
-        <v>2293.578120164641</v>
+        <v>2283.847378773122</v>
       </c>
       <c r="Q45">
-        <v>5075.778120164641</v>
+        <v>5066.047378773122</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1454972386337102</v>
+        <v>0.1470554949424584</v>
       </c>
       <c r="T45">
-        <v>1.542284574142103</v>
+        <v>1.566390303653546</v>
       </c>
       <c r="U45">
         <v>0.06933097776675758</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.481496620270252</v>
+        <v>6.334189878900474</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1067555813416754</v>
+        <v>0.1067278803103713</v>
       </c>
       <c r="C46">
-        <v>9920.471504592118</v>
+        <v>9747.415003766357</v>
       </c>
       <c r="D46">
-        <v>13570.23150459212</v>
+        <v>13572.61500376636</v>
       </c>
       <c r="E46">
-        <v>3939.559999999999</v>
+        <v>4115</v>
       </c>
       <c r="F46">
-        <v>7719.36</v>
+        <v>7894.8</v>
       </c>
       <c r="G46">
         <v>4069.6</v>
@@ -5065,28 +5065,28 @@
         <v>3390</v>
       </c>
       <c r="M46">
-        <v>535.1907765335977</v>
+        <v>547.3542032729978</v>
       </c>
       <c r="N46">
-        <v>2854.809223466402</v>
+        <v>2842.645796727002</v>
       </c>
       <c r="O46">
-        <v>570.9618446932805</v>
+        <v>568.5291593454004</v>
       </c>
       <c r="P46">
-        <v>2283.847378773122</v>
+        <v>2274.116637381602</v>
       </c>
       <c r="Q46">
-        <v>5066.047378773122</v>
+        <v>5056.316637381602</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1470554949424584</v>
+        <v>0.1486704151169793</v>
       </c>
       <c r="T46">
-        <v>1.566390303653546</v>
+        <v>1.591372605147223</v>
       </c>
       <c r="U46">
         <v>0.06933097776675758</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.334189878900474</v>
+        <v>6.193430103813795</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1067278803103713</v>
+        <v>0.1067001792790673</v>
       </c>
       <c r="C47">
-        <v>9747.415003766357</v>
+        <v>9574.359340371593</v>
       </c>
       <c r="D47">
-        <v>13572.61500376636</v>
+        <v>13574.9993403716</v>
       </c>
       <c r="E47">
-        <v>4115</v>
+        <v>4290.440000000001</v>
       </c>
       <c r="F47">
-        <v>7894.8</v>
+        <v>8070.240000000001</v>
       </c>
       <c r="G47">
         <v>4069.6</v>
@@ -5147,28 +5147,28 @@
         <v>3390</v>
       </c>
       <c r="M47">
-        <v>547.3542032729978</v>
+        <v>559.5176300123977</v>
       </c>
       <c r="N47">
-        <v>2842.645796727002</v>
+        <v>2830.482369987602</v>
       </c>
       <c r="O47">
-        <v>568.5291593454004</v>
+        <v>566.0964739975205</v>
       </c>
       <c r="P47">
-        <v>2274.116637381602</v>
+        <v>2264.385895990082</v>
       </c>
       <c r="Q47">
-        <v>5056.316637381602</v>
+        <v>5046.585895990082</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1486704151169793</v>
+        <v>0.1503451471498158</v>
       </c>
       <c r="T47">
-        <v>1.591372605147223</v>
+        <v>1.617280177066592</v>
       </c>
       <c r="U47">
         <v>0.06933097776675758</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.193430103813795</v>
+        <v>6.058790318948279</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1067001792790673</v>
+        <v>0.1066724782477633</v>
       </c>
       <c r="C48">
-        <v>9574.359340371593</v>
+        <v>9401.304514849264</v>
       </c>
       <c r="D48">
-        <v>13574.9993403716</v>
+        <v>13577.38451484927</v>
       </c>
       <c r="E48">
-        <v>4290.440000000001</v>
+        <v>4465.88</v>
       </c>
       <c r="F48">
-        <v>8070.240000000001</v>
+        <v>8245.68</v>
       </c>
       <c r="G48">
         <v>4069.6</v>
@@ -5229,28 +5229,28 @@
         <v>3390</v>
       </c>
       <c r="M48">
-        <v>559.5176300123977</v>
+        <v>571.6810567517977</v>
       </c>
       <c r="N48">
-        <v>2830.482369987602</v>
+        <v>2818.318943248202</v>
       </c>
       <c r="O48">
-        <v>566.0964739975205</v>
+        <v>563.6637886496404</v>
       </c>
       <c r="P48">
-        <v>2264.385895990082</v>
+        <v>2254.655154598562</v>
       </c>
       <c r="Q48">
-        <v>5046.585895990082</v>
+        <v>5036.855154598561</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1503451471498158</v>
+        <v>0.1520830766178536</v>
       </c>
       <c r="T48">
-        <v>1.617280177066592</v>
+        <v>1.644165393209333</v>
       </c>
       <c r="U48">
         <v>0.06933097776675758</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.058790318948279</v>
+        <v>5.92987988663023</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1066724782477633</v>
+        <v>0.1066447772164592</v>
       </c>
       <c r="C49">
-        <v>9401.304514849264</v>
+        <v>9228.250527641087</v>
       </c>
       <c r="D49">
-        <v>13577.38451484927</v>
+        <v>13579.77052764109</v>
       </c>
       <c r="E49">
-        <v>4465.88</v>
+        <v>4641.320000000001</v>
       </c>
       <c r="F49">
-        <v>8245.68</v>
+        <v>8421.120000000001</v>
       </c>
       <c r="G49">
         <v>4069.6</v>
@@ -5311,28 +5311,28 @@
         <v>3390</v>
       </c>
       <c r="M49">
-        <v>571.6810567517977</v>
+        <v>583.8444834911976</v>
       </c>
       <c r="N49">
-        <v>2818.318943248202</v>
+        <v>2806.155516508803</v>
       </c>
       <c r="O49">
-        <v>563.6637886496404</v>
+        <v>561.2311033017605</v>
       </c>
       <c r="P49">
-        <v>2254.655154598562</v>
+        <v>2244.924413207042</v>
       </c>
       <c r="Q49">
-        <v>5036.855154598561</v>
+        <v>5027.124413207042</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1520830766178536</v>
+        <v>0.1538878495269698</v>
       </c>
       <c r="T49">
-        <v>1.644165393209333</v>
+        <v>1.672084656126795</v>
       </c>
       <c r="U49">
         <v>0.06933097776675758</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.92987988663023</v>
+        <v>5.806340722325434</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1066447772164592</v>
+        <v>0.1066170761851552</v>
       </c>
       <c r="C50">
-        <v>9228.250527641088</v>
+        <v>9055.197379189109</v>
       </c>
       <c r="D50">
-        <v>13579.77052764109</v>
+        <v>13582.15737918911</v>
       </c>
       <c r="E50">
-        <v>4641.319999999999</v>
+        <v>4816.759999999999</v>
       </c>
       <c r="F50">
-        <v>8421.119999999999</v>
+        <v>8596.559999999999</v>
       </c>
       <c r="G50">
         <v>4069.6</v>
@@ -5393,28 +5393,28 @@
         <v>3390</v>
       </c>
       <c r="M50">
-        <v>583.8444834911975</v>
+        <v>596.0079102305974</v>
       </c>
       <c r="N50">
-        <v>2806.155516508803</v>
+        <v>2793.992089769403</v>
       </c>
       <c r="O50">
-        <v>561.2311033017605</v>
+        <v>558.7984179538806</v>
       </c>
       <c r="P50">
-        <v>2244.924413207042</v>
+        <v>2235.193671815522</v>
       </c>
       <c r="Q50">
-        <v>5027.124413207042</v>
+        <v>5017.393671815522</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1538878495269698</v>
+        <v>0.1557633978442866</v>
       </c>
       <c r="T50">
-        <v>1.672084656126795</v>
+        <v>1.701098792099843</v>
       </c>
       <c r="U50">
         <v>0.06933097776675758</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.806340722325435</v>
+        <v>5.687843972890223</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1066170761851552</v>
+        <v>0.1065893751538511</v>
       </c>
       <c r="C51">
-        <v>9055.197379189109</v>
+        <v>8882.145069935668</v>
       </c>
       <c r="D51">
-        <v>13582.15737918911</v>
+        <v>13584.54506993567</v>
       </c>
       <c r="E51">
-        <v>4816.759999999999</v>
+        <v>4992.2</v>
       </c>
       <c r="F51">
-        <v>8596.559999999999</v>
+        <v>8772</v>
       </c>
       <c r="G51">
         <v>4069.6</v>
@@ -5475,28 +5475,28 @@
         <v>3390</v>
       </c>
       <c r="M51">
-        <v>596.0079102305974</v>
+        <v>608.1713369699975</v>
       </c>
       <c r="N51">
-        <v>2793.992089769403</v>
+        <v>2781.828663030003</v>
       </c>
       <c r="O51">
-        <v>558.7984179538806</v>
+        <v>556.3657326060005</v>
       </c>
       <c r="P51">
-        <v>2235.193671815522</v>
+        <v>2225.462930424002</v>
       </c>
       <c r="Q51">
-        <v>5017.393671815522</v>
+        <v>5007.662930424001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1557633978442866</v>
+        <v>0.1577139680942962</v>
       </c>
       <c r="T51">
-        <v>1.701098792099843</v>
+        <v>1.731273493511814</v>
       </c>
       <c r="U51">
         <v>0.06933097776675758</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.687843972890223</v>
+        <v>5.574087093432417</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1065893751538511</v>
+        <v>0.1068880741225471</v>
       </c>
       <c r="C52">
-        <v>8882.145069935668</v>
+        <v>8681.002903480347</v>
       </c>
       <c r="D52">
-        <v>13584.54506993567</v>
+        <v>13558.84290348035</v>
       </c>
       <c r="E52">
-        <v>4992.2</v>
+        <v>5167.64</v>
       </c>
       <c r="F52">
-        <v>8772</v>
+        <v>8947.440000000001</v>
       </c>
       <c r="G52">
         <v>4069.6</v>
@@ -5557,45 +5557,45 @@
         <v>3390</v>
       </c>
       <c r="M52">
-        <v>608.1713369699975</v>
+        <v>627.4927157093975</v>
       </c>
       <c r="N52">
-        <v>2781.828663030003</v>
+        <v>2762.507284290602</v>
       </c>
       <c r="O52">
-        <v>556.3657326060005</v>
+        <v>552.5014568581205</v>
       </c>
       <c r="P52">
-        <v>2225.462930424002</v>
+        <v>2210.005827432482</v>
       </c>
       <c r="Q52">
-        <v>5007.662930424001</v>
+        <v>4992.205827432482</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1577139680942962</v>
+        <v>0.159744153456551</v>
       </c>
       <c r="T52">
-        <v>1.731273493511814</v>
+        <v>1.76267981538958</v>
       </c>
       <c r="U52">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>5.574087093432417</v>
+        <v>5.402453152252952</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1068880741225471</v>
+        <v>0.106866773091243</v>
       </c>
       <c r="C53">
-        <v>8681.002903480347</v>
+        <v>8507.392573493064</v>
       </c>
       <c r="D53">
-        <v>13558.84290348035</v>
+        <v>13560.67257349306</v>
       </c>
       <c r="E53">
-        <v>5167.64</v>
+        <v>5343.080000000001</v>
       </c>
       <c r="F53">
-        <v>8947.440000000001</v>
+        <v>9122.880000000001</v>
       </c>
       <c r="G53">
         <v>4069.6</v>
@@ -5639,28 +5639,28 @@
         <v>3390</v>
       </c>
       <c r="M53">
-        <v>627.4927157093975</v>
+        <v>639.7964944487975</v>
       </c>
       <c r="N53">
-        <v>2762.507284290602</v>
+        <v>2750.203505551202</v>
       </c>
       <c r="O53">
-        <v>552.5014568581205</v>
+        <v>550.0407011102405</v>
       </c>
       <c r="P53">
-        <v>2210.005827432482</v>
+        <v>2200.162804440962</v>
       </c>
       <c r="Q53">
-        <v>4992.205827432482</v>
+        <v>4982.362804440962</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.159744153456551</v>
+        <v>0.1618589298755664</v>
       </c>
       <c r="T53">
-        <v>1.76267981538958</v>
+        <v>1.795394734012252</v>
       </c>
       <c r="U53">
         <v>0.07013097776675759</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.402453152252952</v>
+        <v>5.298559822401933</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.106866773091243</v>
+        <v>0.106845472059939</v>
       </c>
       <c r="C54">
-        <v>8507.392573493064</v>
+        <v>8333.782737374502</v>
       </c>
       <c r="D54">
-        <v>13560.67257349306</v>
+        <v>13562.5027373745</v>
       </c>
       <c r="E54">
-        <v>5343.080000000001</v>
+        <v>5518.52</v>
       </c>
       <c r="F54">
-        <v>9122.880000000001</v>
+        <v>9298.32</v>
       </c>
       <c r="G54">
         <v>4069.6</v>
@@ -5721,28 +5721,28 @@
         <v>3390</v>
       </c>
       <c r="M54">
-        <v>639.7964944487975</v>
+        <v>652.1002731881973</v>
       </c>
       <c r="N54">
-        <v>2750.203505551202</v>
+        <v>2737.899726811803</v>
       </c>
       <c r="O54">
-        <v>550.0407011102405</v>
+        <v>547.5799453623606</v>
       </c>
       <c r="P54">
-        <v>2200.162804440962</v>
+        <v>2190.319781449442</v>
       </c>
       <c r="Q54">
-        <v>4982.362804440962</v>
+        <v>4972.519781449442</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1618589298755664</v>
+        <v>0.1640636967804974</v>
       </c>
       <c r="T54">
-        <v>1.795394734012252</v>
+        <v>1.829501776831634</v>
       </c>
       <c r="U54">
         <v>0.07013097776675759</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.298559822401933</v>
+        <v>5.198586995564162</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.106845472059939</v>
+        <v>0.1068241710286349</v>
       </c>
       <c r="C55">
-        <v>8333.782737374502</v>
+        <v>8160.173395324635</v>
       </c>
       <c r="D55">
-        <v>13562.5027373745</v>
+        <v>13564.33339532464</v>
       </c>
       <c r="E55">
-        <v>5518.52</v>
+        <v>5693.96</v>
       </c>
       <c r="F55">
-        <v>9298.32</v>
+        <v>9473.76</v>
       </c>
       <c r="G55">
         <v>4069.6</v>
@@ -5803,28 +5803,28 @@
         <v>3390</v>
       </c>
       <c r="M55">
-        <v>652.1002731881973</v>
+        <v>664.4040519275974</v>
       </c>
       <c r="N55">
-        <v>2737.899726811803</v>
+        <v>2725.595948072403</v>
       </c>
       <c r="O55">
-        <v>547.5799453623606</v>
+        <v>545.1191896144805</v>
       </c>
       <c r="P55">
-        <v>2190.319781449442</v>
+        <v>2180.476758457922</v>
       </c>
       <c r="Q55">
-        <v>4972.519781449442</v>
+        <v>4962.676758457922</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1640636967804974</v>
+        <v>0.1663643231160775</v>
       </c>
       <c r="T55">
-        <v>1.829501776831634</v>
+        <v>1.865091734556205</v>
       </c>
       <c r="U55">
         <v>0.07013097776675759</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.198586995564162</v>
+        <v>5.102316866016677</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1068241710286349</v>
+        <v>0.1068028699973309</v>
       </c>
       <c r="C56">
-        <v>8160.173395324635</v>
+        <v>7986.564547543567</v>
       </c>
       <c r="D56">
-        <v>13564.33339532464</v>
+        <v>13566.16454754357</v>
       </c>
       <c r="E56">
-        <v>5693.96</v>
+        <v>5869.400000000001</v>
       </c>
       <c r="F56">
-        <v>9473.76</v>
+        <v>9649.200000000001</v>
       </c>
       <c r="G56">
         <v>4069.6</v>
@@ -5885,28 +5885,28 @@
         <v>3390</v>
       </c>
       <c r="M56">
-        <v>664.4040519275974</v>
+        <v>676.7078306669973</v>
       </c>
       <c r="N56">
-        <v>2725.595948072403</v>
+        <v>2713.292169333003</v>
       </c>
       <c r="O56">
-        <v>545.1191896144805</v>
+        <v>542.6584338666006</v>
       </c>
       <c r="P56">
-        <v>2180.476758457922</v>
+        <v>2170.633735466402</v>
       </c>
       <c r="Q56">
-        <v>4962.676758457922</v>
+        <v>4952.833735466402</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1663643231160775</v>
+        <v>0.1687671995110168</v>
       </c>
       <c r="T56">
-        <v>1.865091734556205</v>
+        <v>1.902263468179648</v>
       </c>
       <c r="U56">
         <v>0.07013097776675759</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.102316866016677</v>
+        <v>5.009547468452737</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1068028699973309</v>
+        <v>0.1067815689660268</v>
       </c>
       <c r="C57">
-        <v>7986.564547543567</v>
+        <v>7812.956194231492</v>
       </c>
       <c r="D57">
-        <v>13566.16454754357</v>
+        <v>13567.99619423149</v>
       </c>
       <c r="E57">
-        <v>5869.400000000001</v>
+        <v>6044.840000000001</v>
       </c>
       <c r="F57">
-        <v>9649.200000000001</v>
+        <v>9824.640000000001</v>
       </c>
       <c r="G57">
         <v>4069.6</v>
@@ -5967,28 +5967,28 @@
         <v>3390</v>
       </c>
       <c r="M57">
-        <v>676.7078306669973</v>
+        <v>689.0116094063974</v>
       </c>
       <c r="N57">
-        <v>2713.292169333003</v>
+        <v>2700.988390593603</v>
       </c>
       <c r="O57">
-        <v>542.6584338666006</v>
+        <v>540.1976781187205</v>
       </c>
       <c r="P57">
-        <v>2170.633735466402</v>
+        <v>2160.790712474882</v>
       </c>
       <c r="Q57">
-        <v>4952.833735466402</v>
+        <v>4942.990712474882</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1687671995110168</v>
+        <v>0.1712792975602715</v>
       </c>
       <c r="T57">
-        <v>1.902263468179648</v>
+        <v>1.941124826058701</v>
       </c>
       <c r="U57">
         <v>0.07013097776675759</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.009547468452737</v>
+        <v>4.920091263658938</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1067815689660268</v>
+        <v>0.1067602679347228</v>
       </c>
       <c r="C58">
-        <v>7812.956194231492</v>
+        <v>7639.348335588733</v>
       </c>
       <c r="D58">
-        <v>13567.99619423149</v>
+        <v>13569.82833558874</v>
       </c>
       <c r="E58">
-        <v>6044.840000000001</v>
+        <v>6220.280000000002</v>
       </c>
       <c r="F58">
-        <v>9824.640000000001</v>
+        <v>10000.08</v>
       </c>
       <c r="G58">
         <v>4069.6</v>
@@ -6049,28 +6049,28 @@
         <v>3390</v>
       </c>
       <c r="M58">
-        <v>689.0116094063974</v>
+        <v>701.3153881457973</v>
       </c>
       <c r="N58">
-        <v>2700.988390593603</v>
+        <v>2688.684611854203</v>
       </c>
       <c r="O58">
-        <v>540.1976781187205</v>
+        <v>537.7369223708405</v>
       </c>
       <c r="P58">
-        <v>2160.790712474882</v>
+        <v>2150.947689483362</v>
       </c>
       <c r="Q58">
-        <v>4942.990712474882</v>
+        <v>4933.147689483361</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1712792975602715</v>
+        <v>0.173908237379259</v>
       </c>
       <c r="T58">
-        <v>1.941124826058701</v>
+        <v>1.981793688955384</v>
       </c>
       <c r="U58">
         <v>0.07013097776675759</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.920091263658938</v>
+        <v>4.83377387306843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1067602679347228</v>
+        <v>0.1067389669034187</v>
       </c>
       <c r="C59">
-        <v>7639.348335588733</v>
+        <v>7465.7409718157</v>
       </c>
       <c r="D59">
-        <v>13569.82833558874</v>
+        <v>13571.6609718157</v>
       </c>
       <c r="E59">
-        <v>6220.280000000002</v>
+        <v>6395.72</v>
       </c>
       <c r="F59">
-        <v>10000.08</v>
+        <v>10175.52</v>
       </c>
       <c r="G59">
         <v>4069.6</v>
@@ -6131,28 +6131,28 @@
         <v>3390</v>
       </c>
       <c r="M59">
-        <v>701.3153881457973</v>
+        <v>713.6191668851972</v>
       </c>
       <c r="N59">
-        <v>2688.684611854203</v>
+        <v>2676.380833114803</v>
       </c>
       <c r="O59">
-        <v>537.7369223708405</v>
+        <v>535.2761666229607</v>
       </c>
       <c r="P59">
-        <v>2150.947689483362</v>
+        <v>2141.104666491842</v>
       </c>
       <c r="Q59">
-        <v>4933.147689483361</v>
+        <v>4923.304666491842</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.173908237379259</v>
+        <v>0.1766623648086744</v>
       </c>
       <c r="T59">
-        <v>1.981793688955384</v>
+        <v>2.024399164370958</v>
       </c>
       <c r="U59">
         <v>0.07013097776675759</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.83377387306843</v>
+        <v>4.750432944222423</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067389669034187</v>
+        <v>0.1067176658721147</v>
       </c>
       <c r="C60">
-        <v>7465.740971815701</v>
+        <v>7292.134103112916</v>
       </c>
       <c r="D60">
-        <v>13571.6609718157</v>
+        <v>13573.49410311292</v>
       </c>
       <c r="E60">
-        <v>6395.719999999998</v>
+        <v>6571.159999999999</v>
       </c>
       <c r="F60">
-        <v>10175.52</v>
+        <v>10350.96</v>
       </c>
       <c r="G60">
         <v>4069.6</v>
@@ -6213,28 +6213,28 @@
         <v>3390</v>
       </c>
       <c r="M60">
-        <v>713.619166885197</v>
+        <v>725.922945624597</v>
       </c>
       <c r="N60">
-        <v>2676.380833114803</v>
+        <v>2664.077054375403</v>
       </c>
       <c r="O60">
-        <v>535.2761666229607</v>
+        <v>532.8154108750806</v>
       </c>
       <c r="P60">
-        <v>2141.104666491842</v>
+        <v>2131.261643500322</v>
       </c>
       <c r="Q60">
-        <v>4923.304666491842</v>
+        <v>4913.461643500323</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1766623648086743</v>
+        <v>0.1795508399175735</v>
       </c>
       <c r="T60">
-        <v>2.024399164370957</v>
+        <v>2.069082955660461</v>
       </c>
       <c r="U60">
         <v>0.07013097776675759</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.750432944222425</v>
+        <v>4.669917131608484</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1067176658721147</v>
+        <v>0.1066963648408107</v>
       </c>
       <c r="C61">
-        <v>7292.134103112916</v>
+        <v>7118.527729681029</v>
       </c>
       <c r="D61">
-        <v>13573.49410311292</v>
+        <v>13575.32772968103</v>
       </c>
       <c r="E61">
-        <v>6571.159999999999</v>
+        <v>6746.599999999999</v>
       </c>
       <c r="F61">
-        <v>10350.96</v>
+        <v>10526.4</v>
       </c>
       <c r="G61">
         <v>4069.6</v>
@@ -6295,28 +6295,28 @@
         <v>3390</v>
       </c>
       <c r="M61">
-        <v>725.922945624597</v>
+        <v>738.2267243639971</v>
       </c>
       <c r="N61">
-        <v>2664.077054375403</v>
+        <v>2651.773275636003</v>
       </c>
       <c r="O61">
-        <v>532.8154108750806</v>
+        <v>530.3546551272005</v>
       </c>
       <c r="P61">
-        <v>2131.261643500322</v>
+        <v>2121.418620508802</v>
       </c>
       <c r="Q61">
-        <v>4913.461643500323</v>
+        <v>4903.618620508802</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1795508399175735</v>
+        <v>0.1825837387819175</v>
       </c>
       <c r="T61">
-        <v>2.069082955660461</v>
+        <v>2.116000936514439</v>
       </c>
       <c r="U61">
         <v>0.07013097776675759</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.669917131608484</v>
+        <v>4.592085179415009</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1066963648408107</v>
+        <v>0.1066750638095066</v>
       </c>
       <c r="C62">
-        <v>7118.527729681029</v>
+        <v>6944.92185172077</v>
       </c>
       <c r="D62">
-        <v>13575.32772968103</v>
+        <v>13577.16185172077</v>
       </c>
       <c r="E62">
-        <v>6746.599999999999</v>
+        <v>6922.04</v>
       </c>
       <c r="F62">
-        <v>10526.4</v>
+        <v>10701.84</v>
       </c>
       <c r="G62">
         <v>4069.6</v>
@@ -6377,28 +6377,28 @@
         <v>3390</v>
       </c>
       <c r="M62">
-        <v>738.2267243639971</v>
+        <v>750.530503103397</v>
       </c>
       <c r="N62">
-        <v>2651.773275636003</v>
+        <v>2639.469496896603</v>
       </c>
       <c r="O62">
-        <v>530.3546551272005</v>
+        <v>527.8938993793207</v>
       </c>
       <c r="P62">
-        <v>2121.418620508802</v>
+        <v>2111.575597517282</v>
       </c>
       <c r="Q62">
-        <v>4903.618620508802</v>
+        <v>4893.775597517282</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1825837387819175</v>
+        <v>0.1857721709213562</v>
       </c>
       <c r="T62">
-        <v>2.116000936514439</v>
+        <v>2.165324967668622</v>
       </c>
       <c r="U62">
         <v>0.07013097776675759</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.592085179415009</v>
+        <v>4.516805094506567</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1066750638095066</v>
+        <v>0.1066537627782026</v>
       </c>
       <c r="C63">
-        <v>6944.92185172077</v>
+        <v>6771.316469432999</v>
       </c>
       <c r="D63">
-        <v>13577.16185172077</v>
+        <v>13578.996469433</v>
       </c>
       <c r="E63">
-        <v>6922.04</v>
+        <v>7097.48</v>
       </c>
       <c r="F63">
-        <v>10701.84</v>
+        <v>10877.28</v>
       </c>
       <c r="G63">
         <v>4069.6</v>
@@ -6459,28 +6459,28 @@
         <v>3390</v>
       </c>
       <c r="M63">
-        <v>750.530503103397</v>
+        <v>762.8342818427969</v>
       </c>
       <c r="N63">
-        <v>2639.469496896603</v>
+        <v>2627.165718157203</v>
       </c>
       <c r="O63">
-        <v>527.8938993793207</v>
+        <v>525.4331436314407</v>
       </c>
       <c r="P63">
-        <v>2111.575597517282</v>
+        <v>2101.732574525763</v>
       </c>
       <c r="Q63">
-        <v>4893.775597517282</v>
+        <v>4883.932574525763</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1857721709213562</v>
+        <v>0.18912841527866</v>
       </c>
       <c r="T63">
-        <v>2.165324967668622</v>
+        <v>2.217245000462499</v>
       </c>
       <c r="U63">
         <v>0.07013097776675759</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.516805094506567</v>
+        <v>4.44395339943388</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1066537627782026</v>
+        <v>0.1066324617468985</v>
       </c>
       <c r="C64">
-        <v>6771.316469432999</v>
+        <v>6597.711583018676</v>
       </c>
       <c r="D64">
-        <v>13578.996469433</v>
+        <v>13580.83158301867</v>
       </c>
       <c r="E64">
-        <v>7097.48</v>
+        <v>7272.919999999999</v>
       </c>
       <c r="F64">
-        <v>10877.28</v>
+        <v>11052.72</v>
       </c>
       <c r="G64">
         <v>4069.6</v>
@@ -6541,28 +6541,28 @@
         <v>3390</v>
       </c>
       <c r="M64">
-        <v>762.8342818427969</v>
+        <v>775.1380605821969</v>
       </c>
       <c r="N64">
-        <v>2627.165718157203</v>
+        <v>2614.861939417803</v>
       </c>
       <c r="O64">
-        <v>525.4331436314407</v>
+        <v>522.9723878835606</v>
       </c>
       <c r="P64">
-        <v>2101.732574525763</v>
+        <v>2091.889551534242</v>
       </c>
       <c r="Q64">
-        <v>4883.932574525763</v>
+        <v>4874.089551534242</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.18912841527866</v>
+        <v>0.1926660782498721</v>
       </c>
       <c r="T64">
-        <v>2.217245000462499</v>
+        <v>2.271971521515504</v>
       </c>
       <c r="U64">
         <v>0.07013097776675759</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.44395339943388</v>
+        <v>4.373414456585723</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1066324617468985</v>
+        <v>0.1066111607155945</v>
       </c>
       <c r="C65">
-        <v>6597.711583018676</v>
+        <v>6424.107192678865</v>
       </c>
       <c r="D65">
-        <v>13580.83158301867</v>
+        <v>13582.66719267887</v>
       </c>
       <c r="E65">
-        <v>7272.919999999999</v>
+        <v>7448.36</v>
       </c>
       <c r="F65">
-        <v>11052.72</v>
+        <v>11228.16</v>
       </c>
       <c r="G65">
         <v>4069.6</v>
@@ -6623,28 +6623,28 @@
         <v>3390</v>
       </c>
       <c r="M65">
-        <v>775.1380605821969</v>
+        <v>787.4418393215968</v>
       </c>
       <c r="N65">
-        <v>2614.861939417803</v>
+        <v>2602.558160678403</v>
       </c>
       <c r="O65">
-        <v>522.9723878835606</v>
+        <v>520.5116321356807</v>
       </c>
       <c r="P65">
-        <v>2091.889551534242</v>
+        <v>2082.046528542723</v>
       </c>
       <c r="Q65">
-        <v>4874.089551534242</v>
+        <v>4864.246528542722</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1926660782498721</v>
+        <v>0.1964002780528183</v>
       </c>
       <c r="T65">
-        <v>2.271971521515504</v>
+        <v>2.329738404849231</v>
       </c>
       <c r="U65">
         <v>0.07013097776675759</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.373414456585723</v>
+        <v>4.305079855701571</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1066111607155945</v>
+        <v>0.1071098596842904</v>
       </c>
       <c r="C66">
-        <v>6424.107192678865</v>
+        <v>6205.821737886627</v>
       </c>
       <c r="D66">
-        <v>13582.66719267887</v>
+        <v>13539.82173788663</v>
       </c>
       <c r="E66">
-        <v>7448.36</v>
+        <v>7623.8</v>
       </c>
       <c r="F66">
-        <v>11228.16</v>
+        <v>11403.6</v>
       </c>
       <c r="G66">
         <v>4069.6</v>
@@ -6705,45 +6705,45 @@
         <v>3390</v>
       </c>
       <c r="M66">
-        <v>787.4418393215968</v>
+        <v>811.1492180609969</v>
       </c>
       <c r="N66">
-        <v>2602.558160678403</v>
+        <v>2578.850781939003</v>
       </c>
       <c r="O66">
-        <v>520.5116321356807</v>
+        <v>515.7701563878007</v>
       </c>
       <c r="P66">
-        <v>2082.046528542723</v>
+        <v>2063.080625551203</v>
       </c>
       <c r="Q66">
-        <v>4864.246528542722</v>
+        <v>4845.280625551202</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1964002780528183</v>
+        <v>0.2003478607016471</v>
       </c>
       <c r="T66">
-        <v>2.329738404849231</v>
+        <v>2.390806252944886</v>
       </c>
       <c r="U66">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.305079855701571</v>
+        <v>4.179255708467045</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1071098596842904</v>
+        <v>0.1070965586529864</v>
       </c>
       <c r="C67">
-        <v>6205.821737886627</v>
+        <v>6031.520979996927</v>
       </c>
       <c r="D67">
-        <v>13539.82173788663</v>
+        <v>13540.96097999693</v>
       </c>
       <c r="E67">
-        <v>7623.8</v>
+        <v>7799.240000000001</v>
       </c>
       <c r="F67">
-        <v>11403.6</v>
+        <v>11579.04</v>
       </c>
       <c r="G67">
         <v>4069.6</v>
@@ -6787,28 +6787,28 @@
         <v>3390</v>
       </c>
       <c r="M67">
-        <v>811.1492180609969</v>
+        <v>823.6284368003968</v>
       </c>
       <c r="N67">
-        <v>2578.850781939003</v>
+        <v>2566.371563199603</v>
       </c>
       <c r="O67">
-        <v>515.7701563878007</v>
+        <v>513.2743126399207</v>
       </c>
       <c r="P67">
-        <v>2063.080625551203</v>
+        <v>2053.097250559683</v>
       </c>
       <c r="Q67">
-        <v>4845.280625551202</v>
+        <v>4835.297250559683</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2003478607016471</v>
+        <v>0.2045276540945246</v>
       </c>
       <c r="T67">
-        <v>2.390806252944886</v>
+        <v>2.455466327399109</v>
       </c>
       <c r="U67">
         <v>0.07113097776675759</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.179255708467045</v>
+        <v>4.11593365227815</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1070965586529864</v>
+        <v>0.1070832576216823</v>
       </c>
       <c r="C68">
-        <v>6031.520979996927</v>
+        <v>5857.220413835281</v>
       </c>
       <c r="D68">
-        <v>13540.96097999693</v>
+        <v>13542.10041383528</v>
       </c>
       <c r="E68">
-        <v>7799.240000000001</v>
+        <v>7974.680000000001</v>
       </c>
       <c r="F68">
-        <v>11579.04</v>
+        <v>11754.48</v>
       </c>
       <c r="G68">
         <v>4069.6</v>
@@ -6869,28 +6869,28 @@
         <v>3390</v>
       </c>
       <c r="M68">
-        <v>823.6284368003968</v>
+        <v>836.1076555397968</v>
       </c>
       <c r="N68">
-        <v>2566.371563199603</v>
+        <v>2553.892344460203</v>
       </c>
       <c r="O68">
-        <v>513.2743126399207</v>
+        <v>510.7784688920407</v>
       </c>
       <c r="P68">
-        <v>2053.097250559683</v>
+        <v>2043.113875568163</v>
       </c>
       <c r="Q68">
-        <v>4835.297250559683</v>
+        <v>4825.313875568163</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2045276540945246</v>
+        <v>0.2089607682990917</v>
       </c>
       <c r="T68">
-        <v>2.455466327399109</v>
+        <v>2.524045194244497</v>
       </c>
       <c r="U68">
         <v>0.07113097776675759</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.11593365227815</v>
+        <v>4.054501806721759</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1070832576216823</v>
+        <v>0.1070699565903783</v>
       </c>
       <c r="C69">
-        <v>5857.220413835281</v>
+        <v>5682.920039450086</v>
       </c>
       <c r="D69">
-        <v>13542.10041383528</v>
+        <v>13543.24003945009</v>
       </c>
       <c r="E69">
-        <v>7974.680000000001</v>
+        <v>8150.12</v>
       </c>
       <c r="F69">
-        <v>11754.48</v>
+        <v>11929.92</v>
       </c>
       <c r="G69">
         <v>4069.6</v>
@@ -6951,28 +6951,28 @@
         <v>3390</v>
       </c>
       <c r="M69">
-        <v>836.1076555397968</v>
+        <v>848.5868742791966</v>
       </c>
       <c r="N69">
-        <v>2553.892344460203</v>
+        <v>2541.413125720803</v>
       </c>
       <c r="O69">
-        <v>510.7784688920407</v>
+        <v>508.2826251441606</v>
       </c>
       <c r="P69">
-        <v>2043.113875568163</v>
+        <v>2033.130500576643</v>
       </c>
       <c r="Q69">
-        <v>4825.313875568163</v>
+        <v>4815.330500576642</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2089607682990917</v>
+        <v>0.2136709521414442</v>
       </c>
       <c r="T69">
-        <v>2.524045194244497</v>
+        <v>2.596910240267721</v>
       </c>
       <c r="U69">
         <v>0.07113097776675759</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.054501806721759</v>
+        <v>3.994876780152322</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1070699565903783</v>
+        <v>0.1070566555590742</v>
       </c>
       <c r="C70">
-        <v>5682.920039450086</v>
+        <v>5508.619856889763</v>
       </c>
       <c r="D70">
-        <v>13543.24003945009</v>
+        <v>13544.37985688977</v>
       </c>
       <c r="E70">
-        <v>8150.12</v>
+        <v>8325.560000000001</v>
       </c>
       <c r="F70">
-        <v>11929.92</v>
+        <v>12105.36</v>
       </c>
       <c r="G70">
         <v>4069.6</v>
@@ -7033,28 +7033,28 @@
         <v>3390</v>
       </c>
       <c r="M70">
-        <v>848.5868742791966</v>
+        <v>861.0660930185967</v>
       </c>
       <c r="N70">
-        <v>2541.413125720803</v>
+        <v>2528.933906981403</v>
       </c>
       <c r="O70">
-        <v>508.2826251441606</v>
+        <v>505.7867813962807</v>
       </c>
       <c r="P70">
-        <v>2033.130500576643</v>
+        <v>2023.147125585122</v>
       </c>
       <c r="Q70">
-        <v>4815.330500576642</v>
+        <v>4805.347125585122</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2136709521414442</v>
+        <v>0.2186850188123357</v>
       </c>
       <c r="T70">
-        <v>2.596910240267721</v>
+        <v>2.674476257002122</v>
       </c>
       <c r="U70">
         <v>0.07113097776675759</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.994876780152322</v>
+        <v>3.936980015222577</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1070566555590742</v>
+        <v>0.1070433545277702</v>
       </c>
       <c r="C71">
-        <v>5508.619856889763</v>
+        <v>5334.319866202752</v>
       </c>
       <c r="D71">
-        <v>13544.37985688977</v>
+        <v>13545.51986620275</v>
       </c>
       <c r="E71">
-        <v>8325.560000000001</v>
+        <v>8501</v>
       </c>
       <c r="F71">
-        <v>12105.36</v>
+        <v>12280.8</v>
       </c>
       <c r="G71">
         <v>4069.6</v>
@@ -7115,28 +7115,28 @@
         <v>3390</v>
       </c>
       <c r="M71">
-        <v>861.0660930185967</v>
+        <v>873.5453117579966</v>
       </c>
       <c r="N71">
-        <v>2528.933906981403</v>
+        <v>2516.454688242004</v>
       </c>
       <c r="O71">
-        <v>505.7867813962807</v>
+        <v>503.2909376484008</v>
       </c>
       <c r="P71">
-        <v>2023.147125585122</v>
+        <v>2013.163750593603</v>
       </c>
       <c r="Q71">
-        <v>4805.347125585122</v>
+        <v>4795.363750593602</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2186850188123357</v>
+        <v>0.2240333565946198</v>
       </c>
       <c r="T71">
-        <v>2.674476257002122</v>
+        <v>2.757213341518815</v>
       </c>
       <c r="U71">
         <v>0.07113097776675759</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.936980015222577</v>
+        <v>3.880737443576541</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1070433545277702</v>
+        <v>0.1070300534964662</v>
       </c>
       <c r="C72">
-        <v>5334.319866202752</v>
+        <v>5160.020067437501</v>
       </c>
       <c r="D72">
-        <v>13545.51986620275</v>
+        <v>13546.6600674375</v>
       </c>
       <c r="E72">
-        <v>8501</v>
+        <v>8676.440000000002</v>
       </c>
       <c r="F72">
-        <v>12280.8</v>
+        <v>12456.24</v>
       </c>
       <c r="G72">
         <v>4069.6</v>
@@ -7197,28 +7197,28 @@
         <v>3390</v>
       </c>
       <c r="M72">
-        <v>873.5453117579966</v>
+        <v>886.0245304973967</v>
       </c>
       <c r="N72">
-        <v>2516.454688242004</v>
+        <v>2503.975469502603</v>
       </c>
       <c r="O72">
-        <v>503.2909376484008</v>
+        <v>500.7950939005207</v>
       </c>
       <c r="P72">
-        <v>2013.163750593603</v>
+        <v>2003.180375602082</v>
       </c>
       <c r="Q72">
-        <v>4795.363750593602</v>
+        <v>4785.380375602082</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2240333565946198</v>
+        <v>0.2297505452584409</v>
       </c>
       <c r="T72">
-        <v>2.757213341518815</v>
+        <v>2.845656431864247</v>
       </c>
       <c r="U72">
         <v>0.07113097776675759</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.880737443576541</v>
+        <v>3.826079169723349</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1070300534964662</v>
+        <v>0.1070167524651621</v>
       </c>
       <c r="C73">
-        <v>5160.020067437503</v>
+        <v>4985.720460642489</v>
       </c>
       <c r="D73">
-        <v>13546.6600674375</v>
+        <v>13547.80046064249</v>
       </c>
       <c r="E73">
-        <v>8676.439999999999</v>
+        <v>8851.880000000001</v>
       </c>
       <c r="F73">
-        <v>12456.24</v>
+        <v>12631.68</v>
       </c>
       <c r="G73">
         <v>4069.6</v>
@@ -7279,28 +7279,28 @@
         <v>3390</v>
       </c>
       <c r="M73">
-        <v>886.0245304973965</v>
+        <v>898.5037492367965</v>
       </c>
       <c r="N73">
-        <v>2503.975469502604</v>
+        <v>2491.496250763204</v>
       </c>
       <c r="O73">
-        <v>500.7950939005207</v>
+        <v>498.2992501526408</v>
       </c>
       <c r="P73">
-        <v>2003.180375602083</v>
+        <v>1993.197000610563</v>
       </c>
       <c r="Q73">
-        <v>4785.380375602082</v>
+        <v>4775.397000610563</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2297505452584408</v>
+        <v>0.2358761045411062</v>
       </c>
       <c r="T73">
-        <v>2.845656431864246</v>
+        <v>2.940416885805779</v>
       </c>
       <c r="U73">
         <v>0.07113097776675759</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.82607916972335</v>
+        <v>3.77293918125497</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1070167524651621</v>
+        <v>0.1070034514338581</v>
       </c>
       <c r="C74">
-        <v>4985.720460642489</v>
+        <v>4811.421045866187</v>
       </c>
       <c r="D74">
-        <v>13547.80046064249</v>
+        <v>13548.94104586619</v>
       </c>
       <c r="E74">
-        <v>8851.880000000001</v>
+        <v>9027.32</v>
       </c>
       <c r="F74">
-        <v>12631.68</v>
+        <v>12807.12</v>
       </c>
       <c r="G74">
         <v>4069.6</v>
@@ -7361,28 +7361,28 @@
         <v>3390</v>
       </c>
       <c r="M74">
-        <v>898.5037492367965</v>
+        <v>910.9829679761964</v>
       </c>
       <c r="N74">
-        <v>2491.496250763204</v>
+        <v>2479.017032023803</v>
       </c>
       <c r="O74">
-        <v>498.2992501526408</v>
+        <v>495.8034064047607</v>
       </c>
       <c r="P74">
-        <v>1993.197000610563</v>
+        <v>1983.213625619043</v>
       </c>
       <c r="Q74">
-        <v>4775.397000610563</v>
+        <v>4765.413625619043</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2358761045411062</v>
+        <v>0.2424554089558208</v>
       </c>
       <c r="T74">
-        <v>2.940416885805779</v>
+        <v>3.04219663263187</v>
       </c>
       <c r="U74">
         <v>0.07113097776675759</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.77293918125497</v>
+        <v>3.721255082881615</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1070034514338581</v>
+        <v>0.106990150402554</v>
       </c>
       <c r="C75">
-        <v>4811.421045866187</v>
+        <v>4637.121823157113</v>
       </c>
       <c r="D75">
-        <v>13548.94104586619</v>
+        <v>13550.08182315711</v>
       </c>
       <c r="E75">
-        <v>9027.32</v>
+        <v>9202.759999999998</v>
       </c>
       <c r="F75">
-        <v>12807.12</v>
+        <v>12982.56</v>
       </c>
       <c r="G75">
         <v>4069.6</v>
@@ -7443,28 +7443,28 @@
         <v>3390</v>
       </c>
       <c r="M75">
-        <v>910.9829679761964</v>
+        <v>923.4621867155963</v>
       </c>
       <c r="N75">
-        <v>2479.017032023803</v>
+        <v>2466.537813284403</v>
       </c>
       <c r="O75">
-        <v>495.8034064047607</v>
+        <v>493.3075626568807</v>
       </c>
       <c r="P75">
-        <v>1983.213625619043</v>
+        <v>1973.230250627523</v>
       </c>
       <c r="Q75">
-        <v>4765.413625619043</v>
+        <v>4755.430250627523</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2424554089558208</v>
+        <v>0.2495408137101289</v>
       </c>
       <c r="T75">
-        <v>3.04219663263187</v>
+        <v>3.151805590752277</v>
       </c>
       <c r="U75">
         <v>0.07113097776675759</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.721255082881615</v>
+        <v>3.670967852031863</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.106990150402554</v>
+        <v>0.10697684937125</v>
       </c>
       <c r="C76">
-        <v>4637.121823157113</v>
+        <v>4462.822792563773</v>
       </c>
       <c r="D76">
-        <v>13550.08182315711</v>
+        <v>13551.22279256377</v>
       </c>
       <c r="E76">
-        <v>9202.759999999998</v>
+        <v>9378.200000000001</v>
       </c>
       <c r="F76">
-        <v>12982.56</v>
+        <v>13158</v>
       </c>
       <c r="G76">
         <v>4069.6</v>
@@ -7525,28 +7525,28 @@
         <v>3390</v>
       </c>
       <c r="M76">
-        <v>923.4621867155963</v>
+        <v>935.9414054549964</v>
       </c>
       <c r="N76">
-        <v>2466.537813284403</v>
+        <v>2454.058594545004</v>
       </c>
       <c r="O76">
-        <v>493.3075626568807</v>
+        <v>490.8117189090008</v>
       </c>
       <c r="P76">
-        <v>1973.230250627523</v>
+        <v>1963.246875636003</v>
       </c>
       <c r="Q76">
-        <v>4755.430250627523</v>
+        <v>4745.446875636003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2495408137101289</v>
+        <v>0.2571930508447816</v>
       </c>
       <c r="T76">
-        <v>3.151805590752277</v>
+        <v>3.270183265522316</v>
       </c>
       <c r="U76">
         <v>0.07113097776675759</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.670967852031863</v>
+        <v>3.622021614004772</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.10697684937125</v>
+        <v>0.1069635483399459</v>
       </c>
       <c r="C77">
-        <v>4462.822792563773</v>
+        <v>4288.523954134705</v>
       </c>
       <c r="D77">
-        <v>13551.22279256377</v>
+        <v>13552.36395413471</v>
       </c>
       <c r="E77">
-        <v>9378.200000000001</v>
+        <v>9553.639999999999</v>
       </c>
       <c r="F77">
-        <v>13158</v>
+        <v>13333.44</v>
       </c>
       <c r="G77">
         <v>4069.6</v>
@@ -7607,28 +7607,28 @@
         <v>3390</v>
       </c>
       <c r="M77">
-        <v>935.9414054549964</v>
+        <v>948.4206241943963</v>
       </c>
       <c r="N77">
-        <v>2454.058594545004</v>
+        <v>2441.579375805604</v>
       </c>
       <c r="O77">
-        <v>490.8117189090008</v>
+        <v>488.3158751611208</v>
       </c>
       <c r="P77">
-        <v>1963.246875636003</v>
+        <v>1953.263500644483</v>
       </c>
       <c r="Q77">
-        <v>4745.446875636003</v>
+        <v>4735.463500644482</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2571930508447816</v>
+        <v>0.2654829744073221</v>
       </c>
       <c r="T77">
-        <v>3.270183265522316</v>
+        <v>3.398425746523191</v>
       </c>
       <c r="U77">
         <v>0.07113097776675759</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.622021614004772</v>
+        <v>3.57436343487313</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1069635483399459</v>
+        <v>0.1069502473086419</v>
       </c>
       <c r="C78">
-        <v>4288.523954134705</v>
+        <v>4114.225307918467</v>
       </c>
       <c r="D78">
-        <v>13552.36395413471</v>
+        <v>13553.50530791847</v>
       </c>
       <c r="E78">
-        <v>9553.639999999999</v>
+        <v>9729.080000000002</v>
       </c>
       <c r="F78">
-        <v>13333.44</v>
+        <v>13508.88</v>
       </c>
       <c r="G78">
         <v>4069.6</v>
@@ -7689,28 +7689,28 @@
         <v>3390</v>
       </c>
       <c r="M78">
-        <v>948.4206241943963</v>
+        <v>960.8998429337963</v>
       </c>
       <c r="N78">
-        <v>2441.579375805604</v>
+        <v>2429.100157066204</v>
       </c>
       <c r="O78">
-        <v>488.3158751611208</v>
+        <v>485.8200314132408</v>
       </c>
       <c r="P78">
-        <v>1953.263500644483</v>
+        <v>1943.280125652963</v>
       </c>
       <c r="Q78">
-        <v>4735.463500644482</v>
+        <v>4725.480125652963</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2654829744073221</v>
+        <v>0.2744937608883443</v>
       </c>
       <c r="T78">
-        <v>3.398425746523191</v>
+        <v>3.537819747611099</v>
       </c>
       <c r="U78">
         <v>0.07113097776675759</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.57436343487313</v>
+        <v>3.527943130524128</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1069502473086419</v>
+        <v>0.1069369462773378</v>
       </c>
       <c r="C79">
-        <v>4114.225307918467</v>
+        <v>3939.926853963614</v>
       </c>
       <c r="D79">
-        <v>13553.50530791847</v>
+        <v>13554.64685396362</v>
       </c>
       <c r="E79">
-        <v>9729.080000000002</v>
+        <v>9904.52</v>
       </c>
       <c r="F79">
-        <v>13508.88</v>
+        <v>13684.32</v>
       </c>
       <c r="G79">
         <v>4069.6</v>
@@ -7771,28 +7771,28 @@
         <v>3390</v>
       </c>
       <c r="M79">
-        <v>960.8998429337963</v>
+        <v>973.3790616731961</v>
       </c>
       <c r="N79">
-        <v>2429.100157066204</v>
+        <v>2416.620938326804</v>
       </c>
       <c r="O79">
-        <v>485.8200314132408</v>
+        <v>483.3241876653608</v>
       </c>
       <c r="P79">
-        <v>1943.280125652963</v>
+        <v>1933.296750661443</v>
       </c>
       <c r="Q79">
-        <v>4725.480125652963</v>
+        <v>4715.496750661443</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2744937608883443</v>
+        <v>0.2843237097767322</v>
       </c>
       <c r="T79">
-        <v>3.537819747611099</v>
+        <v>3.689885930616089</v>
       </c>
       <c r="U79">
         <v>0.07113097776675759</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.527943130524128</v>
+        <v>3.482713090389203</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1069369462773378</v>
+        <v>0.1069236452460338</v>
       </c>
       <c r="C80">
-        <v>3939.926853963614</v>
+        <v>3765.628592318744</v>
       </c>
       <c r="D80">
-        <v>13554.64685396362</v>
+        <v>13555.78859231874</v>
       </c>
       <c r="E80">
-        <v>9904.52</v>
+        <v>10079.96</v>
       </c>
       <c r="F80">
-        <v>13684.32</v>
+        <v>13859.76</v>
       </c>
       <c r="G80">
         <v>4069.6</v>
@@ -7853,28 +7853,28 @@
         <v>3390</v>
       </c>
       <c r="M80">
-        <v>973.3790616731961</v>
+        <v>985.8582804125962</v>
       </c>
       <c r="N80">
-        <v>2416.620938326804</v>
+        <v>2404.141719587404</v>
       </c>
       <c r="O80">
-        <v>483.3241876653608</v>
+        <v>480.8283439174808</v>
       </c>
       <c r="P80">
-        <v>1933.296750661443</v>
+        <v>1923.313375669923</v>
       </c>
       <c r="Q80">
-        <v>4715.496750661443</v>
+        <v>4705.513375669923</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2843237097767322</v>
+        <v>0.295089844273538</v>
       </c>
       <c r="T80">
-        <v>3.689885930616089</v>
+        <v>3.856434607240602</v>
       </c>
       <c r="U80">
         <v>0.07113097776675759</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.482713090389203</v>
+        <v>3.438628114561491</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1069236452460338</v>
+        <v>0.1069103442147297</v>
       </c>
       <c r="C81">
-        <v>3765.628592318744</v>
+        <v>3591.33052303244</v>
       </c>
       <c r="D81">
-        <v>13555.78859231874</v>
+        <v>13556.93052303244</v>
       </c>
       <c r="E81">
-        <v>10079.96</v>
+        <v>10255.4</v>
       </c>
       <c r="F81">
-        <v>13859.76</v>
+        <v>14035.2</v>
       </c>
       <c r="G81">
         <v>4069.6</v>
@@ -7935,28 +7935,28 @@
         <v>3390</v>
       </c>
       <c r="M81">
-        <v>985.8582804125962</v>
+        <v>998.3374991519961</v>
       </c>
       <c r="N81">
-        <v>2404.141719587404</v>
+        <v>2391.662500848004</v>
       </c>
       <c r="O81">
-        <v>480.8283439174808</v>
+        <v>478.3325001696008</v>
       </c>
       <c r="P81">
-        <v>1923.313375669923</v>
+        <v>1913.330000678403</v>
       </c>
       <c r="Q81">
-        <v>4705.513375669923</v>
+        <v>4695.530000678404</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.295089844273538</v>
+        <v>0.3069325922200244</v>
       </c>
       <c r="T81">
-        <v>3.856434607240602</v>
+        <v>4.039638151527567</v>
       </c>
       <c r="U81">
         <v>0.07113097776675759</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.438628114561491</v>
+        <v>3.395645263129473</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1069103442147297</v>
+        <v>0.1068970431834257</v>
       </c>
       <c r="C82">
-        <v>3591.33052303244</v>
+        <v>3417.032646153335</v>
       </c>
       <c r="D82">
-        <v>13556.93052303244</v>
+        <v>13558.07264615334</v>
       </c>
       <c r="E82">
-        <v>10255.4</v>
+        <v>10430.84</v>
       </c>
       <c r="F82">
-        <v>14035.2</v>
+        <v>14210.64</v>
       </c>
       <c r="G82">
         <v>4069.6</v>
@@ -8017,28 +8017,28 @@
         <v>3390</v>
       </c>
       <c r="M82">
-        <v>998.3374991519961</v>
+        <v>1010.816717891396</v>
       </c>
       <c r="N82">
-        <v>2391.662500848004</v>
+        <v>2379.183282108604</v>
       </c>
       <c r="O82">
-        <v>478.3325001696008</v>
+        <v>475.8366564217208</v>
       </c>
       <c r="P82">
-        <v>1913.330000678403</v>
+        <v>1903.346625686883</v>
       </c>
       <c r="Q82">
-        <v>4695.530000678404</v>
+        <v>4685.546625686882</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3069325922200244</v>
+        <v>0.3200219452135094</v>
       </c>
       <c r="T82">
-        <v>4.039638151527567</v>
+        <v>4.242126279423687</v>
       </c>
       <c r="U82">
         <v>0.07113097776675759</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.395645263129473</v>
+        <v>3.353723716671084</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1068970431834257</v>
+        <v>0.1068837421521216</v>
       </c>
       <c r="C83">
-        <v>3417.032646153335</v>
+        <v>3242.734961730057</v>
       </c>
       <c r="D83">
-        <v>13558.07264615334</v>
+        <v>13559.21496173006</v>
       </c>
       <c r="E83">
-        <v>10430.84</v>
+        <v>10606.28</v>
       </c>
       <c r="F83">
-        <v>14210.64</v>
+        <v>14386.08</v>
       </c>
       <c r="G83">
         <v>4069.6</v>
@@ -8099,28 +8099,28 @@
         <v>3390</v>
       </c>
       <c r="M83">
-        <v>1010.816717891396</v>
+        <v>1023.295936630796</v>
       </c>
       <c r="N83">
-        <v>2379.183282108604</v>
+        <v>2366.704063369204</v>
       </c>
       <c r="O83">
-        <v>475.8366564217208</v>
+        <v>473.3408126738408</v>
       </c>
       <c r="P83">
-        <v>1903.346625686883</v>
+        <v>1893.363250695363</v>
       </c>
       <c r="Q83">
-        <v>4685.546625686882</v>
+        <v>4675.563250695363</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3200219452135094</v>
+        <v>0.334565670761826</v>
       </c>
       <c r="T83">
-        <v>4.242126279423687</v>
+        <v>4.467113088197151</v>
       </c>
       <c r="U83">
         <v>0.07113097776675759</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.353723716671084</v>
+        <v>3.312824646955583</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1068837421521216</v>
+        <v>0.1068704411208176</v>
       </c>
       <c r="C84">
-        <v>3242.734961730057</v>
+        <v>3068.437469811252</v>
       </c>
       <c r="D84">
-        <v>13559.21496173006</v>
+        <v>13560.35746981125</v>
       </c>
       <c r="E84">
-        <v>10606.28</v>
+        <v>10781.72</v>
       </c>
       <c r="F84">
-        <v>14386.08</v>
+        <v>14561.52</v>
       </c>
       <c r="G84">
         <v>4069.6</v>
@@ -8181,28 +8181,28 @@
         <v>3390</v>
       </c>
       <c r="M84">
-        <v>1023.295936630796</v>
+        <v>1035.775155370196</v>
       </c>
       <c r="N84">
-        <v>2366.704063369204</v>
+        <v>2354.224844629804</v>
       </c>
       <c r="O84">
-        <v>473.3408126738408</v>
+        <v>470.8449689259608</v>
       </c>
       <c r="P84">
-        <v>1893.363250695363</v>
+        <v>1883.379875703843</v>
       </c>
       <c r="Q84">
-        <v>4675.563250695363</v>
+        <v>4665.579875703843</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.334565670761826</v>
+        <v>0.3508204228452387</v>
       </c>
       <c r="T84">
-        <v>4.467113088197151</v>
+        <v>4.718568933296907</v>
       </c>
       <c r="U84">
         <v>0.07113097776675759</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.312824646955583</v>
+        <v>3.272911096992263</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1068704411208176</v>
+        <v>0.1068571400895136</v>
       </c>
       <c r="C85">
-        <v>3068.437469811252</v>
+        <v>2894.140170445584</v>
       </c>
       <c r="D85">
-        <v>13560.35746981125</v>
+        <v>13561.50017044559</v>
       </c>
       <c r="E85">
-        <v>10781.72</v>
+        <v>10957.16</v>
       </c>
       <c r="F85">
-        <v>14561.52</v>
+        <v>14736.96</v>
       </c>
       <c r="G85">
         <v>4069.6</v>
@@ -8263,28 +8263,28 @@
         <v>3390</v>
       </c>
       <c r="M85">
-        <v>1035.775155370196</v>
+        <v>1048.254374109596</v>
       </c>
       <c r="N85">
-        <v>2354.224844629804</v>
+        <v>2341.745625890404</v>
       </c>
       <c r="O85">
-        <v>470.8449689259608</v>
+        <v>468.3491251780808</v>
       </c>
       <c r="P85">
-        <v>1883.379875703843</v>
+        <v>1873.396500712323</v>
       </c>
       <c r="Q85">
-        <v>4665.579875703843</v>
+        <v>4655.596500712323</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3508204228452387</v>
+        <v>0.3691070189390779</v>
       </c>
       <c r="T85">
-        <v>4.718568933296907</v>
+        <v>5.001456759034132</v>
       </c>
       <c r="U85">
         <v>0.07113097776675759</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.272911096992263</v>
+        <v>3.233947869647117</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1068571400895136</v>
+        <v>0.1068438390582095</v>
       </c>
       <c r="C86">
-        <v>2894.140170445586</v>
+        <v>2719.843063681745</v>
       </c>
       <c r="D86">
-        <v>13561.50017044559</v>
+        <v>13562.64306368174</v>
       </c>
       <c r="E86">
-        <v>10957.16</v>
+        <v>11132.6</v>
       </c>
       <c r="F86">
-        <v>14736.96</v>
+        <v>14912.4</v>
       </c>
       <c r="G86">
         <v>4069.6</v>
@@ -8345,28 +8345,28 @@
         <v>3390</v>
       </c>
       <c r="M86">
-        <v>1048.254374109596</v>
+        <v>1060.733592848996</v>
       </c>
       <c r="N86">
-        <v>2341.745625890404</v>
+        <v>2329.266407151004</v>
       </c>
       <c r="O86">
-        <v>468.3491251780808</v>
+        <v>465.8532814302009</v>
       </c>
       <c r="P86">
-        <v>1873.396500712323</v>
+        <v>1863.413125720803</v>
       </c>
       <c r="Q86">
-        <v>4655.596500712323</v>
+        <v>4645.613125720804</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3691070189390778</v>
+        <v>0.3898318278454289</v>
       </c>
       <c r="T86">
-        <v>5.001456759034129</v>
+        <v>5.322062961536317</v>
       </c>
       <c r="U86">
         <v>0.07113097776675759</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.233947869647118</v>
+        <v>3.195901424121857</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1068438390582095</v>
+        <v>0.1068305380269055</v>
       </c>
       <c r="C87">
-        <v>2719.843063681745</v>
+        <v>2545.546149568425</v>
       </c>
       <c r="D87">
-        <v>13562.64306368174</v>
+        <v>13563.78614956842</v>
       </c>
       <c r="E87">
-        <v>11132.6</v>
+        <v>11308.04</v>
       </c>
       <c r="F87">
-        <v>14912.4</v>
+        <v>15087.84</v>
       </c>
       <c r="G87">
         <v>4069.6</v>
@@ -8427,28 +8427,28 @@
         <v>3390</v>
       </c>
       <c r="M87">
-        <v>1060.733592848996</v>
+        <v>1073.212811588396</v>
       </c>
       <c r="N87">
-        <v>2329.266407151004</v>
+        <v>2316.787188411604</v>
       </c>
       <c r="O87">
-        <v>465.8532814302009</v>
+        <v>463.3574376823208</v>
       </c>
       <c r="P87">
-        <v>1863.413125720803</v>
+        <v>1853.429750729283</v>
       </c>
       <c r="Q87">
-        <v>4645.613125720804</v>
+        <v>4635.629750729283</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3898318278454289</v>
+        <v>0.4135173237384017</v>
       </c>
       <c r="T87">
-        <v>5.322062961536317</v>
+        <v>5.688470050110246</v>
       </c>
       <c r="U87">
         <v>0.07113097776675759</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.195901424121857</v>
+        <v>3.158739779655324</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1068305380269055</v>
+        <v>0.1068172369956014</v>
       </c>
       <c r="C88">
-        <v>2545.546149568425</v>
+        <v>2371.249428154339</v>
       </c>
       <c r="D88">
-        <v>13563.78614956842</v>
+        <v>13564.92942815434</v>
       </c>
       <c r="E88">
-        <v>11308.04</v>
+        <v>11483.48</v>
       </c>
       <c r="F88">
-        <v>15087.84</v>
+        <v>15263.28</v>
       </c>
       <c r="G88">
         <v>4069.6</v>
@@ -8509,28 +8509,28 @@
         <v>3390</v>
       </c>
       <c r="M88">
-        <v>1073.212811588396</v>
+        <v>1085.692030327796</v>
       </c>
       <c r="N88">
-        <v>2316.787188411604</v>
+        <v>2304.307969672204</v>
       </c>
       <c r="O88">
-        <v>463.3574376823208</v>
+        <v>460.8615939344409</v>
       </c>
       <c r="P88">
-        <v>1853.429750729283</v>
+        <v>1843.446375737763</v>
       </c>
       <c r="Q88">
-        <v>4635.629750729283</v>
+        <v>4625.646375737763</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4135173237384017</v>
+        <v>0.4408467420764471</v>
       </c>
       <c r="T88">
-        <v>5.688470050110246</v>
+        <v>6.11124746000324</v>
       </c>
       <c r="U88">
         <v>0.07113097776675759</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.158739779655324</v>
+        <v>3.122432425866183</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1068172369956014</v>
+        <v>0.1068039359642974</v>
       </c>
       <c r="C89">
-        <v>2371.249428154339</v>
+        <v>2196.952899488226</v>
       </c>
       <c r="D89">
-        <v>13564.92942815434</v>
+        <v>13566.07289948822</v>
       </c>
       <c r="E89">
-        <v>11483.48</v>
+        <v>11658.92</v>
       </c>
       <c r="F89">
-        <v>15263.28</v>
+        <v>15438.72</v>
       </c>
       <c r="G89">
         <v>4069.6</v>
@@ -8591,28 +8591,28 @@
         <v>3390</v>
       </c>
       <c r="M89">
-        <v>1085.692030327796</v>
+        <v>1098.171249067196</v>
       </c>
       <c r="N89">
-        <v>2304.307969672204</v>
+        <v>2291.828750932804</v>
       </c>
       <c r="O89">
-        <v>460.8615939344409</v>
+        <v>458.3657501865609</v>
       </c>
       <c r="P89">
-        <v>1843.446375737763</v>
+        <v>1833.463000746243</v>
       </c>
       <c r="Q89">
-        <v>4625.646375737763</v>
+        <v>4615.663000746243</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4408467420764471</v>
+        <v>0.4727310634708335</v>
       </c>
       <c r="T89">
-        <v>6.11124746000324</v>
+        <v>6.604487771545068</v>
       </c>
       <c r="U89">
         <v>0.07113097776675759</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.122432425866183</v>
+        <v>3.086950239208612</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1068039359642974</v>
+        <v>0.1067906349329933</v>
       </c>
       <c r="C90">
-        <v>2196.952899488226</v>
+        <v>2022.656563618824</v>
       </c>
       <c r="D90">
-        <v>13566.07289948822</v>
+        <v>13567.21656361883</v>
       </c>
       <c r="E90">
-        <v>11658.92</v>
+        <v>11834.36</v>
       </c>
       <c r="F90">
-        <v>15438.72</v>
+        <v>15614.16</v>
       </c>
       <c r="G90">
         <v>4069.6</v>
@@ -8673,28 +8673,28 @@
         <v>3390</v>
       </c>
       <c r="M90">
-        <v>1098.171249067196</v>
+        <v>1110.650467806596</v>
       </c>
       <c r="N90">
-        <v>2291.828750932804</v>
+        <v>2279.349532193404</v>
       </c>
       <c r="O90">
-        <v>458.3657501865609</v>
+        <v>455.8699064386809</v>
       </c>
       <c r="P90">
-        <v>1833.463000746243</v>
+        <v>1823.479625754723</v>
       </c>
       <c r="Q90">
-        <v>4615.663000746243</v>
+        <v>4605.679625754723</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4727310634708335</v>
+        <v>0.5104125342096537</v>
       </c>
       <c r="T90">
-        <v>6.604487771545068</v>
+        <v>7.187408139730865</v>
       </c>
       <c r="U90">
         <v>0.07113097776675759</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.086950239208612</v>
+        <v>3.052265405060201</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1067906349329933</v>
+        <v>0.1067773339016893</v>
       </c>
       <c r="C91">
-        <v>2022.656563618824</v>
+        <v>1848.3604205949</v>
       </c>
       <c r="D91">
-        <v>13567.21656361883</v>
+        <v>13568.3604205949</v>
       </c>
       <c r="E91">
-        <v>11834.36</v>
+        <v>12009.8</v>
       </c>
       <c r="F91">
-        <v>15614.16</v>
+        <v>15789.6</v>
       </c>
       <c r="G91">
         <v>4069.6</v>
@@ -8755,28 +8755,28 @@
         <v>3390</v>
       </c>
       <c r="M91">
-        <v>1110.650467806596</v>
+        <v>1123.129686545996</v>
       </c>
       <c r="N91">
-        <v>2279.349532193404</v>
+        <v>2266.870313454005</v>
       </c>
       <c r="O91">
-        <v>455.8699064386809</v>
+        <v>453.3740626908009</v>
       </c>
       <c r="P91">
-        <v>1823.479625754723</v>
+        <v>1813.496250763204</v>
       </c>
       <c r="Q91">
-        <v>4605.679625754723</v>
+        <v>4595.696250763203</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5104125342096537</v>
+        <v>0.5556302990962382</v>
       </c>
       <c r="T91">
-        <v>7.187408139730865</v>
+        <v>7.886912581553822</v>
       </c>
       <c r="U91">
         <v>0.07113097776675759</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.052265405060201</v>
+        <v>3.018351345003977</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1067773339016893</v>
+        <v>0.1085840328703852</v>
       </c>
       <c r="C92">
-        <v>1848.3604205949</v>
+        <v>1519.294838484726</v>
       </c>
       <c r="D92">
-        <v>13568.3604205949</v>
+        <v>13414.73483848473</v>
       </c>
       <c r="E92">
-        <v>12009.8</v>
+        <v>12185.24</v>
       </c>
       <c r="F92">
-        <v>15789.6</v>
+        <v>15965.04</v>
       </c>
       <c r="G92">
         <v>4069.6</v>
@@ -8837,45 +8837,45 @@
         <v>3390</v>
       </c>
       <c r="M92">
-        <v>1123.129686545996</v>
+        <v>1175.521505285396</v>
       </c>
       <c r="N92">
-        <v>2266.870313454005</v>
+        <v>2214.478494714604</v>
       </c>
       <c r="O92">
-        <v>453.3740626908009</v>
+        <v>442.8956989429209</v>
       </c>
       <c r="P92">
-        <v>1813.496250763204</v>
+        <v>1771.582795771684</v>
       </c>
       <c r="Q92">
-        <v>4595.696250763203</v>
+        <v>4553.782795771684</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5556302990962382</v>
+        <v>0.6108964561798412</v>
       </c>
       <c r="T92">
-        <v>7.886912581553822</v>
+        <v>8.74186245489299</v>
       </c>
       <c r="U92">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y92">
-        <v>3.018351345003977</v>
+        <v>2.883826441930528</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1085840328703852</v>
+        <v>0.1085907318390812</v>
       </c>
       <c r="C93">
-        <v>1519.294838484726</v>
+        <v>1343.291690956155</v>
       </c>
       <c r="D93">
-        <v>13414.73483848473</v>
+        <v>13414.17169095616</v>
       </c>
       <c r="E93">
-        <v>12185.24</v>
+        <v>12360.68</v>
       </c>
       <c r="F93">
-        <v>15965.04</v>
+        <v>16140.48</v>
       </c>
       <c r="G93">
         <v>4069.6</v>
@@ -8919,28 +8919,28 @@
         <v>3390</v>
       </c>
       <c r="M93">
-        <v>1175.521505285396</v>
+        <v>1188.439324024795</v>
       </c>
       <c r="N93">
-        <v>2214.478494714604</v>
+        <v>2201.560675975205</v>
       </c>
       <c r="O93">
-        <v>442.8956989429209</v>
+        <v>440.3121351950409</v>
       </c>
       <c r="P93">
-        <v>1771.582795771684</v>
+        <v>1761.248540780164</v>
       </c>
       <c r="Q93">
-        <v>4553.782795771684</v>
+        <v>4543.448540780164</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6108964561798412</v>
+        <v>0.6799791525343453</v>
       </c>
       <c r="T93">
-        <v>8.74186245489299</v>
+        <v>9.810549796566953</v>
       </c>
       <c r="U93">
         <v>0.07363097776675757</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.883826441930528</v>
+        <v>2.852480502344326</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1085907318390812</v>
+        <v>0.1085974308077771</v>
       </c>
       <c r="C94">
-        <v>1343.291690956155</v>
+        <v>1167.28859070721</v>
       </c>
       <c r="D94">
-        <v>13414.17169095616</v>
+        <v>13413.60859070721</v>
       </c>
       <c r="E94">
-        <v>12360.68</v>
+        <v>12536.12</v>
       </c>
       <c r="F94">
-        <v>16140.48</v>
+        <v>16315.92</v>
       </c>
       <c r="G94">
         <v>4069.6</v>
@@ -9001,28 +9001,28 @@
         <v>3390</v>
       </c>
       <c r="M94">
-        <v>1188.439324024795</v>
+        <v>1201.357142764195</v>
       </c>
       <c r="N94">
-        <v>2201.560675975205</v>
+        <v>2188.642857235805</v>
       </c>
       <c r="O94">
-        <v>440.3121351950409</v>
+        <v>437.7285714471609</v>
       </c>
       <c r="P94">
-        <v>1761.248540780164</v>
+        <v>1750.914285788644</v>
       </c>
       <c r="Q94">
-        <v>4543.448540780164</v>
+        <v>4533.114285788643</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6799791525343453</v>
+        <v>0.7687997621329931</v>
       </c>
       <c r="T94">
-        <v>9.810549796566953</v>
+        <v>11.18457637871919</v>
       </c>
       <c r="U94">
         <v>0.07363097776675757</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.852480502344326</v>
+        <v>2.821808668985785</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1085974308077771</v>
+        <v>0.1086041297764731</v>
       </c>
       <c r="C95">
-        <v>1167.28859070721</v>
+        <v>991.2855377319393</v>
       </c>
       <c r="D95">
-        <v>13413.60859070721</v>
+        <v>13413.04553773194</v>
       </c>
       <c r="E95">
-        <v>12536.12</v>
+        <v>12711.56</v>
       </c>
       <c r="F95">
-        <v>16315.92</v>
+        <v>16491.36</v>
       </c>
       <c r="G95">
         <v>4069.6</v>
@@ -9083,28 +9083,28 @@
         <v>3390</v>
       </c>
       <c r="M95">
-        <v>1201.357142764195</v>
+        <v>1214.274961503595</v>
       </c>
       <c r="N95">
-        <v>2188.642857235805</v>
+        <v>2175.725038496405</v>
       </c>
       <c r="O95">
-        <v>437.7285714471609</v>
+        <v>435.1450076992809</v>
       </c>
       <c r="P95">
-        <v>1750.914285788644</v>
+        <v>1740.580030797124</v>
       </c>
       <c r="Q95">
-        <v>4533.114285788643</v>
+        <v>4522.780030797123</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7687997621329931</v>
+        <v>0.8872272415978569</v>
       </c>
       <c r="T95">
-        <v>11.18457637871919</v>
+        <v>13.01661182158884</v>
       </c>
       <c r="U95">
         <v>0.07363097776675757</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.821808668985785</v>
+        <v>2.791789427826362</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1086041297764731</v>
+        <v>0.108610828745169</v>
       </c>
       <c r="C96">
-        <v>991.2855377319393</v>
+        <v>815.2825320243828</v>
       </c>
       <c r="D96">
-        <v>13413.04553773194</v>
+        <v>13412.48253202439</v>
       </c>
       <c r="E96">
-        <v>12711.56</v>
+        <v>12887</v>
       </c>
       <c r="F96">
-        <v>16491.36</v>
+        <v>16666.8</v>
       </c>
       <c r="G96">
         <v>4069.6</v>
@@ -9165,28 +9165,28 @@
         <v>3390</v>
       </c>
       <c r="M96">
-        <v>1214.274961503595</v>
+        <v>1227.192780242995</v>
       </c>
       <c r="N96">
-        <v>2175.725038496405</v>
+        <v>2162.807219757005</v>
       </c>
       <c r="O96">
-        <v>435.1450076992809</v>
+        <v>432.5614439514009</v>
       </c>
       <c r="P96">
-        <v>1740.580030797124</v>
+        <v>1730.245775805604</v>
       </c>
       <c r="Q96">
-        <v>4522.780030797123</v>
+        <v>4512.445775805603</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8872272415978569</v>
+        <v>1.053025712848667</v>
       </c>
       <c r="T96">
-        <v>13.01661182158884</v>
+        <v>15.58146144160635</v>
       </c>
       <c r="U96">
         <v>0.07363097776675757</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.791789427826362</v>
+        <v>2.762402170691348</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.108610828745169</v>
+        <v>0.108617527713865</v>
       </c>
       <c r="C97">
-        <v>815.2825320243828</v>
+        <v>639.2795735785985</v>
       </c>
       <c r="D97">
-        <v>13412.48253202439</v>
+        <v>13411.9195735786</v>
       </c>
       <c r="E97">
-        <v>12887</v>
+        <v>13062.44</v>
       </c>
       <c r="F97">
-        <v>16666.8</v>
+        <v>16842.24</v>
       </c>
       <c r="G97">
         <v>4069.6</v>
@@ -9247,28 +9247,28 @@
         <v>3390</v>
       </c>
       <c r="M97">
-        <v>1227.192780242995</v>
+        <v>1240.110598982395</v>
       </c>
       <c r="N97">
-        <v>2162.807219757005</v>
+        <v>2149.889401017605</v>
       </c>
       <c r="O97">
-        <v>432.5614439514009</v>
+        <v>429.977880203521</v>
       </c>
       <c r="P97">
-        <v>1730.245775805604</v>
+        <v>1719.911520814084</v>
       </c>
       <c r="Q97">
-        <v>4512.445775805603</v>
+        <v>4502.111520814084</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.053025712848667</v>
+        <v>1.301723419724881</v>
       </c>
       <c r="T97">
-        <v>15.58146144160635</v>
+        <v>19.42873587163261</v>
       </c>
       <c r="U97">
         <v>0.07363097776675757</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.762402170691348</v>
+        <v>2.733627148079979</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.108617527713865</v>
+        <v>0.1086242266825609</v>
       </c>
       <c r="C98">
-        <v>639.2795735786021</v>
+        <v>463.2766623886346</v>
       </c>
       <c r="D98">
-        <v>13411.9195735786</v>
+        <v>13411.35666238863</v>
       </c>
       <c r="E98">
-        <v>13062.44</v>
+        <v>13237.88</v>
       </c>
       <c r="F98">
-        <v>16842.24</v>
+        <v>17017.68</v>
       </c>
       <c r="G98">
         <v>4069.6</v>
@@ -9329,28 +9329,28 @@
         <v>3390</v>
       </c>
       <c r="M98">
-        <v>1240.110598982395</v>
+        <v>1253.028417721795</v>
       </c>
       <c r="N98">
-        <v>2149.889401017605</v>
+        <v>2136.971582278205</v>
       </c>
       <c r="O98">
-        <v>429.977880203521</v>
+        <v>427.394316455641</v>
       </c>
       <c r="P98">
-        <v>1719.911520814084</v>
+        <v>1709.577265822564</v>
       </c>
       <c r="Q98">
-        <v>4502.111520814084</v>
+        <v>4491.777265822564</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.301723419724878</v>
+        <v>1.716219597851901</v>
       </c>
       <c r="T98">
-        <v>19.42873587163256</v>
+        <v>25.84085992167632</v>
       </c>
       <c r="U98">
         <v>0.07363097776675757</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.73362714807998</v>
+        <v>2.705445424903898</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1086242266825609</v>
+        <v>0.1086309256512569</v>
       </c>
       <c r="C99">
-        <v>463.2766623886346</v>
+        <v>287.273798448532</v>
       </c>
       <c r="D99">
-        <v>13411.35666238863</v>
+        <v>13410.79379844853</v>
       </c>
       <c r="E99">
-        <v>13237.88</v>
+        <v>13413.32</v>
       </c>
       <c r="F99">
-        <v>17017.68</v>
+        <v>17193.12</v>
       </c>
       <c r="G99">
         <v>4069.6</v>
@@ -9411,28 +9411,28 @@
         <v>3390</v>
       </c>
       <c r="M99">
-        <v>1253.028417721795</v>
+        <v>1265.946236461195</v>
       </c>
       <c r="N99">
-        <v>2136.971582278205</v>
+        <v>2124.053763538805</v>
       </c>
       <c r="O99">
-        <v>427.394316455641</v>
+        <v>424.810752707761</v>
       </c>
       <c r="P99">
-        <v>1709.577265822564</v>
+        <v>1699.243010831044</v>
       </c>
       <c r="Q99">
-        <v>4491.777265822564</v>
+        <v>4481.443010831044</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.716219597851901</v>
+        <v>2.545211954105945</v>
       </c>
       <c r="T99">
-        <v>25.84085992167632</v>
+        <v>38.66510802176381</v>
       </c>
       <c r="U99">
         <v>0.07363097776675757</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.705445424903898</v>
+        <v>2.67783883893549</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1086309256512569</v>
+        <v>0.1086376246199528</v>
       </c>
       <c r="C100">
-        <v>287.273798448532</v>
+        <v>111.2709817523501</v>
       </c>
       <c r="D100">
-        <v>13410.79379844853</v>
+        <v>13410.23098175235</v>
       </c>
       <c r="E100">
-        <v>13413.32</v>
+        <v>13588.76</v>
       </c>
       <c r="F100">
-        <v>17193.12</v>
+        <v>17368.56</v>
       </c>
       <c r="G100">
         <v>4069.6</v>
@@ -9493,28 +9493,28 @@
         <v>3390</v>
       </c>
       <c r="M100">
-        <v>1265.946236461195</v>
+        <v>1278.864055200595</v>
       </c>
       <c r="N100">
-        <v>2124.053763538805</v>
+        <v>2111.135944799405</v>
       </c>
       <c r="O100">
-        <v>424.810752707761</v>
+        <v>422.227188959881</v>
       </c>
       <c r="P100">
-        <v>1699.243010831044</v>
+        <v>1688.908755839524</v>
       </c>
       <c r="Q100">
-        <v>4481.443010831044</v>
+        <v>4471.108755839524</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.545211954105945</v>
+        <v>5.03218902286808</v>
       </c>
       <c r="T100">
-        <v>38.66510802176381</v>
+        <v>77.13785232202632</v>
       </c>
       <c r="U100">
         <v>0.07363097776675757</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.67783883893549</v>
+        <v>2.650789961774525</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1086376246199528</v>
-      </c>
-      <c r="C101">
-        <v>111.2709817523501</v>
-      </c>
-      <c r="D101">
-        <v>13410.23098175235</v>
-      </c>
-      <c r="E101">
-        <v>13588.76</v>
-      </c>
-      <c r="F101">
-        <v>17368.56</v>
-      </c>
-      <c r="G101">
-        <v>4069.6</v>
-      </c>
-      <c r="H101">
-        <v>13764.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6172.2</v>
-      </c>
-      <c r="K101">
-        <v>2782.2</v>
-      </c>
-      <c r="L101">
-        <v>3390</v>
-      </c>
-      <c r="M101">
-        <v>1278.864055200595</v>
-      </c>
-      <c r="N101">
-        <v>2111.135944799405</v>
-      </c>
-      <c r="O101">
-        <v>422.227188959881</v>
-      </c>
-      <c r="P101">
-        <v>1688.908755839524</v>
-      </c>
-      <c r="Q101">
-        <v>4471.108755839524</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.03218902286808</v>
-      </c>
-      <c r="T101">
-        <v>77.13785232202632</v>
-      </c>
-      <c r="U101">
-        <v>0.07363097776675757</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05890478221340606</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.650789961774525</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
